--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined.xlsx
@@ -735,7 +735,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9214285714285715</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -748,9 +748,13 @@
         </is>
       </c>
       <c r="Z2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Stakeholder Feedback Solicitation</t>
+        </is>
+      </c>
       <c r="AB2" t="b">
         <v>0</v>
       </c>
@@ -906,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9628571428571429</v>
+        <v>0.95</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
@@ -1073,7 +1077,7 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9214285714285715</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1086,9 +1090,13 @@
         </is>
       </c>
       <c r="Z4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Creative Thinking</t>
+        </is>
+      </c>
       <c r="AB4" t="b">
         <v>0</v>
       </c>
@@ -1244,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9557142857142856</v>
+        <v>0.95</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
@@ -1399,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9571428571428571</v>
+        <v>0.95</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
@@ -1408,9 +1416,13 @@
         </is>
       </c>
       <c r="Z6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Idea Generation</t>
+        </is>
+      </c>
       <c r="AB6" t="b">
         <v>0</v>
       </c>
@@ -1554,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.95</v>
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
@@ -1563,9 +1575,13 @@
         </is>
       </c>
       <c r="Z7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Stakeholder Feedback Solicitation</t>
+        </is>
+      </c>
       <c r="AB7" t="b">
         <v>0</v>
       </c>
@@ -1713,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.92</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1726,9 +1742,13 @@
         </is>
       </c>
       <c r="Z8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Solution Viability Assessment</t>
+        </is>
+      </c>
       <c r="AB8" t="b">
         <v>0</v>
       </c>
@@ -1884,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9614285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
@@ -1893,9 +1913,13 @@
         </is>
       </c>
       <c r="Z9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Issue Scope Definition</t>
+        </is>
+      </c>
       <c r="AB9" t="b">
         <v>0</v>
       </c>
@@ -2043,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.9614285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
@@ -2052,9 +2076,13 @@
         </is>
       </c>
       <c r="Z10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Solution Presentation</t>
+        </is>
+      </c>
       <c r="AB10" t="b">
         <v>0</v>
       </c>
@@ -2099,7 +2127,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Information Research</t>
+          <t>Research Information Gathering</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2195,25 +2223,25 @@
         </is>
       </c>
       <c r="V11" t="b">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>keep:4, "Information Research":3</t>
+        </is>
+      </c>
+      <c r="Z11" t="b">
         <v>1</v>
       </c>
-      <c r="W11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>keep:3, "Information Research":4</t>
-        </is>
-      </c>
-      <c r="Z11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Idea Viability Evaluation</t>
+        </is>
+      </c>
       <c r="AB11" t="b">
         <v>0</v>
       </c>
@@ -2361,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.95</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2370,7 +2398,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:4, "Solution Presentation":3</t>
         </is>
       </c>
       <c r="Z12" t="b">
@@ -2528,22 +2556,26 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>keep:6, "Solution Refinement":1</t>
+          <t>keep:0, "Solution Refinement":7</t>
         </is>
       </c>
       <c r="Z13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Solution Viability Assessment</t>
+        </is>
+      </c>
       <c r="AB13" t="b">
         <v>0</v>
       </c>
@@ -2687,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.95</v>
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
@@ -2696,9 +2728,13 @@
         </is>
       </c>
       <c r="Z14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Idea Viability Evaluation</t>
+        </is>
+      </c>
       <c r="AB14" t="b">
         <v>0</v>
       </c>
@@ -2850,7 +2886,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.95</v>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
@@ -2859,9 +2895,13 @@
         </is>
       </c>
       <c r="Z15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Stakeholder Viewpoint Elicitation</t>
+        </is>
+      </c>
       <c r="AB15" t="b">
         <v>0</v>
       </c>
@@ -2906,7 +2946,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Team Facilitation</t>
+          <t>Discussion Facilitation</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3010,21 +3050,29 @@
         </is>
       </c>
       <c r="V16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9528571428571428</v>
-      </c>
-      <c r="X16" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/7: </t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:2, "Discussion Facilitation":5</t>
         </is>
       </c>
       <c r="Z16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Teamwork</t>
+        </is>
+      </c>
       <c r="AB16" t="b">
         <v>0</v>
       </c>
@@ -3177,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
@@ -3329,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
@@ -3489,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.95</v>
       </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr">
@@ -3641,12 +3689,12 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9528571428571428</v>
+        <v>0.95</v>
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:4, "Improvement Requirements Communication":3</t>
         </is>
       </c>
       <c r="Z20" t="b">
@@ -3797,16 +3845,16 @@
         <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9339999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>keep:2, "Insight Presentation":5</t>
+          <t>keep:3, "Insight Presentation":4</t>
         </is>
       </c>
       <c r="Z21" t="b">
@@ -3957,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.9142857142857144</v>
+        <v>0.95</v>
       </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
@@ -3970,13 +4018,9 @@
       </c>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Foundation skill (reading/interpretation) implicit in PCs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -4121,12 +4165,12 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.9566666666666667</v>
+        <v>0.95</v>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>keep:6, "Review Outcome Documentation":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z23" t="b">
@@ -4281,7 +4325,7 @@
         <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>0.9400000000000002</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -4445,16 +4489,16 @@
         <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>0.92</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>keep:1, "Practice Review":6</t>
+          <t>keep:0, "Practice Review":7</t>
         </is>
       </c>
       <c r="Z25" t="b">
@@ -4609,7 +4653,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.95</v>
       </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr">
@@ -4761,7 +4805,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0.9557142857142856</v>
+        <v>0.95</v>
       </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
@@ -4917,7 +4961,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.95</v>
       </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr">
@@ -5077,7 +5121,7 @@
         <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>0.9614285714285714</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -5086,7 +5130,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Technology Platform Utilisation":1</t>
         </is>
       </c>
       <c r="Z29" t="b">
@@ -5241,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.9542857142857143</v>
+        <v>0.95</v>
       </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr">
@@ -5401,7 +5445,7 @@
         <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -5676,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>0.9628571428571429</v>
+        <v>0.95</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -5839,7 +5883,7 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.9542857142857143</v>
+        <v>0.95</v>
       </c>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr">
@@ -5895,7 +5939,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Device Configuration Setup</t>
+          <t>Device Setup</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5991,21 +6035,29 @@
         </is>
       </c>
       <c r="V36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>0.958</v>
-      </c>
-      <c r="X36" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>keep:5, "Device Configuration":2</t>
+          <t>keep:2, "Device Setup":4, "Device Configuration":1</t>
         </is>
       </c>
       <c r="Z36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Device Inventory Management</t>
+        </is>
+      </c>
       <c r="AB36" t="b">
         <v>0</v>
       </c>
@@ -6149,7 +6201,7 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.9542857142857143</v>
+        <v>0.95</v>
       </c>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr">
@@ -6321,7 +6373,7 @@
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>keep:5, "Device Register Management":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z38" t="b">
@@ -6535,7 +6587,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Password Strength Creation</t>
+          <t>Password Creation</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -6631,15 +6683,19 @@
         </is>
       </c>
       <c r="V40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
-        <v>0.9571428571428571</v>
-      </c>
-      <c r="X40" t="inlineStr"/>
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 7/7: </t>
+        </is>
+      </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:0, "Password Creation":7</t>
         </is>
       </c>
       <c r="Z40" t="b">
@@ -6797,12 +6853,12 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>keep:6, "Physical Security Plan Development":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z41" t="b">
@@ -6956,7 +7012,7 @@
         <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>0.9257142857142856</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -6965,7 +7021,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>keep:0, "Data Risk Categorisation/Risk Categorisation":7</t>
+          <t>keep:0, "Data Risk Categorisation":7</t>
         </is>
       </c>
       <c r="Z42" t="b">
@@ -7123,7 +7179,7 @@
         <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>0.9214285714285715</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -7132,7 +7188,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:0, "Physical Security Plan Communication":7</t>
+          <t>keep:0, "Physical Security Plan Communication/Physical Security Communication":7</t>
         </is>
       </c>
       <c r="Z43" t="b">
@@ -7294,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.96</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
@@ -7457,7 +7513,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0.9557142857142856</v>
+        <v>0.95</v>
       </c>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr">
@@ -7616,12 +7672,12 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.958</v>
+        <v>0.9516666666666667</v>
       </c>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>keep:5, "Security Development Monitoring":2</t>
+          <t>keep:6, "Security Development Monitoring":1</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -7779,7 +7835,7 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr">
@@ -7835,7 +7891,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Multi-factor Authentication Enablement</t>
+          <t>Two-factor Authentication Enablement</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -7942,16 +7998,16 @@
         <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>keep:0, "Multi-factor Authentication Enablement":7</t>
+          <t>keep:6, "Multi-factor Authentication Enablement":1</t>
         </is>
       </c>
       <c r="Z48" t="b">
@@ -8092,7 +8148,7 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0.9571428571428571</v>
+        <v>0.95</v>
       </c>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr">
@@ -8242,7 +8298,7 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0.9528571428571428</v>
+        <v>0.95</v>
       </c>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr">
@@ -8388,7 +8444,7 @@
         <v>1</v>
       </c>
       <c r="W51" t="n">
-        <v>0.9528571428571428</v>
+        <v>0.95</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -8543,7 +8599,7 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>keep:5, "Evaluation Documentation":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z52" t="b">
@@ -8594,7 +8650,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ICT Gap Identification</t>
+          <t>Ict Gap Identification</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -8693,19 +8749,15 @@
         </is>
       </c>
       <c r="V53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0.9500000000000001</v>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 7/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>keep:0, "ICT Gap Identification":7</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z53" t="b">
@@ -8862,7 +8914,7 @@
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr">
@@ -9008,12 +9060,12 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:5, "Innovative Idea Investigation":2</t>
         </is>
       </c>
       <c r="Z55" t="b">
@@ -9064,7 +9116,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Numerical Data Interpretation</t>
+          <t>Financial Impact Interpretation</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -9151,15 +9203,19 @@
         </is>
       </c>
       <c r="V56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" t="n">
-        <v>0.9533333333333333</v>
-      </c>
-      <c r="X56" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>keep:6, "Financial Impact Analysis":1</t>
+          <t>keep:0, "Financial Impact Interpretation":4, "Financial Impact Assessment":3</t>
         </is>
       </c>
       <c r="Z56" t="b">
@@ -9300,12 +9356,12 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>0.9533333333333333</v>
+        <v>0.95</v>
       </c>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>keep:6, "Action Plan Detailing":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z57" t="b">
@@ -9446,7 +9502,7 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr">
@@ -9592,7 +9648,7 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.95</v>
       </c>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr">
@@ -9750,7 +9806,7 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr">
@@ -9912,7 +9968,7 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>0.9557142857142856</v>
+        <v>0.9528571428571428</v>
       </c>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr">
@@ -10058,7 +10114,7 @@
         <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>0.9471428571428572</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr">
@@ -10204,7 +10260,7 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>0.9614285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr">
@@ -10260,7 +10316,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Complex Text Analysis</t>
+          <t>Legislative Text Analysis</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -10350,15 +10406,19 @@
         </is>
       </c>
       <c r="V64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W64" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X64" t="inlineStr"/>
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 7/7: </t>
+        </is>
+      </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:0, "Legislative Text Analysis":7</t>
         </is>
       </c>
       <c r="Z64" t="b">
@@ -10502,12 +10562,12 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>0.9566666666666667</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>keep:6, "Compliance Assessment":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z65" t="b">
@@ -10651,7 +10711,7 @@
         <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>0.9557142857142856</v>
+        <v>0.95</v>
       </c>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr">
@@ -10800,12 +10860,12 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Feedback Management":1</t>
         </is>
       </c>
       <c r="Z67" t="b">
@@ -10949,7 +11009,7 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr">
@@ -11098,7 +11158,7 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.95</v>
       </c>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr">
@@ -11247,7 +11307,7 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr">
@@ -11396,7 +11456,7 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.95</v>
       </c>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr">
@@ -11405,9 +11465,13 @@
         </is>
       </c>
       <c r="Z71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA71" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Policy Distribution</t>
+        </is>
+      </c>
       <c r="AB71" t="b">
         <v>0</v>
       </c>
@@ -11545,7 +11609,7 @@
         <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>0.9571428571428571</v>
+        <v>0.95</v>
       </c>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr">
@@ -11694,7 +11758,7 @@
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>0.9528571428571428</v>
+        <v>0.95</v>
       </c>
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr">
@@ -11843,7 +11907,7 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr">
@@ -11992,7 +12056,7 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>0.9542857142857143</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr">
@@ -12141,12 +12205,12 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0.9557142857142856</v>
+        <v>0.952</v>
       </c>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:5, "Digital Information Security":2</t>
         </is>
       </c>
       <c r="Z76" t="b">
@@ -12197,7 +12261,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Stakeholder Communication</t>
+          <t>Policy Distribution</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -12287,21 +12351,29 @@
         </is>
       </c>
       <c r="V77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W77" t="n">
-        <v>0.9542857142857143</v>
-      </c>
-      <c r="X77" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/7: </t>
+        </is>
+      </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:2, "Policy Distribution":5</t>
         </is>
       </c>
       <c r="Z77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA77" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Policy Distribution</t>
+        </is>
+      </c>
       <c r="AB77" t="b">
         <v>0</v>
       </c>
@@ -12439,7 +12511,7 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>0.9557142857142856</v>
+        <v>0.95</v>
       </c>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr">
@@ -12595,7 +12667,7 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.95</v>
       </c>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr">
@@ -12651,7 +12723,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Blockchain Anomaly Resolution</t>
+          <t>Blockchain Problem Solving</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -12748,19 +12820,15 @@
         </is>
       </c>
       <c r="V80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>0.9179999999999999</v>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:2, "Blockchain Anomaly Resolution":5</t>
+          <t>keep:2, "Blockchain Anomaly Resolution":3, "Blockchain Anomaly Problem Solving":2</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -12768,9 +12836,13 @@
       </c>
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC80" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Foundation Skill 'Problem solving' is already implicit in many performance criteria and other skills; it does not represent a distinct activity specific to this unit</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -12911,7 +12983,7 @@
         <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr">
@@ -13067,7 +13139,7 @@
         <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>0.9557142857142856</v>
+        <v>0.95</v>
       </c>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr">
@@ -13223,12 +13295,12 @@
         <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>0.9559999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>keep:5, "Design Plan Documentation":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z83" t="b">
@@ -13379,18 +13451,22 @@
         <v>0</v>
       </c>
       <c r="W84" t="n">
-        <v>0.9533333333333333</v>
+        <v>0.95</v>
       </c>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>keep:6, "Documentation Submission Management":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA84" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>Design Documentation Preparation</t>
+        </is>
+      </c>
       <c r="AB84" t="b">
         <v>0</v>
       </c>
@@ -13535,7 +13611,7 @@
         <v>0</v>
       </c>
       <c r="W85" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr">
@@ -13691,7 +13767,7 @@
         <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr">
@@ -13747,7 +13823,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Maintenance Testing Execution</t>
+          <t>Maintenance Testing</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -13844,15 +13920,19 @@
         </is>
       </c>
       <c r="V87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W87" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X87" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 6/7: </t>
+        </is>
+      </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>keep:4, "Maintenance Testing":3</t>
+          <t>keep:1, "Maintenance Testing":6</t>
         </is>
       </c>
       <c r="Z87" t="b">
@@ -13903,7 +13983,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Security Platform Determination</t>
+          <t>Security Platform Selection</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -14000,19 +14080,15 @@
         </is>
       </c>
       <c r="V88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>keep:1, "Security Platform Determination/Security and Platform Determination":4, "Security and Platform Selection":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z88" t="b">
@@ -14163,7 +14239,7 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>0.9542857142857143</v>
+        <v>0.95</v>
       </c>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr">
@@ -14319,7 +14395,7 @@
         <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>0.9571428571428571</v>
+        <v>0.95</v>
       </c>
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr">
@@ -14475,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>0.9571428571428571</v>
+        <v>0.95</v>
       </c>
       <c r="X91" t="inlineStr"/>
       <c r="Y91" t="inlineStr">
@@ -14631,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>0.9528571428571428</v>
+        <v>0.95</v>
       </c>
       <c r="X92" t="inlineStr"/>
       <c r="Y92" t="inlineStr">
@@ -14787,7 +14863,7 @@
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>0.9557142857142856</v>
+        <v>0.95</v>
       </c>
       <c r="X93" t="inlineStr"/>
       <c r="Y93" t="inlineStr">
@@ -14946,7 +15022,7 @@
         <v>1</v>
       </c>
       <c r="W94" t="n">
-        <v>0.9357142857142856</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -15117,7 +15193,7 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>0.9571428571428571</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr">
@@ -15276,7 +15352,7 @@
         <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.95</v>
       </c>
       <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr">
@@ -15435,7 +15511,7 @@
         <v>1</v>
       </c>
       <c r="W97" t="n">
-        <v>0.9566666666666667</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -15602,7 +15678,7 @@
         <v>1</v>
       </c>
       <c r="W98" t="n">
-        <v>0.92</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -15761,7 +15837,7 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>0.9614285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr">
@@ -15924,7 +16000,7 @@
         <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>0.9571428571428571</v>
+        <v>0.95</v>
       </c>
       <c r="X100" t="inlineStr"/>
       <c r="Y100" t="inlineStr">
@@ -15933,9 +16009,13 @@
         </is>
       </c>
       <c r="Z100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA100" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>Threat Risk Assessment</t>
+        </is>
+      </c>
       <c r="AB100" t="b">
         <v>0</v>
       </c>
@@ -16083,7 +16163,7 @@
         <v>1</v>
       </c>
       <c r="W101" t="n">
-        <v>0.92</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -16246,7 +16326,7 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>0.9557142857142856</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X102" t="inlineStr"/>
       <c r="Y102" t="inlineStr">
@@ -16405,12 +16485,12 @@
         <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>0.96</v>
+        <v>0.9528571428571428</v>
       </c>
       <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>keep:6, "Log Ingestion":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z103" t="b">
@@ -16564,7 +16644,7 @@
         <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>0.9542857142857143</v>
+        <v>0.95</v>
       </c>
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr">
@@ -16723,7 +16803,7 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>0.9571428571428571</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr">
@@ -17029,7 +17109,7 @@
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>0.9557142857142856</v>
+        <v>0.95</v>
       </c>
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr">
@@ -17182,12 +17262,12 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>0.9566666666666667</v>
+        <v>0.95</v>
       </c>
       <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>keep:6, "Critical Infrastructure Protection Research":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z108" t="b">
@@ -17335,7 +17415,7 @@
         <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>0.9628571428571429</v>
+        <v>0.95</v>
       </c>
       <c r="X109" t="inlineStr"/>
       <c r="Y109" t="inlineStr">
@@ -17488,7 +17568,7 @@
         <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr">
@@ -17641,7 +17721,7 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>0.9557142857142856</v>
+        <v>0.95</v>
       </c>
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr">
@@ -17794,7 +17874,7 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>0.9557142857142856</v>
+        <v>0.95</v>
       </c>
       <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr">
@@ -18003,7 +18083,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Protection Plan Analysis</t>
+          <t>Critical Infrastructure Protection Analysis</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -18097,15 +18177,19 @@
         </is>
       </c>
       <c r="V114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W114" t="n">
-        <v>0.9583333333333334</v>
-      </c>
-      <c r="X114" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 6/7: </t>
+        </is>
+      </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>keep:6, "Critical Infrastructure Protection Analysis":1</t>
+          <t>keep:1, "Critical Infrastructure Protection Analysis":6</t>
         </is>
       </c>
       <c r="Z114" t="b">
@@ -18253,12 +18337,12 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>keep:6, "Protection Plan Development":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z115" t="b">
@@ -18309,7 +18393,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Protection Plan Testing</t>
+          <t>Protection Testing Execution</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -18403,19 +18487,15 @@
         </is>
       </c>
       <c r="V116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W116" t="n">
-        <v>0.9259999999999999</v>
-      </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X116" t="inlineStr"/>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>keep:2, "Protection Plan Testing":5</t>
+          <t>keep:5, "Protection Plan Testing":2</t>
         </is>
       </c>
       <c r="Z116" t="b">
@@ -18563,7 +18643,7 @@
         <v>0</v>
       </c>
       <c r="W117" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X117" t="inlineStr"/>
       <c r="Y117" t="inlineStr">
@@ -18619,7 +18699,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Risk Assessment Evaluation</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -18713,15 +18793,19 @@
         </is>
       </c>
       <c r="V118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W118" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="X118" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/7: </t>
+        </is>
+      </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:6, "Risk Assessment":1</t>
+          <t>keep:0, "Risk Assessment":5, "Risk Evaluation":2</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -18869,7 +18953,7 @@
         <v>0</v>
       </c>
       <c r="W119" t="n">
-        <v>0.9614285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X119" t="inlineStr"/>
       <c r="Y119" t="inlineStr">
@@ -19022,7 +19106,7 @@
         <v>0</v>
       </c>
       <c r="W120" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr">
@@ -19078,7 +19162,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Data Classification Identification</t>
+          <t>Data Type Identification</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -19182,15 +19266,19 @@
         </is>
       </c>
       <c r="V121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W121" t="n">
-        <v>0.9557142857142856</v>
-      </c>
-      <c r="X121" t="inlineStr"/>
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 7/7: </t>
+        </is>
+      </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:0, "Data Type Identification":7</t>
         </is>
       </c>
       <c r="Z121" t="b">
@@ -19344,12 +19432,12 @@
         <v>0</v>
       </c>
       <c r="W122" t="n">
-        <v>0.9516666666666667</v>
+        <v>0.95</v>
       </c>
       <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>keep:6, "Feedback Management":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z122" t="b">
@@ -19499,7 +19587,7 @@
         <v>0</v>
       </c>
       <c r="W123" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="X123" t="inlineStr"/>
       <c r="Y123" t="inlineStr">
@@ -19555,7 +19643,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Problem Solving in Security</t>
+          <t>Contextual Anomaly Identification</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -19662,22 +19750,26 @@
         <v>1</v>
       </c>
       <c r="W124" t="n">
-        <v>0.95</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:5, "Contextual Anomaly Identification":2</t>
+          <t>keep:0, "Contextual Anomaly Identification":7</t>
         </is>
       </c>
       <c r="Z124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA124" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>Problem solving</t>
+        </is>
+      </c>
       <c r="AB124" t="b">
         <v>0</v>
       </c>
@@ -19722,7 +19814,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Security Requirements Documentation</t>
+          <t>Security Architecture Documentation</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -19822,19 +19914,15 @@
         </is>
       </c>
       <c r="V125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 7/7: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="X125" t="inlineStr"/>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>keep:0, "Security Requirements Documentation":7</t>
+          <t>keep:6, "Security Findings Documentation":1</t>
         </is>
       </c>
       <c r="Z125" t="b">
@@ -19988,7 +20076,7 @@
         <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>0.9557142857142856</v>
+        <v>0.9528571428571428</v>
       </c>
       <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr">
@@ -20147,7 +20235,7 @@
         <v>0</v>
       </c>
       <c r="W127" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.9542857142857143</v>
       </c>
       <c r="X127" t="inlineStr"/>
       <c r="Y127" t="inlineStr">
@@ -20310,7 +20398,7 @@
         <v>0</v>
       </c>
       <c r="W128" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.95</v>
       </c>
       <c r="X128" t="inlineStr"/>
       <c r="Y128" t="inlineStr">
@@ -20473,7 +20561,7 @@
         <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>0.9471428571428572</v>
+        <v>0.95</v>
       </c>
       <c r="X129" t="inlineStr"/>
       <c r="Y129" t="inlineStr">
@@ -20486,9 +20574,13 @@
       </c>
       <c r="AA129" t="inlineStr"/>
       <c r="AB129" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC129" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Skill is a Foundation Skill (Planning and organising) that is already implicit in the performance criteria and elements; it does not represent a distinct workplace activity</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -20628,7 +20720,7 @@
         <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>0.9642857142857143</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr">
@@ -20791,7 +20883,7 @@
         <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>0.9614285714285714</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr">
@@ -20954,7 +21046,7 @@
         <v>0</v>
       </c>
       <c r="W132" t="n">
-        <v>0.9571428571428571</v>
+        <v>0.95</v>
       </c>
       <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr">
@@ -20963,9 +21055,13 @@
         </is>
       </c>
       <c r="Z132" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA132" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>Security Architecture Documentation</t>
+        </is>
+      </c>
       <c r="AB132" t="b">
         <v>0</v>
       </c>
@@ -21010,7 +21106,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Technical Specification Reading</t>
+          <t>Technical Documentation Reading</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -21110,15 +21206,19 @@
         </is>
       </c>
       <c r="V133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W133" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="X133" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/7: </t>
+        </is>
+      </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>keep:3, "Technical Documentation Reading":3, "&lt;name&gt;":1</t>
+          <t>keep:2, "Technical Documentation Reading":5</t>
         </is>
       </c>
       <c r="Z133" t="b">
@@ -21289,7 +21389,7 @@
         <v>0</v>
       </c>
       <c r="W134" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr">
@@ -21302,9 +21402,13 @@
       </c>
       <c r="AA134" t="inlineStr"/>
       <c r="AB134" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC134" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>FS describes work style (autonomous decision making) rather than a distinct workplace activity; the capability is implicit in performance criteria and elements</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -21629,7 +21733,7 @@
         <v>0</v>
       </c>
       <c r="W136" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.95</v>
       </c>
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr">
@@ -21685,7 +21789,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Incident Response Evaluation</t>
+          <t>Incident Response Plan Evaluation</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -21798,15 +21902,19 @@
         </is>
       </c>
       <c r="V137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W137" t="n">
-        <v>0.9583333333333334</v>
-      </c>
-      <c r="X137" t="inlineStr"/>
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 7/7: </t>
+        </is>
+      </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>keep:6, "Incident Response Plan Evaluation":1</t>
+          <t>keep:0, "Incident Response Plan Evaluation":7</t>
         </is>
       </c>
       <c r="Z137" t="b">
@@ -21973,7 +22081,7 @@
         <v>0</v>
       </c>
       <c r="W138" t="n">
-        <v>0.9614285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr">
@@ -22141,7 +22249,7 @@
         <v>0</v>
       </c>
       <c r="W139" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr">
@@ -22313,16 +22421,16 @@
         <v>1</v>
       </c>
       <c r="W140" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Exercise Design":7</t>
+          <t>keep:0, "Incident Response Exercise Design/Incident Response Red‑Team Design":6, "Incident Response Red Teaming":1</t>
         </is>
       </c>
       <c r="Z140" t="b">
@@ -22489,7 +22597,7 @@
         <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.95</v>
       </c>
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr">
@@ -22545,7 +22653,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Risk Analysis</t>
+          <t>Technical Data Interpretation</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -22662,15 +22770,19 @@
         </is>
       </c>
       <c r="V142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W142" t="n">
-        <v>0.9214285714285715</v>
-      </c>
-      <c r="X142" t="inlineStr"/>
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 7/7: </t>
+        </is>
+      </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:0, "Technical Data Interpretation/Data Interpretation":7</t>
         </is>
       </c>
       <c r="Z142" t="b">
@@ -22845,7 +22957,7 @@
         <v>0</v>
       </c>
       <c r="W143" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr">
@@ -23021,7 +23133,7 @@
         <v>0</v>
       </c>
       <c r="W144" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr">
@@ -23210,9 +23322,13 @@
       </c>
       <c r="AA145" t="inlineStr"/>
       <c r="AB145" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC145" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Foundation Skill describing data interpretation is already embedded in multiple performance criteria (e.g., 3.2 Assist in collecting, processing and preserving evidence; 5.1 Collect, analyse and report incident management measures) and does not add a distinct capability</t>
+        </is>
+      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
@@ -23362,7 +23478,7 @@
         <v>0</v>
       </c>
       <c r="W146" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr">
@@ -24026,7 +24142,7 @@
         <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr">
@@ -24191,7 +24307,7 @@
         <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>0.9528571428571428</v>
+        <v>0.95</v>
       </c>
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="inlineStr">
@@ -24356,22 +24472,26 @@
         <v>1</v>
       </c>
       <c r="W152" t="n">
-        <v>0.9057142857142858</v>
+        <v>0.9</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>keep:0, "Business Data Analysis":7</t>
+          <t>keep:1, "Business Data Analysis":6</t>
         </is>
       </c>
       <c r="Z152" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA152" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>Numeracy</t>
+        </is>
+      </c>
       <c r="AB152" t="b">
         <v>0</v>
       </c>
@@ -24525,7 +24645,7 @@
         <v>0</v>
       </c>
       <c r="W153" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr">
@@ -24694,12 +24814,12 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>0.9485714285714285</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Plan Improvement":1</t>
         </is>
       </c>
       <c r="Z154" t="b">
@@ -24859,7 +24979,7 @@
         <v>0</v>
       </c>
       <c r="W155" t="n">
-        <v>0.9557142857142856</v>
+        <v>0.95</v>
       </c>
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr">
@@ -25024,7 +25144,7 @@
         <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr">
@@ -25080,7 +25200,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Strategic Planning</t>
+          <t>Strategy Prioritisation</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -25186,15 +25306,19 @@
         </is>
       </c>
       <c r="V157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W157" t="n">
-        <v>0.9514285714285714</v>
-      </c>
-      <c r="X157" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:3, "Strategy Prioritisation":4</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25354,7 +25478,7 @@
         <v>0</v>
       </c>
       <c r="W158" t="n">
-        <v>0.9585714285714285</v>
+        <v>0.95</v>
       </c>
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="inlineStr">
@@ -25363,9 +25487,13 @@
         </is>
       </c>
       <c r="Z158" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA158" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>Teamwork</t>
+        </is>
+      </c>
       <c r="AB158" t="b">
         <v>0</v>
       </c>
@@ -25519,7 +25647,7 @@
         <v>0</v>
       </c>
       <c r="W159" t="n">
-        <v>0.9571428571428571</v>
+        <v>0.95</v>
       </c>
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="inlineStr">
@@ -25684,7 +25812,7 @@
         <v>0</v>
       </c>
       <c r="W160" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr">

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ160"/>
+  <dimension ref="A1:AJ171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1090,13 +1090,9 @@
         </is>
       </c>
       <c r="Z4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Creative Thinking</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="b">
         <v>0</v>
       </c>
@@ -1261,9 +1257,13 @@
         </is>
       </c>
       <c r="Z5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Planning and organising</t>
+        </is>
+      </c>
       <c r="AB5" t="b">
         <v>0</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
@@ -1729,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9028571428571429</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1913,13 +1913,9 @@
         </is>
       </c>
       <c r="Z9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Issue Scope Definition</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="b">
         <v>0</v>
       </c>
@@ -2076,13 +2072,9 @@
         </is>
       </c>
       <c r="Z10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Solution Presentation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="b">
         <v>0</v>
       </c>
@@ -2127,7 +2119,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Research Information Gathering</t>
+          <t>Information Research</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2223,15 +2215,19 @@
         </is>
       </c>
       <c r="V11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X11" t="inlineStr"/>
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 7/7: </t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>keep:4, "Information Research":3</t>
+          <t>keep:0, "Information Research":7</t>
         </is>
       </c>
       <c r="Z11" t="b">
@@ -2389,7 +2385,7 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2398,7 +2394,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>keep:4, "Solution Presentation":3</t>
+          <t>keep:6, "Solution Presentation":1</t>
         </is>
       </c>
       <c r="Z12" t="b">
@@ -2556,26 +2552,22 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>keep:0, "Solution Refinement":7</t>
+          <t>keep:3, "Solution Refinement":4</t>
         </is>
       </c>
       <c r="Z13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Solution Viability Assessment</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="b">
         <v>0</v>
       </c>
@@ -3053,16 +3045,16 @@
         <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:2, "Discussion Facilitation":5</t>
+          <t>keep:0, "Discussion Facilitation":7</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -3694,7 +3686,7 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>keep:4, "Improvement Requirements Communication":3</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z20" t="b">
@@ -3845,16 +3837,16 @@
         <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>keep:3, "Insight Presentation":4</t>
+          <t>keep:4, "Insight Presentation":3</t>
         </is>
       </c>
       <c r="Z21" t="b">
@@ -5939,7 +5931,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Device Setup</t>
+          <t>Device Configuration Setup</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6035,29 +6027,21 @@
         </is>
       </c>
       <c r="V36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>keep:2, "Device Setup":4, "Device Configuration":1</t>
+          <t>keep:6, "Device Configuration":1</t>
         </is>
       </c>
       <c r="Z36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Device Inventory Management</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="b">
         <v>0</v>
       </c>
@@ -6385,9 +6369,13 @@
       </c>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>Skill name uses "Inventory" which is not in unit text; the activity is to create and maintain a register, not manage an inventory</t>
+        </is>
+      </c>
       <c r="AF38" t="inlineStr">
         <is>
           <t>Creates and updates a register of networked devices to support inventory tracking and asset management.</t>
@@ -7179,16 +7167,16 @@
         <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:0, "Physical Security Plan Communication/Physical Security Communication":7</t>
+          <t>keep:2, "Physical Security Plan Communication":5</t>
         </is>
       </c>
       <c r="Z43" t="b">
@@ -7350,7 +7338,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
@@ -7672,12 +7660,12 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.9516666666666667</v>
+        <v>0.95</v>
       </c>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>keep:6, "Security Development Monitoring":1</t>
+          <t>keep:5, "Security Development Monitoring":2</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -7998,7 +7986,7 @@
         <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -8007,7 +7995,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>keep:6, "Multi-factor Authentication Enablement":1</t>
+          <t>keep:5, "Multi-factor Authentication Enablement":2</t>
         </is>
       </c>
       <c r="Z48" t="b">
@@ -8914,7 +8902,7 @@
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr">
@@ -8970,7 +8958,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Innovative Solution Investigation</t>
+          <t>Innovative Idea Investigation</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -9057,15 +9045,19 @@
         </is>
       </c>
       <c r="V55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X55" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>keep:5, "Innovative Idea Investigation":2</t>
+          <t>keep:3, "Innovative Idea Investigation":4</t>
         </is>
       </c>
       <c r="Z55" t="b">
@@ -9968,7 +9960,7 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>0.9528571428571428</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr">
@@ -10114,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr">
@@ -10422,9 +10414,13 @@
         </is>
       </c>
       <c r="Z64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>Legislative Analysis</t>
+        </is>
+      </c>
       <c r="AB64" t="b">
         <v>0</v>
       </c>
@@ -10562,7 +10558,7 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr">
@@ -10860,12 +10856,12 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>keep:6, "Feedback Management":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z67" t="b">
@@ -11465,13 +11461,9 @@
         </is>
       </c>
       <c r="Z71" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>Policy Distribution</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA71" t="inlineStr"/>
       <c r="AB71" t="b">
         <v>0</v>
       </c>
@@ -11907,7 +11899,7 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr">
@@ -11920,9 +11912,13 @@
       </c>
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC74" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Foundation Skill 'Planning and organising' is implicit in the performance criteria and elements; it does not represent a distinct activity separate from the unit's PCs</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -12056,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr">
@@ -12205,7 +12201,7 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0.952</v>
+        <v>0.95</v>
       </c>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
@@ -12261,7 +12257,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Policy Distribution</t>
+          <t>Stakeholder Communication</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -12351,29 +12347,21 @@
         </is>
       </c>
       <c r="V77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>keep:2, "Policy Distribution":5</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>Policy Distribution</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="b">
         <v>0</v>
       </c>
@@ -12511,7 +12499,7 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr">
@@ -12667,12 +12655,12 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Blockchain Platform Installation":1</t>
         </is>
       </c>
       <c r="Z79" t="b">
@@ -12723,7 +12711,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Blockchain Problem Solving</t>
+          <t>Blockchain Anomaly Solving</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -12820,15 +12808,19 @@
         </is>
       </c>
       <c r="V80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X80" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/7: </t>
+        </is>
+      </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:2, "Blockchain Anomaly Resolution":3, "Blockchain Anomaly Problem Solving":2</t>
+          <t>keep:1, "Blockchain Anomaly Solving/Blockchain Anomaly Problem Solving":4, "Blockchain Anomaly Resolution":2</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -12836,13 +12828,9 @@
       </c>
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Foundation Skill 'Problem solving' is already implicit in many performance criteria and other skills; it does not represent a distinct activity specific to this unit</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC80" t="inlineStr"/>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -13927,12 +13915,12 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>keep:1, "Maintenance Testing":6</t>
+          <t>keep:2, "Maintenance Testing":5</t>
         </is>
       </c>
       <c r="Z87" t="b">
@@ -14720,9 +14708,13 @@
       </c>
       <c r="AA92" t="inlineStr"/>
       <c r="AB92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC92" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Foundation Skill already covered by performance criteria and other skills; not a distinct workplace activity</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -15193,7 +15185,7 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr">
@@ -15511,7 +15503,7 @@
         <v>1</v>
       </c>
       <c r="W97" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.9516666666666667</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -16009,13 +16001,9 @@
         </is>
       </c>
       <c r="Z100" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>Threat Risk Assessment</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="b">
         <v>0</v>
       </c>
@@ -16326,7 +16314,7 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X102" t="inlineStr"/>
       <c r="Y102" t="inlineStr">
@@ -16485,7 +16473,7 @@
         <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>0.9528571428571428</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr">
@@ -16494,9 +16482,13 @@
         </is>
       </c>
       <c r="Z103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA103" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>Data Log Ingestion</t>
+        </is>
+      </c>
       <c r="AB103" t="b">
         <v>0</v>
       </c>
@@ -16803,7 +16795,7 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr">
@@ -18027,12 +18019,12 @@
         <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>keep:6, "Protection Strategy Coordination":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z113" t="b">
@@ -18184,12 +18176,12 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>keep:1, "Critical Infrastructure Protection Analysis":6</t>
+          <t>keep:3, "Critical Infrastructure Protection Analysis":4</t>
         </is>
       </c>
       <c r="Z114" t="b">
@@ -18495,7 +18487,7 @@
       <c r="X116" t="inlineStr"/>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>keep:5, "Protection Plan Testing":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z116" t="b">
@@ -18800,12 +18792,12 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 4/7: </t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:0, "Risk Assessment":5, "Risk Evaluation":2</t>
+          <t>keep:2, "Risk Assessment":4, "Risk Evaluation":1</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -19759,21 +19751,21 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:0, "Contextual Anomaly Identification":7</t>
+          <t>keep:0, "Contextual Anomaly Identification/Security Anomaly Identification":7</t>
         </is>
       </c>
       <c r="Z124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA124" t="inlineStr"/>
+      <c r="AB124" t="b">
         <v>1</v>
       </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>Problem solving</t>
-        </is>
-      </c>
-      <c r="AB124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC124" t="inlineStr"/>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Foundation Skill 'Problem solving' is already implicit in performance criteria and other skills; it does not represent a distinct activity in this unit</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
@@ -19917,12 +19909,12 @@
         <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X125" t="inlineStr"/>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>keep:6, "Security Findings Documentation":1</t>
+          <t>keep:4, "Security Findings Documentation":3</t>
         </is>
       </c>
       <c r="Z125" t="b">
@@ -20076,7 +20068,7 @@
         <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>0.9528571428571428</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr">
@@ -20235,7 +20227,7 @@
         <v>0</v>
       </c>
       <c r="W127" t="n">
-        <v>0.9542857142857143</v>
+        <v>0.95</v>
       </c>
       <c r="X127" t="inlineStr"/>
       <c r="Y127" t="inlineStr">
@@ -20578,7 +20570,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Skill is a Foundation Skill (Planning and organising) that is already implicit in the performance criteria and elements; it does not represent a distinct workplace activity</t>
+          <t>FS describes work style (planning and organising) implicit in PCs, not a distinct skill</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -20720,7 +20712,7 @@
         <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr">
@@ -20883,7 +20875,7 @@
         <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr">
@@ -21406,7 +21398,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>FS describes work style (autonomous decision making) rather than a distinct workplace activity; the capability is implicit in performance criteria and elements</t>
+          <t>FS describes work style (autonomous decision making) rather than a distinct workplace activity; the capability is already implicit in performance criteria</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -21565,12 +21557,12 @@
         <v>0</v>
       </c>
       <c r="W135" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Forensic Evidence Procedure Development":1</t>
         </is>
       </c>
       <c r="Z135" t="b">
@@ -21738,7 +21730,7 @@
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:5, "Incident Report Preparation":2</t>
         </is>
       </c>
       <c r="Z136" t="b">
@@ -22597,12 +22589,12 @@
         <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Communication Effectiveness Assessment":1</t>
         </is>
       </c>
       <c r="Z141" t="b">
@@ -22773,7 +22765,7 @@
         <v>1</v>
       </c>
       <c r="W142" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9028571428571429</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
@@ -23326,7 +23318,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Foundation Skill describing data interpretation is already embedded in multiple performance criteria (e.g., 3.2 Assist in collecting, processing and preserving evidence; 5.1 Collect, analyse and report incident management measures) and does not add a distinct capability</t>
+          <t>Foundation Skill implicit in performance criteria; interpreting and documenting technical data is already required in multiple PCs (e.g., evidence collection, incident analysis) and does not add a distinct standalone capability</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -24472,16 +24464,16 @@
         <v>1</v>
       </c>
       <c r="W152" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>keep:1, "Business Data Analysis":6</t>
+          <t>keep:0, "Business Data Analysis":7</t>
         </is>
       </c>
       <c r="Z152" t="b">
@@ -24489,7 +24481,7 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>Numeracy</t>
+          <t>Risk Analysis</t>
         </is>
       </c>
       <c r="AB152" t="b">
@@ -24814,18 +24806,22 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>keep:6, "Plan Improvement":1</t>
+          <t>keep:5, "Plan Improvement":2</t>
         </is>
       </c>
       <c r="Z154" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA154" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>Problem solving</t>
+        </is>
+      </c>
       <c r="AB154" t="b">
         <v>0</v>
       </c>
@@ -25313,12 +25309,12 @@
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:3, "Strategy Prioritisation":4</t>
+          <t>keep:2, "Strategy Prioritisation":5</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25487,13 +25483,9 @@
         </is>
       </c>
       <c r="Z158" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA158" t="inlineStr"/>
       <c r="AB158" t="b">
         <v>0</v>
       </c>
@@ -25852,6 +25844,1333 @@
         <v>0</v>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>BSBCRT512</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Originate and develop concepts</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Response Substantiation</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>INTERPERSONAL</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>APPLY</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>PRACTICAL</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>evidence based answers, stakeholder queries, substantiated responses, data support, reasoning justification</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>3.2 Respond to questions with substantiated answers</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>1. Scope issue
+2. Generate and present solutions
+3. Refine solutions for implementation</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>1.1 Select issue to be explored in consultation with relevant personnel
+1.2 Assess possible solutions to business issue and identify restrictions according to job role and organisational policy
+1.3 Research information on possible solutions to identified issue
+1.4 Assess factors affecting viability of possible solutions
+2.1 Brainstorm ideas for addressing issue
+2.2 Evaluate ideas against identified factors affecting viability
+2.3 Compare ideas with best practice examples of similar products or programs or processes or services
+2.4 Select and present a solution in relevant format to stakeholders
+3.1 Seek feedback on ideas from stakeholders
+3.2 Respond to questions with substantiated answers
+3.3 Document feedback according to organisational requirements
+3.4 Refine and finalise solution according to task requirements</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>Learning | Reflects and evaluates methods used to develop concepts and seeks ways to improve | Actively elicits views and opinions of others to develop and refine ideas
+Oral communication | Expresses thoughtful and challenging opinions using engaging language and non-verbal features | Elicits views and information from others using a range of active listening and questioning techniques
+Reading | Interprets and evaluates a range of complex information
+Writing | Documents findings and ideas using language and structure to suit the purpose | Prepares proposals and plans for relevant stakeholders incorporating appropriate vocabulary and grammatical structures
+Teamwork | Collaborates with others to achieve joint outcomes, playing an active role in facilitating effective group interaction and influencing direction | Selects and uses appropriate conventions and protocols when communicating with internal and external stakeholders to seek or share information
+Planning and organising | Uses systematic, analytical processes in complex, non-routine situations to gather and evaluate possible concepts, and select the most appropriate concept for development | Monitors outcomes, considering results from a range of perspectives and identifying key concepts and principles that may be adaptable to future situations
+Technology | Uses main features and functions of digital tools to complete work tasks and access information</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>This unit describes the skills and knowledge required to originate and develop concepts for products, programs, processes or services to an operational level.
+The unit applies to individuals who develop concepts for any business or community activity or process. This may include marketing and advertising campaigns, staff development programs, information technology and communication systems, radio and television programs and entertainment events. These individuals operate with a high degree of autonomy and also collaborate with others to generate ideas and refine concepts for implementation.
+No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr"/>
+      <c r="W161" t="inlineStr"/>
+      <c r="X161" t="inlineStr"/>
+      <c r="Y161" t="inlineStr"/>
+      <c r="Z161" t="inlineStr"/>
+      <c r="AA161" t="inlineStr"/>
+      <c r="AB161" t="inlineStr"/>
+      <c r="AC161" t="inlineStr"/>
+      <c r="AD161" t="inlineStr"/>
+      <c r="AE161" t="inlineStr"/>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="inlineStr"/>
+      <c r="AH161" t="inlineStr"/>
+      <c r="AI161" t="inlineStr"/>
+      <c r="AJ161" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>BSBXCS401</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Maintain security of digital devices</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Device Data Identification</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>DOMAIN_KNOWLEDGE</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>ASSIST</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>THEORETICAL</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>1.2 Confirm what information is held on the registered devices</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>1. Identify appropriate security for digital devices
+2. Apply protection strategies to digital devices
+3. Evaluate effectiveness of applied protection strategies
+4. Patch software across multiple devices</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>1.1 Create and maintain register of digital devices on organisation’s network
+1.2 Confirm what information is held on the registered devices
+1.3 Categorise level of risk associated with each device based on sensitivity of information stored
+1.4 Select required security protocol to manage level of risk associated with each device
+2.1 Install and run latest anti-malware on each device
+2.2 Create strong passwords across personal and work accounts
+2.3 Switch on two-factor authentication where available
+2.4 Encrypt devices according to instructions
+2.5 Develop associated physical security plan and communicate this to whole organisation
+3.1 Review number of breaches and business impact over review period
+3.2 Monitor latest developments in digital security
+3.3 Support organisation to select most appropriate security strategies
+4.1 Apply updates to software and applications across own desktop and mobile devices
+4.2 Ensure that new devices are updated and configured correctly as part of initial start-up procedure</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>Learning | Modifies behaviour following exposure to new information
+Numeracy | Interprets mathematical data | Completes at times complex calculations and records mathematical data
+Reading | Recognises and interprets information from relevant sources to determine organisational expectations relating to cyber security
+Technology | Uses appropriate technology platforms to assist with protection strategies relating to cyber security</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>This unit describes the skills and knowledge required ensure the cyber security of digital devices.
+It applies to those working in a broad range of industries who as part of their job role ensure the security of digital devices used.
+No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr"/>
+      <c r="W162" t="inlineStr"/>
+      <c r="X162" t="inlineStr"/>
+      <c r="Y162" t="inlineStr"/>
+      <c r="Z162" t="inlineStr"/>
+      <c r="AA162" t="inlineStr"/>
+      <c r="AB162" t="inlineStr"/>
+      <c r="AC162" t="inlineStr"/>
+      <c r="AD162" t="inlineStr"/>
+      <c r="AE162" t="inlineStr"/>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="inlineStr"/>
+      <c r="AH162" t="inlineStr"/>
+      <c r="AI162" t="inlineStr"/>
+      <c r="AJ162" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ICTICT532</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Apply IP, ethics and privacy in ICT environments</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Sign‑off Acquisition</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>INTERPERSONAL</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>APPLY</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>PRACTICAL</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Secures final approval from designated personnel by coordinating, presenting, and confirming required documentation.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>approval process, stakeholder engagement, documentation review, final sign‑off, authority confirmation</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>4.3 Obtain final sign-off from required personnel</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>1. Establish organisational IP requirements
+2. Review and determine organisational IP, ethics and privacy policies
+3. Contribute to privacy policy
+4. Maintain ethics code</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>1.1 Identify industry standard intellectual property (IP) and copyright legislation, policies and procedures
+1.2 Identify and document organisational policy and industry standard legislation against organisational work practices
+1.3 Distribute new or revised policy and procedures to stakeholders according to organisational procedures
+2.1 Review organisational privacy policy and procedures and determine compliance with industry standard requirements
+2.2 Review organisational code of ethics and determine compliance with industry standard requirements
+2.3 Review ethical work practices and feedback and determine application of code according to organisational requirements
+3.1 Update privacy policy and procedures and code of ethics to align with required privacy legislation
+3.2 Distribute revised policy, procedures and ethics to required personnel
+3.3 Implement new work procedures and ethics according to organisational requirements
+3.4 Test level of integrity, confidentiality, security and availability of information according to industry standards and organisational policies and procedures
+4.1 Establish and document review and grievance procedures and submit to required personnel
+4.2 Seek and respond to review and grievance procedure documents feedback from required personnel
+4.3 Obtain final sign-off from required personnel</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>Learning | Uses each experience to reflect on ways in which variables impact on decision outcomes and to gain insights into what constitutes decision making in different contexts
+Oral communication | Participates in verbal exchange of ideas and elicits views and opinions of others using listening and questioning techniques | Identifies requirements of important communication exchanges, selecting channels, format, tone and content to suit purpose and audience
+Reading | Analyses and evaluates complex text to determine legislative and organisational standards, and applies information to organisational policies and processes
+Writing | Integrates information and ideas from a range of sources, utilising support materials and specialised and cohesive language in a format and style applicable to audience and organisation
+Planning and organising | Sequences and schedules complex activities, monitors implementation and manages communication
+Self-management | Identifies and analyses changes to legislation and regulations applicable to own rights and responsibilities | Identifies implications of changes to legislation and regulations applicable to own rights and responsibilities when negotiating, planning and undertaking work
+Technology | Uses digital technologies and systems safely, legally and ethically when gathering, storing, accessing and sharing information, with a growing awareness of the permanence and transparency of all activities</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>This unit describes the skills and knowledge required to maintain professional and ethical conduct, as well as to ensure that personal information of stakeholders is handled in a confidential and professional manner when dealing with stakeholders in an Information and Communications Technology (ICT) environment.
+It applies to ICT personnel who are required to gather information to determine the organisation’s code of ethics and protect and maintain privacy policies and system security.
+No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr"/>
+      <c r="W163" t="inlineStr"/>
+      <c r="X163" t="inlineStr"/>
+      <c r="Y163" t="inlineStr"/>
+      <c r="Z163" t="inlineStr"/>
+      <c r="AA163" t="inlineStr"/>
+      <c r="AB163" t="inlineStr"/>
+      <c r="AC163" t="inlineStr"/>
+      <c r="AD163" t="inlineStr"/>
+      <c r="AE163" t="inlineStr"/>
+      <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="inlineStr"/>
+      <c r="AH163" t="inlineStr"/>
+      <c r="AI163" t="inlineStr"/>
+      <c r="AJ163" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>ICTICT527</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Develop and maintain blockchain solutions</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Process Suitability Assessment</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>COGNITIVE</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>APPLY</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>THEORETICAL</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>process analysis, transaction types, blockchain suitability, legislative compliance, organisational policies</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>1.2 Identify organisational processes and transactional types suitable for blockchain technology
+1.4 Determine legislation and organisational policies and procedures for blockchain and determine impact on solution</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>1. Determine blockchain solution requirements
+2. Design blockchain solution components
+3. Implement blockchain solution
+4. Maintain blockchain solution</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>1.1 Establish blockchain objectives, purpose and requirements according to organisational needs
+1.2 Identify organisational processes and transactional types suitable for blockchain technology
+1.3 Identify organisational use-case according to organisational needs
+1.4 Determine legislation and organisational policies and procedures for blockchain and determine impact on solution
+2.1 Gather data according to organisational needs
+2.2 Design integration workflow according to organisational need
+2.3 Determine security and platform for blockchain solution
+2.4 Document design plan according to organisational needs
+3.1 Set up required platform according to design plan
+3.2 Initialise blockchain solution according to vendor specifications
+3.3 Implement required consensus portal
+3.4 Execute smart command in required platform according to blockchain solution
+3.5 Debug and scale blockchain solution
+4.1 Test performance against organisational needs and requirements
+4.2 Determine and conduct maintenance tests
+4.3 Determine and document maintenance schedule
+4.4 Submit documentation to required personnel and seek and respond to feedback</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>S KILL | D ESCRIPTION
+Learning | Monitors outcomes of decisions, considering results and identifying key concepts and principles that may be adaptable in the future
+Numeracy | Uses mathematical formulae to calculate required equipment, undertake measurements and determine response times
+Oral communication | Obtains information to confirm requirements and responsibilities distinctively using appropriate industry language
+Reading | Recognises and interprets technical, manufacturer and organisational documentation to determine and confirm job requirements
+Writing | Prepares documentation outlining maintenance schedule according to specified requirements
+Planning and organising | Operates from a broad conceptual plan, developing the operational detail in stages, regularly reviewing priorities and performance during implementation, and identifying and addressing issues
+Problem solving | Uses nuanced understanding of context to recognise anomalies and subtle deviations to normal expectations, focusing attention and remedying problems as they arise
+Self-management | Takes full responsibility for identifying and considering relevant organisational protocols and requirements | Uses systematic processes, setting goals, gathering required information and identifying and evaluating options against agreed criteria
+Technology | Demonstrates a sophisticated understanding of principles, concepts, language and practices associated with the digital world</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>This unit describes the skills and knowledge required to identify, develop and maintain blockchain solutions to specified business needs.
+It applies to those in roles, including senior software developers or blockchain developers, who perform the planning, development and implementation of new and existing technologies to business models in the Information and Communications Technology (ICT) and related industries.
+No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr"/>
+      <c r="V164" t="inlineStr"/>
+      <c r="W164" t="inlineStr"/>
+      <c r="X164" t="inlineStr"/>
+      <c r="Y164" t="inlineStr"/>
+      <c r="Z164" t="inlineStr"/>
+      <c r="AA164" t="inlineStr"/>
+      <c r="AB164" t="inlineStr"/>
+      <c r="AC164" t="inlineStr"/>
+      <c r="AD164" t="inlineStr"/>
+      <c r="AE164" t="inlineStr"/>
+      <c r="AF164" t="inlineStr"/>
+      <c r="AG164" t="inlineStr"/>
+      <c r="AH164" t="inlineStr"/>
+      <c r="AI164" t="inlineStr"/>
+      <c r="AJ164" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ICTCYS407</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Gather, analyse and interpret threat data</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Data Log Strategy Discussion</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>INTERPERSONAL</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>ASSIST</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>PRACTICAL</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>1.3 Discuss and confirm data log requirements and strategy to process data with required personnel</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>1. Gather threat data
+2. Analyse threat data
+3. Interpret and finalise threat data</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>1.1 Identify legislative requirements and organisational policies and procedures to gather, analyse and interpret threat data
+1.2 Identify security equipment on network and data sources
+1.3 Discuss and confirm data log requirements and strategy to process data with required personnel
+1.4 Collect information from alerts, logs and reported events and create a dataset according to organisational policies and procedures
+2.1 Ingest data logs into analytic platform according to user instructions
+2.2 Obtain and analyse results for reliability and consistency
+2.3 Check for false positives and false negative results
+2.4 Detect and describe discrepancies and inconsistencies in data
+3.1 Discuss and review threat data and results with required personnel
+3.2 Discuss and assess identified threats, risks and their likelihood of occurrence and impacts of risks,
+3.3 Suggest and confirm lessons learnt, action steps, recommendations and mitigation strategies with required personnel
+3.4 Document results, findings and recommendations into report according to organisational procedures
+3.5 Distribute documentation to required personnel and store according to organisational policies and procedures</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>Learning | Identifies and gathers information applicable to organisational procedures and threat data
+Numeracy | Uses tools when measuring and recording data, and interprets results through mathematical data
+Reading | Interprets information from different sources in a range of formats when identifying threat data
+Writing | Prepares complex workplace documentation detailing research findings and recommendations using required structure, layout and technical language
+Planning and organising | Uses problem solving skills when interpreting the nature and impact of threat data
+Technology | Uses required technological tools and software in gathering, analysing and interpreting threat data</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>This unit describes the skills and knowledge required to gather data from various sources, analyse, and interpret information for threats, inconsistencies and discrepancies.
+It applies to individuals who work in information technology security, including network and security specialists, and gather logs from devices, check abnormalities and respond accordingly. These individuals are responsible for supporting and preventing cyber threats attacking data in all business functions and in any industry context.
+No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
+      <c r="W165" t="inlineStr"/>
+      <c r="X165" t="inlineStr"/>
+      <c r="Y165" t="inlineStr"/>
+      <c r="Z165" t="inlineStr"/>
+      <c r="AA165" t="inlineStr"/>
+      <c r="AB165" t="inlineStr"/>
+      <c r="AC165" t="inlineStr"/>
+      <c r="AD165" t="inlineStr"/>
+      <c r="AE165" t="inlineStr"/>
+      <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="inlineStr"/>
+      <c r="AH165" t="inlineStr"/>
+      <c r="AI165" t="inlineStr"/>
+      <c r="AJ165" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ICTCYS407</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Gather, analyse and interpret threat data</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Reliability Consistency Analysis</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>APPLY</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>PRACTICAL</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>reliability assessment, consistency verification, data validation, threat analysis, result evaluation</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>2.2 Obtain and analyse results for reliability and consistency</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>1. Gather threat data
+2. Analyse threat data
+3. Interpret and finalise threat data</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>1.1 Identify legislative requirements and organisational policies and procedures to gather, analyse and interpret threat data
+1.2 Identify security equipment on network and data sources
+1.3 Discuss and confirm data log requirements and strategy to process data with required personnel
+1.4 Collect information from alerts, logs and reported events and create a dataset according to organisational policies and procedures
+2.1 Ingest data logs into analytic platform according to user instructions
+2.2 Obtain and analyse results for reliability and consistency
+2.3 Check for false positives and false negative results
+2.4 Detect and describe discrepancies and inconsistencies in data
+3.1 Discuss and review threat data and results with required personnel
+3.2 Discuss and assess identified threats, risks and their likelihood of occurrence and impacts of risks,
+3.3 Suggest and confirm lessons learnt, action steps, recommendations and mitigation strategies with required personnel
+3.4 Document results, findings and recommendations into report according to organisational procedures
+3.5 Distribute documentation to required personnel and store according to organisational policies and procedures</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>Learning | Identifies and gathers information applicable to organisational procedures and threat data
+Numeracy | Uses tools when measuring and recording data, and interprets results through mathematical data
+Reading | Interprets information from different sources in a range of formats when identifying threat data
+Writing | Prepares complex workplace documentation detailing research findings and recommendations using required structure, layout and technical language
+Planning and organising | Uses problem solving skills when interpreting the nature and impact of threat data
+Technology | Uses required technological tools and software in gathering, analysing and interpreting threat data</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>This unit describes the skills and knowledge required to gather data from various sources, analyse, and interpret information for threats, inconsistencies and discrepancies.
+It applies to individuals who work in information technology security, including network and security specialists, and gather logs from devices, check abnormalities and respond accordingly. These individuals are responsible for supporting and preventing cyber threats attacking data in all business functions and in any industry context.
+No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr"/>
+      <c r="V166" t="inlineStr"/>
+      <c r="W166" t="inlineStr"/>
+      <c r="X166" t="inlineStr"/>
+      <c r="Y166" t="inlineStr"/>
+      <c r="Z166" t="inlineStr"/>
+      <c r="AA166" t="inlineStr"/>
+      <c r="AB166" t="inlineStr"/>
+      <c r="AC166" t="inlineStr"/>
+      <c r="AD166" t="inlineStr"/>
+      <c r="AE166" t="inlineStr"/>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="inlineStr"/>
+      <c r="AH166" t="inlineStr"/>
+      <c r="AI166" t="inlineStr"/>
+      <c r="AJ166" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>ICTCYS610</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Protect critical infrastructure for organisations</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Plan Alignment Evaluation</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>COGNITIVE</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>APPLY</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>THEORETICAL</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Evaluates how well the current protection plan meets organisational needs and regulatory requirements.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>plan effectiveness, organisational alignment, regulatory compliance, critical assets, operational systems</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>1.3 Determine effectiveness and alignment of existing plan to organisational requirements
+1.4 Identify operational systems, critical assets, segmentation and legislative requirements</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>1. Research critical infrastructure need for an organisation
+2. Develop protection strategy
+3. Implement protection strategy
+4. Test implementation outcomes</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>1.1 Research organisation’s need for critical infrastructure protection and document findings according to organisational requirements
+1.2 Analyse organisation’s existing critical infrastructure protection plan
+1.3 Determine effectiveness and alignment of existing plan to organisational requirements
+1.4 Identify operational systems, critical assets, segmentation and legislative requirements
+1.5 Determine level of protection, vulnerability, risk and mitigation according to organisational requirements
+2.1 Consolidate research findings and map critical processes according to organisational requirements
+2.2 Develop and document critical infrastructure protection plan according to organisational policies and procedures
+2.3 Submit protection plan to required personnel and seek and respond to feedback
+3.1 Backup data according to organisational policies and procedures
+3.2 Secure devices according to protection plan and technical requirements
+3.3 Implement network segmentation according to protection plan and technical requirements
+3.4 Apply software patches according to technical requirements
+3.5 Implement additional protection plan requirements and asset management processes
+4.1 Test deployment of protection plan according to organisational policies and procedures
+4.2 Obtain and analyse results according to organisational policies and procedures
+4.3 Determine and document additional protection methods for critical infrastructure protection
+4.4 Submit documentation to required personnel and seek and respond to feedback</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>S KILL | DESCRIPTION
+Reading | Identifies technical, manufacturer and organisational from documentation to determine and confirm job requirements
+Writing | Prepares complex workplace documentation detailing processes and outcomes using required structure, layout and required language
+Planning and organising | Develops the operational detail in stages, regularly reviewing priorities and performance during strategy development and implementation, and identifies and addresses issues challenges as they arise
+Problem solving | Identifies context to recognise anomalies and subtle deviations to normal expectations, focusing attention and remedying problems as they arise
+Self-management | Takes full responsibility for identifying and considering organisational protocols and requirements
+Technology | Identifies principles, concepts, language and practices associated with the digital and cyber world</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>This unit describes the skills and knowledge required to analyse an organisation’s critical cyber operations and develop and implement a critical protections strategy that addresses the needs of the organisation.
+It applies to those who work as senior network and server administrators, cyber security analysts, security engineers, network engineers other cyber security related roles and are responsible for cyber security activities, including researching, developing and implementing protection strategies.
+No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr"/>
+      <c r="V167" t="inlineStr"/>
+      <c r="W167" t="inlineStr"/>
+      <c r="X167" t="inlineStr"/>
+      <c r="Y167" t="inlineStr"/>
+      <c r="Z167" t="inlineStr"/>
+      <c r="AA167" t="inlineStr"/>
+      <c r="AB167" t="inlineStr"/>
+      <c r="AC167" t="inlineStr"/>
+      <c r="AD167" t="inlineStr"/>
+      <c r="AE167" t="inlineStr"/>
+      <c r="AF167" t="inlineStr"/>
+      <c r="AG167" t="inlineStr"/>
+      <c r="AH167" t="inlineStr"/>
+      <c r="AI167" t="inlineStr"/>
+      <c r="AJ167" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>ICTSAS524</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Develop, implement and evaluate an incident response plan</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Plan Alignment Documentation</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>APPLY</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>PRACTICAL</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>The worker determines how the current incident response plan meets required standards and records the findings for review.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>incident response plan, alignment assessment, documentation, requirements, feedback</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>1.4 Determine and document alignment of organisation’s existing incident response plan against identified requirements
+1.5 Submit documentation to required personnel, seek and respond to feedback</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>1. Prepare to develop an incident response plan
+2. Develop the incident response plan
+3. Implement the incident response plan
+4. Evaluate incident response plans</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>1.1 Identify and document organisational incident response plan requirements
+1.2 Identify and document incident response team services according to organisational requirements
+1.3 Identify incident response plan structure according to organisational requirements
+1.4 Determine and document alignment of organisation’s existing incident response plan against identified requirements
+1.5 Submit documentation to required personnel, seek and respond to feedback
+2.1 Develop and document incident management policy according to task requirements
+2.2 Create incident response plans according to organisational requirements and security policies and procedures
+2.3 Develop incident handling and reporting procedures
+2.4 Create incident response exercises, red-teaming activities, staffing and training requirements
+2.5 Develop procedure for collecting and protecting forensic evidence during incident response procedures according to organisational requirements
+2.6 Establish and document incident the response plan
+3.1 Apply response actions to reported security incident according to incident response plan and task requirements
+3.2 Assist in collecting, processing and preserving evidence according to requirements
+3.3 Execute incident response plans, red-teaming activities and incident response exercises
+3.4 Document security incident response and actions according to task requirements
+3.5 Collect, analyse and report incident management measures according to task requirements
+4.1 Assess and document efficiency and effectiveness of incident response plans activities
+4.2 Examine and document effectiveness of red teaming and incident response tests, training and exercises
+4.3 Assess effectiveness of communication between incident response team and required internal and external organisations
+4.4 Determine and document response improvement activities
+4.5 Submit documentation to required personnel and obtain final task sign off</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>S KILL | DESCRIPTION
+Learning | Monitors outcomes of decisions, considering results and identifying key concepts and principles that may be adaptable in the future
+Numeracy | Interprets, analyses and documents numerical and technical system data | Uses mathematical equations to calculate data for technical reports
+Oral communication | Uses listening and questioning techniques to confirm task requirements and relevant information using succinct language
+Reading | Analyses textual information and data to determine necessary actions
+Writing | Prepares required workplace documentation detailing processes and outcomes using cohesive language
+Teamwork | Uses a variety of relevant communication tools and strategies in building and maintaining effective working relationships | Influences and fosters a collaborative culture facilitating a sense of commitment and workplace cohesion | Understands diversity and seeks to integrate diversity into the work context for managing change, making decisions and achieving shared outcomes
+Planning and organising | Monitors and reviews the organisations policies, procedures and adherence to legislative requirements in order to implement and manage change
+Self-management | Works autonomously, making high-level decisions to achieve and improve organisational goals
+Problem solving | Develops and implements strategies that ensure organisational policies, procedures and regulatory requirements are met | Operates from a broad conceptual plan, developing the operational detail in stages, regularly reviewing priorities and performance during implementation, and identifying and addressing issues</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>This unit describes the skills and knowledge required to develop and implement an incident response plan. The results of the incident response plan must be evaluated if they affect the mission of the organisation.
+It applies to individuals who apply high-level technical skills and specialised knowledge to provide broad systems administration and support functions.
+No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr"/>
+      <c r="W168" t="inlineStr"/>
+      <c r="X168" t="inlineStr"/>
+      <c r="Y168" t="inlineStr"/>
+      <c r="Z168" t="inlineStr"/>
+      <c r="AA168" t="inlineStr"/>
+      <c r="AB168" t="inlineStr"/>
+      <c r="AC168" t="inlineStr"/>
+      <c r="AD168" t="inlineStr"/>
+      <c r="AE168" t="inlineStr"/>
+      <c r="AF168" t="inlineStr"/>
+      <c r="AG168" t="inlineStr"/>
+      <c r="AH168" t="inlineStr"/>
+      <c r="AI168" t="inlineStr"/>
+      <c r="AJ168" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>ICTSAS524</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Develop, implement and evaluate an incident response plan</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Evidence Preservation Assistance</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>ASSIST</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>PRACTICAL</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Assist in gathering, processing, and preserving incident evidence in line with organisational requirements and standards.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, organisational requirements</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>3.2 Assist in collecting, processing and preserving evidence according to requirements</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>1. Prepare to develop an incident response plan
+2. Develop the incident response plan
+3. Implement the incident response plan
+4. Evaluate incident response plans</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>1.1 Identify and document organisational incident response plan requirements
+1.2 Identify and document incident response team services according to organisational requirements
+1.3 Identify incident response plan structure according to organisational requirements
+1.4 Determine and document alignment of organisation’s existing incident response plan against identified requirements
+1.5 Submit documentation to required personnel, seek and respond to feedback
+2.1 Develop and document incident management policy according to task requirements
+2.2 Create incident response plans according to organisational requirements and security policies and procedures
+2.3 Develop incident handling and reporting procedures
+2.4 Create incident response exercises, red-teaming activities, staffing and training requirements
+2.5 Develop procedure for collecting and protecting forensic evidence during incident response procedures according to organisational requirements
+2.6 Establish and document incident the response plan
+3.1 Apply response actions to reported security incident according to incident response plan and task requirements
+3.2 Assist in collecting, processing and preserving evidence according to requirements
+3.3 Execute incident response plans, red-teaming activities and incident response exercises
+3.4 Document security incident response and actions according to task requirements
+3.5 Collect, analyse and report incident management measures according to task requirements
+4.1 Assess and document efficiency and effectiveness of incident response plans activities
+4.2 Examine and document effectiveness of red teaming and incident response tests, training and exercises
+4.3 Assess effectiveness of communication between incident response team and required internal and external organisations
+4.4 Determine and document response improvement activities
+4.5 Submit documentation to required personnel and obtain final task sign off</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>S KILL | DESCRIPTION
+Learning | Monitors outcomes of decisions, considering results and identifying key concepts and principles that may be adaptable in the future
+Numeracy | Interprets, analyses and documents numerical and technical system data | Uses mathematical equations to calculate data for technical reports
+Oral communication | Uses listening and questioning techniques to confirm task requirements and relevant information using succinct language
+Reading | Analyses textual information and data to determine necessary actions
+Writing | Prepares required workplace documentation detailing processes and outcomes using cohesive language
+Teamwork | Uses a variety of relevant communication tools and strategies in building and maintaining effective working relationships | Influences and fosters a collaborative culture facilitating a sense of commitment and workplace cohesion | Understands diversity and seeks to integrate diversity into the work context for managing change, making decisions and achieving shared outcomes
+Planning and organising | Monitors and reviews the organisations policies, procedures and adherence to legislative requirements in order to implement and manage change
+Self-management | Works autonomously, making high-level decisions to achieve and improve organisational goals
+Problem solving | Develops and implements strategies that ensure organisational policies, procedures and regulatory requirements are met | Operates from a broad conceptual plan, developing the operational detail in stages, regularly reviewing priorities and performance during implementation, and identifying and addressing issues</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>This unit describes the skills and knowledge required to develop and implement an incident response plan. The results of the incident response plan must be evaluated if they affect the mission of the organisation.
+It applies to individuals who apply high-level technical skills and specialised knowledge to provide broad systems administration and support functions.
+No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr"/>
+      <c r="W169" t="inlineStr"/>
+      <c r="X169" t="inlineStr"/>
+      <c r="Y169" t="inlineStr"/>
+      <c r="Z169" t="inlineStr"/>
+      <c r="AA169" t="inlineStr"/>
+      <c r="AB169" t="inlineStr"/>
+      <c r="AC169" t="inlineStr"/>
+      <c r="AD169" t="inlineStr"/>
+      <c r="AE169" t="inlineStr"/>
+      <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="inlineStr"/>
+      <c r="AH169" t="inlineStr"/>
+      <c r="AI169" t="inlineStr"/>
+      <c r="AJ169" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ICTSAS526</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Review and update disaster recovery and contingency plans</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Critical Function Identification</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>DOMAIN_KNOWLEDGE</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>APPLY</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>THEORETICAL</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Identify essential business functions, critical data, and software, and assess risk impacts on ICT systems.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>business critical functions, security environment, critical data, software assets, risk impact assessment</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>1.1 Identify required business critical functions and security environment
+1.2 Identify required critical data and software
+1.3 Assess potential impact of business risk and threats on ICT systems</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>1. Evaluate system impact on business continuity
+2. Evaluate system threats
+3. Formulate prevention and recovery strategy
+4. Develop disaster recovery plan</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>1.1 Identify required business critical functions and security environment
+1.2 Identify required critical data and software
+1.3 Assess potential impact of business risk and threats on ICT systems
+1.4 Identify statutory requirements, commercial requirements and contingency requirements according to organisational requirements
+2.1 Identify and document internal and external business environment system threats
+2.2 Evaluate and document risk minimisation alternatives against organisational cost constraints and organisational requirements
+2.3 Submit document to required personnel, seek and respond to feedback
+3.1 Evaluate and document prevention and recovery options against business specifications and cost constraints
+3.2 Review industry standard operational procedures and check required risk safeguards and contingency plans are in place
+3.3 Submit disaster recovery and prevention strategy to required personnel and seek and respond to feedback
+4.1 Identify and document disaster recovery resources according to cost constraints and organisational requirements
+4.2 Identify and document disaster strategy processes
+4.3 Identify required cut-over criteria plan
+4.4 Document disaster recovery plan and submit to required personnel and seek and respond to feedback
+4.5 Obtain final task sign off</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>S KILL | DESCRIPTION
+Numeracy | Analyses, interprets and documents numerical, financial and technical system data
+Oral communication | Uses listening and questioning techniques to confirm information using relevant industry language for intended audience
+Reading | Researches and analyses textual information and technical data/specifications from a range of documentation and sources to inform the development of contingency plans
+Writing | Prepares required documentation detailing evaluation and strategy using required language and formats appropriate to the task
+Teamwork | Uses relevant communication tools and strategies in building and maintaining effective working relationships | Influences and fosters a collaborative culture that facilitates a sense of commitment and workplace cohesion
+Planning and organising | Demonstrates strategic planning of priorities and outcomes within a flexible, efficient and effective context in a diverse environment exposed to competing demands
+Problem solving | Gathers and analyses data and seeks feedback to improve plans and processes
+Self-management | Develops and implements strategies to ensure organisational policies, procedures and regulatory requirements are met | Monitors and reviews the organisations policies, procedures and adherence to legislative requirements to implement and manage change</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>This unit describes the skills and knowledge required to analyse the impact of the system on the organisation and carry out risk analysis, disaster recovery and contingency planning.
+It applies to individuals who apply a wide range of higher-level technical skills and systematic problem-solving approaches in Information and Communications Technology (ICT) related areas.
+No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr"/>
+      <c r="V170" t="inlineStr"/>
+      <c r="W170" t="inlineStr"/>
+      <c r="X170" t="inlineStr"/>
+      <c r="Y170" t="inlineStr"/>
+      <c r="Z170" t="inlineStr"/>
+      <c r="AA170" t="inlineStr"/>
+      <c r="AB170" t="inlineStr"/>
+      <c r="AC170" t="inlineStr"/>
+      <c r="AD170" t="inlineStr"/>
+      <c r="AE170" t="inlineStr"/>
+      <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="inlineStr"/>
+      <c r="AH170" t="inlineStr"/>
+      <c r="AI170" t="inlineStr"/>
+      <c r="AJ170" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>ICTSAS526</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Review and update disaster recovery and contingency plans</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Disaster Strategy Documentation</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>APPLY</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>PRACTICAL</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Creates and records detailed disaster strategy processes, cut‑over criteria, and secures final task sign‑off.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, implementation</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>4.2 Identify and document disaster strategy processes
+4.3 Identify required cut-over criteria plan
+4.5 Obtain final task sign off</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>1. Evaluate system impact on business continuity
+2. Evaluate system threats
+3. Formulate prevention and recovery strategy
+4. Develop disaster recovery plan</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>1.1 Identify required business critical functions and security environment
+1.2 Identify required critical data and software
+1.3 Assess potential impact of business risk and threats on ICT systems
+1.4 Identify statutory requirements, commercial requirements and contingency requirements according to organisational requirements
+2.1 Identify and document internal and external business environment system threats
+2.2 Evaluate and document risk minimisation alternatives against organisational cost constraints and organisational requirements
+2.3 Submit document to required personnel, seek and respond to feedback
+3.1 Evaluate and document prevention and recovery options against business specifications and cost constraints
+3.2 Review industry standard operational procedures and check required risk safeguards and contingency plans are in place
+3.3 Submit disaster recovery and prevention strategy to required personnel and seek and respond to feedback
+4.1 Identify and document disaster recovery resources according to cost constraints and organisational requirements
+4.2 Identify and document disaster strategy processes
+4.3 Identify required cut-over criteria plan
+4.4 Document disaster recovery plan and submit to required personnel and seek and respond to feedback
+4.5 Obtain final task sign off</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>S KILL | DESCRIPTION
+Numeracy | Analyses, interprets and documents numerical, financial and technical system data
+Oral communication | Uses listening and questioning techniques to confirm information using relevant industry language for intended audience
+Reading | Researches and analyses textual information and technical data/specifications from a range of documentation and sources to inform the development of contingency plans
+Writing | Prepares required documentation detailing evaluation and strategy using required language and formats appropriate to the task
+Teamwork | Uses relevant communication tools and strategies in building and maintaining effective working relationships | Influences and fosters a collaborative culture that facilitates a sense of commitment and workplace cohesion
+Planning and organising | Demonstrates strategic planning of priorities and outcomes within a flexible, efficient and effective context in a diverse environment exposed to competing demands
+Problem solving | Gathers and analyses data and seeks feedback to improve plans and processes
+Self-management | Develops and implements strategies to ensure organisational policies, procedures and regulatory requirements are met | Monitors and reviews the organisations policies, procedures and adherence to legislative requirements to implement and manage change</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>This unit describes the skills and knowledge required to analyse the impact of the system on the organisation and carry out risk analysis, disaster recovery and contingency planning.
+It applies to individuals who apply a wide range of higher-level technical skills and systematic problem-solving approaches in Information and Communications Technology (ICT) related areas.
+No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr"/>
+      <c r="V171" t="inlineStr"/>
+      <c r="W171" t="inlineStr"/>
+      <c r="X171" t="inlineStr"/>
+      <c r="Y171" t="inlineStr"/>
+      <c r="Z171" t="inlineStr"/>
+      <c r="AA171" t="inlineStr"/>
+      <c r="AB171" t="inlineStr"/>
+      <c r="AC171" t="inlineStr"/>
+      <c r="AD171" t="inlineStr"/>
+      <c r="AE171" t="inlineStr"/>
+      <c r="AF171" t="inlineStr"/>
+      <c r="AG171" t="inlineStr"/>
+      <c r="AH171" t="inlineStr"/>
+      <c r="AI171" t="inlineStr"/>
+      <c r="AJ171" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_pcs_fs_app_refined.xlsx
@@ -588,27 +588,27 @@
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
+          <t>added_from_pc</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>org_description</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>description_changed</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>org_keywords</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>keywords_changed</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>added_from_pc</t>
         </is>
       </c>
     </row>
@@ -763,21 +763,21 @@
         <v>0</v>
       </c>
       <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr">
+      <c r="AF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Elicits others’ views and integrates feedback to refine ideas during collaborative discussions.</t>
         </is>
       </c>
-      <c r="AG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>communication, empathy, feedback, stakeholder engagement, interpersonal skills</t>
         </is>
-      </c>
-      <c r="AI2" t="b">
-        <v>0</v>
       </c>
       <c r="AJ2" t="b">
         <v>0</v>
@@ -930,21 +930,21 @@
         <v>0</v>
       </c>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr">
+      <c r="AF3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Compares project concepts against industry best‑practice examples of similar products to identify improvement opportunities.</t>
         </is>
       </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AH3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>benchmarking, best practice, performance metrics, competitive analysis, industry standards</t>
         </is>
-      </c>
-      <c r="AI3" t="b">
-        <v>0</v>
       </c>
       <c r="AJ3" t="b">
         <v>0</v>
@@ -1101,21 +1101,21 @@
         <v>0</v>
       </c>
       <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr">
+      <c r="AF4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>Generates diverse solutions by leading focused brainstorming sessions to address identified issues.</t>
         </is>
       </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AH4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>ideation, creative problem solving, mind mapping, group facilitation, innovation techniques</t>
         </is>
-      </c>
-      <c r="AI4" t="b">
-        <v>0</v>
       </c>
       <c r="AJ4" t="b">
         <v>0</v>
@@ -1257,13 +1257,9 @@
         </is>
       </c>
       <c r="Z5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Planning and organising</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="b">
         <v>0</v>
       </c>
@@ -1272,21 +1268,21 @@
         <v>0</v>
       </c>
       <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr">
+      <c r="AF5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>Applies systematic analytical methods to collect and assess concepts in complex, non‑routine scenarios.</t>
         </is>
       </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AH5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>analytical methodology, systematic concept evaluation, ideation processes, feasibility analysis, design thinking</t>
         </is>
-      </c>
-      <c r="AI5" t="b">
-        <v>0</v>
       </c>
       <c r="AJ5" t="b">
         <v>0</v>
@@ -1416,13 +1412,9 @@
         </is>
       </c>
       <c r="Z6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Idea Generation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="b">
         <v>0</v>
       </c>
@@ -1431,21 +1423,21 @@
         <v>0</v>
       </c>
       <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr">
+      <c r="AF6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>Applies creative thinking techniques to develop innovative solutions to workplace challenges.</t>
         </is>
       </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AH6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>ideation, innovation, brainstorming, design thinking, problem solving</t>
         </is>
-      </c>
-      <c r="AI6" t="b">
-        <v>0</v>
       </c>
       <c r="AJ6" t="b">
         <v>0</v>
@@ -1566,7 +1558,7 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
@@ -1575,13 +1567,9 @@
         </is>
       </c>
       <c r="Z7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Stakeholder Feedback Solicitation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="b">
         <v>0</v>
       </c>
@@ -1590,21 +1578,21 @@
         <v>0</v>
       </c>
       <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr">
+      <c r="AF7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>Records and formats feedback in line with organisational standards to ensure consistent documentation.</t>
         </is>
       </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AH7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>record‑keeping, compliance, audit trail, quality assurance, organisational standards</t>
         </is>
-      </c>
-      <c r="AI7" t="b">
-        <v>0</v>
       </c>
       <c r="AJ7" t="b">
         <v>0</v>
@@ -1729,16 +1717,16 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9028571428571429</v>
+        <v>0.9</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>keep:0, "Idea Viability Evaluation":7</t>
+          <t>keep:0, "Idea Viability Evaluation":5, "Idea Viability Assessment":2</t>
         </is>
       </c>
       <c r="Z8" t="b">
@@ -1757,21 +1745,21 @@
         <v>0</v>
       </c>
       <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr">
+      <c r="AF8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>Assesses ideas by systematically comparing them against identified viability factors.</t>
         </is>
       </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AH8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>feasibility analysis, risk assessment, criteria weighting, business case evaluation, market viability</t>
         </is>
-      </c>
-      <c r="AI8" t="b">
-        <v>0</v>
       </c>
       <c r="AJ8" t="b">
         <v>0</v>
@@ -1924,21 +1912,21 @@
         <v>0</v>
       </c>
       <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr">
+      <c r="AF9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>Collaborates with relevant personnel to identify and select consultation issues for focused analysis.</t>
         </is>
       </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AH9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
         <is>
           <t>stakeholder engagement, problem identification, needs assessment, consultation processes, decision‑making</t>
         </is>
-      </c>
-      <c r="AI9" t="b">
-        <v>0</v>
       </c>
       <c r="AJ9" t="b">
         <v>0</v>
@@ -2083,21 +2071,21 @@
         <v>0</v>
       </c>
       <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr">
+      <c r="AF10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>Drafts detailed proposals and plans using sector‑specific terminology for stakeholder review.</t>
         </is>
       </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AH10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>stakeholder communication, business case development, grant and RFP responses, technical documentation, persuasive writing</t>
         </is>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
       </c>
       <c r="AJ10" t="b">
         <v>0</v>
@@ -2231,13 +2219,9 @@
         </is>
       </c>
       <c r="Z11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Idea Viability Evaluation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="b">
         <v>0</v>
       </c>
@@ -2246,21 +2230,21 @@
         <v>0</v>
       </c>
       <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr">
+      <c r="AF11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="inlineStr">
         <is>
           <t>Gathers and evaluates relevant data to identify viable solutions to the identified issue.</t>
         </is>
       </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AH11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
         <is>
           <t>literature review, data collection, search strategies, online databases, evidence‑based analysis</t>
         </is>
-      </c>
-      <c r="AI11" t="b">
-        <v>0</v>
       </c>
       <c r="AJ11" t="b">
         <v>0</v>
@@ -2409,21 +2393,21 @@
         <v>0</v>
       </c>
       <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr">
+      <c r="AF12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="inlineStr">
         <is>
           <t>Selects appropriate solution formats and delivers tailored presentations to stakeholders.</t>
         </is>
       </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AH12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
         <is>
           <t>stakeholder communication, visual presentation tools, solution pitching, format selection, business briefings</t>
         </is>
-      </c>
-      <c r="AI12" t="b">
-        <v>0</v>
       </c>
       <c r="AJ12" t="b">
         <v>0</v>
@@ -2576,21 +2560,21 @@
         <v>0</v>
       </c>
       <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr">
+      <c r="AF13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="inlineStr">
         <is>
           <t>Iteratively refines and finalises solutions to meet specific task requirements.</t>
         </is>
       </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AH13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
         <is>
           <t>requirements analysis, design optimisation, prototype testing, continuous improvement, validation feedback</t>
         </is>
-      </c>
-      <c r="AI13" t="b">
-        <v>0</v>
       </c>
       <c r="AJ13" t="b">
         <v>0</v>
@@ -2720,13 +2704,9 @@
         </is>
       </c>
       <c r="Z14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Idea Viability Evaluation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="b">
         <v>0</v>
       </c>
@@ -2735,21 +2715,21 @@
         <v>0</v>
       </c>
       <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr">
+      <c r="AF14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="inlineStr">
         <is>
           <t>Evaluates alternative solutions to a business problem, identifying constraints to determine feasible options.</t>
         </is>
       </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AH14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
         <is>
           <t>feasibility analysis, constraint identification, business issue evaluation, risk assessment, decision matrices</t>
         </is>
-      </c>
-      <c r="AI14" t="b">
-        <v>0</v>
       </c>
       <c r="AJ14" t="b">
         <v>0</v>
@@ -2887,13 +2867,9 @@
         </is>
       </c>
       <c r="Z15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Stakeholder Viewpoint Elicitation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="b">
         <v>0</v>
       </c>
@@ -2902,21 +2878,21 @@
         <v>0</v>
       </c>
       <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr">
+      <c r="AF15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="inlineStr">
         <is>
           <t>Proactively seeks stakeholder input on ideas to refine concepts and align expectations.</t>
         </is>
       </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
+      <c r="AH15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
         <is>
           <t>stakeholder engagement, feedback collection, surveys, interviews, communication</t>
         </is>
-      </c>
-      <c r="AI15" t="b">
-        <v>0</v>
       </c>
       <c r="AJ15" t="b">
         <v>0</v>
@@ -3045,16 +3021,16 @@
         <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 5/7: </t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>keep:0, "Discussion Facilitation":7</t>
+          <t>keep:2, "Discussion Facilitation":5</t>
         </is>
       </c>
       <c r="Z16" t="b">
@@ -3073,21 +3049,21 @@
         <v>0</v>
       </c>
       <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr">
+      <c r="AF16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="inlineStr">
         <is>
           <t>Guides group discussions, encourages participation and coordinates tasks to achieve shared outcomes.</t>
         </is>
       </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AH16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
         <is>
           <t>group dynamics, collaboration tools, meeting facilitation, conflict resolution, consensus building</t>
         </is>
-      </c>
-      <c r="AI16" t="b">
-        <v>0</v>
       </c>
       <c r="AJ16" t="b">
         <v>0</v>
@@ -3237,21 +3213,21 @@
         <v>0</v>
       </c>
       <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr">
+      <c r="AF17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="inlineStr">
         <is>
           <t>Designs, implements and updates organisation‑wide cyber security awareness programs in line with best practice.</t>
         </is>
       </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AH17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
         <is>
           <t>cyber security, security awareness training, risk management, phishing simulations, compliance governance</t>
         </is>
-      </c>
-      <c r="AI17" t="b">
-        <v>0</v>
       </c>
       <c r="AJ17" t="b">
         <v>0</v>
@@ -3389,21 +3365,21 @@
         <v>0</v>
       </c>
       <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr">
+      <c r="AF18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="inlineStr">
         <is>
           <t>Writes workplace documents using precise cyber security terminology to clearly convey technical information.</t>
         </is>
       </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AH18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
         <is>
           <t>cyber security terminology, technical documentation, information security policies, industry standards (ISO 27001, NIST), risk assessment reporting</t>
         </is>
-      </c>
-      <c r="AI18" t="b">
-        <v>0</v>
       </c>
       <c r="AJ18" t="b">
         <v>0</v>
@@ -3549,21 +3525,21 @@
         <v>0</v>
       </c>
       <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr">
+      <c r="AF19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="inlineStr">
         <is>
           <t>Assesses cyber security awareness within the work area through surveys and interviews to establish baseline levels.</t>
         </is>
       </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
+      <c r="AH19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
         <is>
           <t>cyber security, risk awareness, security posture, threat intelligence, security metrics</t>
         </is>
-      </c>
-      <c r="AI19" t="b">
-        <v>0</v>
       </c>
       <c r="AJ19" t="b">
         <v>0</v>
@@ -3701,21 +3677,21 @@
         <v>0</v>
       </c>
       <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr">
+      <c r="AF20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="inlineStr">
         <is>
           <t>Communicates review results and cyber security improvement needs in accordance with organisational policies and procedures.</t>
         </is>
       </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AH20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
         <is>
           <t>cyber security, policy compliance, risk communication, security standards, stakeholder reporting</t>
         </is>
-      </c>
-      <c r="AI20" t="b">
-        <v>0</v>
       </c>
       <c r="AJ20" t="b">
         <v>0</v>
@@ -3846,7 +3822,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>keep:4, "Insight Presentation":3</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z21" t="b">
@@ -3861,21 +3837,21 @@
         <v>0</v>
       </c>
       <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr">
+      <c r="AF21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="inlineStr">
         <is>
           <t>Delivers concise insight presentations derived from reviews and training to designated personnel.</t>
         </is>
       </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
+      <c r="AH21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
         <is>
           <t>stakeholder communication, knowledge transfer, visual storytelling, training briefings, presentation tools</t>
         </is>
-      </c>
-      <c r="AI21" t="b">
-        <v>0</v>
       </c>
       <c r="AJ21" t="b">
         <v>0</v>
@@ -4017,21 +3993,21 @@
         <v>0</v>
       </c>
       <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr">
+      <c r="AF22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="inlineStr">
         <is>
           <t>Interprets Notifiable Data Breach and related privacy legislation to assess impacts on organisational data protection.</t>
         </is>
       </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
+      <c r="AH22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
         <is>
           <t>Notifiable Data Breach, Australian Privacy Act, data protection compliance, privacy law interpretation, regulatory risk assessment</t>
         </is>
-      </c>
-      <c r="AI22" t="b">
-        <v>0</v>
       </c>
       <c r="AJ22" t="b">
         <v>0</v>
@@ -4177,21 +4153,21 @@
         <v>0</v>
       </c>
       <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr">
+      <c r="AF23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="inlineStr">
         <is>
           <t>Prepares detailed review outcome reports outlining improvement recommendations for relevant personnel.</t>
         </is>
       </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
+      <c r="AH23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
         <is>
           <t>reporting, review outcomes, improvement recommendations, stakeholder communication, record‑keeping</t>
         </is>
-      </c>
-      <c r="AI23" t="b">
-        <v>0</v>
       </c>
       <c r="AJ23" t="b">
         <v>0</v>
@@ -4341,21 +4317,21 @@
         <v>0</v>
       </c>
       <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr">
+      <c r="AF24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="inlineStr">
         <is>
           <t>Drafts cyber security policies and procedures and disseminates them to relevant staff.</t>
         </is>
       </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
+      <c r="AH24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
         <is>
           <t>cyber security governance, policy development, risk management, compliance frameworks, stakeholder communication</t>
         </is>
-      </c>
-      <c r="AI24" t="b">
-        <v>0</v>
       </c>
       <c r="AJ24" t="b">
         <v>0</v>
@@ -4505,21 +4481,21 @@
         <v>0</v>
       </c>
       <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr">
+      <c r="AF25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="inlineStr">
         <is>
           <t>Conducts systematic reviews of cyber security practices to ensure alignment with organisational policies and procedures.</t>
         </is>
       </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
+      <c r="AH25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
         <is>
           <t>cyber security, policy compliance, risk assessment, security governance, audit controls</t>
         </is>
-      </c>
-      <c r="AI25" t="b">
-        <v>0</v>
       </c>
       <c r="AJ25" t="b">
         <v>0</v>
@@ -4665,21 +4641,21 @@
         <v>0</v>
       </c>
       <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr">
+      <c r="AF26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="inlineStr">
         <is>
           <t>Maintains up‑to‑date cyber security protection records by organising and documenting relevant data.</t>
         </is>
       </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
+      <c r="AH26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
         <is>
           <t>cyber security documentation, information security records, compliance logging, data governance, audit trail management</t>
         </is>
-      </c>
-      <c r="AI26" t="b">
-        <v>0</v>
       </c>
       <c r="AJ26" t="b">
         <v>0</v>
@@ -4817,21 +4793,21 @@
         <v>0</v>
       </c>
       <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr">
+      <c r="AF27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="inlineStr">
         <is>
           <t>Engages relevant stakeholders through meetings and surveys to gather input that informs decision‑making.</t>
         </is>
       </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
+      <c r="AH27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
         <is>
           <t>stakeholder engagement, consultation workshops, decision support, needs analysis, facilitation</t>
         </is>
-      </c>
-      <c r="AI27" t="b">
-        <v>0</v>
       </c>
       <c r="AJ27" t="b">
         <v>0</v>
@@ -4973,21 +4949,21 @@
         <v>0</v>
       </c>
       <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr">
+      <c r="AF28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="inlineStr">
         <is>
           <t>Collaborates with interdisciplinary teams to design and implement cyber security measures.</t>
         </is>
       </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
+      <c r="AH28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
         <is>
           <t>interdisciplinary teamwork, cyber security coordination, cross‑functional communication, stakeholder engagement, collaboration tools</t>
         </is>
-      </c>
-      <c r="AI28" t="b">
-        <v>0</v>
       </c>
       <c r="AJ28" t="b">
         <v>0</v>
@@ -5113,7 +5089,7 @@
         <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -5122,7 +5098,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>keep:6, "Technology Platform Utilisation":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z29" t="b">
@@ -5137,21 +5113,21 @@
         <v>0</v>
       </c>
       <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr">
+      <c r="AF29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="inlineStr">
         <is>
           <t>Selects and operates suitable platforms to deliver cyber security awareness initiatives across the work area.</t>
         </is>
       </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
+      <c r="AH29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
         <is>
           <t>cyber security, security platforms, SIEM, threat monitoring, information security</t>
         </is>
-      </c>
-      <c r="AI29" t="b">
-        <v>0</v>
       </c>
       <c r="AJ29" t="b">
         <v>0</v>
@@ -5297,21 +5273,21 @@
         <v>0</v>
       </c>
       <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr">
+      <c r="AF30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="inlineStr">
         <is>
           <t>Analyses current cyber threat reports to assess organisational impacts and advise on security measures.</t>
         </is>
       </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
+      <c r="AH30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
         <is>
           <t>cyber security, threat intelligence, trend monitoring, vulnerability assessment, security analytics</t>
         </is>
-      </c>
-      <c r="AI30" t="b">
-        <v>0</v>
       </c>
       <c r="AJ30" t="b">
         <v>0</v>
@@ -5461,21 +5437,21 @@
         <v>0</v>
       </c>
       <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr">
+      <c r="AF31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="inlineStr">
         <is>
           <t>Coordinates training sessions and information updates by scheduling, delivering and recording activities.</t>
         </is>
       </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
+      <c r="AH31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
         <is>
           <t>training schedules, learning management systems, record management, information updates, training logistics</t>
         </is>
-      </c>
-      <c r="AI31" t="b">
-        <v>0</v>
       </c>
       <c r="AJ31" t="b">
         <v>0</v>
@@ -5525,16 +5501,16 @@
         <v>0</v>
       </c>
       <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="b">
+      <c r="AF32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="b">
         <v>1</v>
       </c>
-      <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="b">
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="b">
         <v>1</v>
-      </c>
-      <c r="AJ32" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -5581,16 +5557,16 @@
         <v>0</v>
       </c>
       <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="b">
+      <c r="AF33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="b">
         <v>1</v>
       </c>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="b">
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="b">
         <v>1</v>
-      </c>
-      <c r="AJ33" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -5736,21 +5712,21 @@
         <v>0</v>
       </c>
       <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr">
+      <c r="AF34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="inlineStr">
         <is>
           <t>Installs and configures up‑to‑date anti‑malware on all workstations to ensure continuous protection.</t>
         </is>
       </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
+      <c r="AH34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
         <is>
           <t>cyber security, endpoint protection, malware scanning, signature updates, security hygiene</t>
         </is>
-      </c>
-      <c r="AI34" t="b">
-        <v>0</v>
       </c>
       <c r="AJ34" t="b">
         <v>0</v>
@@ -5895,21 +5871,21 @@
         <v>0</v>
       </c>
       <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr">
+      <c r="AF35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="inlineStr">
         <is>
           <t>Analyses breach volumes and assesses business impacts across review periods to inform risk mitigation.</t>
         </is>
       </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
+      <c r="AH35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
         <is>
           <t>risk assessment, incident tracking, business impact analysis, compliance reporting, security metrics</t>
         </is>
-      </c>
-      <c r="AI35" t="b">
-        <v>0</v>
       </c>
       <c r="AJ35" t="b">
         <v>0</v>
@@ -6030,12 +6006,12 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>keep:6, "Device Configuration":1</t>
+          <t>keep:5, "Device Configuration":2</t>
         </is>
       </c>
       <c r="Z36" t="b">
@@ -6050,21 +6026,21 @@
         <v>0</v>
       </c>
       <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr">
+      <c r="AF36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="inlineStr">
         <is>
           <t>Performs initial device set‑up by updating firmware and configuring settings on new devices.</t>
         </is>
       </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
+      <c r="AH36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
         <is>
           <t>device provisioning, firmware updates, configuration management, hardware initialisation, system onboarding</t>
         </is>
-      </c>
-      <c r="AI36" t="b">
-        <v>0</v>
       </c>
       <c r="AJ36" t="b">
         <v>0</v>
@@ -6205,21 +6181,21 @@
         <v>0</v>
       </c>
       <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr">
+      <c r="AF37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="inlineStr">
         <is>
           <t>Implements device encryption in accordance with prescribed procedures to secure hardware.</t>
         </is>
       </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
+      <c r="AH37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
         <is>
           <t>encryption, device security, endpoint encryption, mobile device management, cryptography</t>
         </is>
-      </c>
-      <c r="AI37" t="b">
-        <v>0</v>
       </c>
       <c r="AJ37" t="b">
         <v>0</v>
@@ -6373,24 +6349,24 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>Skill name uses "Inventory" which is not in unit text; the activity is to create and maintain a register, not manage an inventory</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
+          <t>Skill name uses "Inventory" instead of "register" and frames activity as inventory management, which is not the terminology used in the unit</t>
+        </is>
+      </c>
+      <c r="AF38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="inlineStr">
         <is>
           <t>Creates and updates a register of networked devices to support inventory tracking and asset management.</t>
         </is>
       </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
+      <c r="AH38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
         <is>
           <t>IT asset tracking, hardware registers, network inventories, CMDB, asset management software</t>
         </is>
-      </c>
-      <c r="AI38" t="b">
-        <v>0</v>
       </c>
       <c r="AJ38" t="b">
         <v>0</v>
@@ -6539,21 +6515,21 @@
         <v>0</v>
       </c>
       <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr">
+      <c r="AF39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="inlineStr">
         <is>
           <t>Conducts gap analyses to assess and benchmark best‑practice implementation effectiveness.</t>
         </is>
       </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
+      <c r="AH39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
         <is>
           <t>benchmarking, performance metrics, best‑practice assessment, process improvement, effectiveness evaluation</t>
         </is>
-      </c>
-      <c r="AI39" t="b">
-        <v>0</v>
       </c>
       <c r="AJ39" t="b">
         <v>0</v>
@@ -6575,7 +6551,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Password Creation</t>
+          <t>Password Strength Creation</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -6671,19 +6647,15 @@
         </is>
       </c>
       <c r="V40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 7/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>keep:0, "Password Creation":7</t>
+          <t>keep:5, "Password Creation/Strong Password Creation":2</t>
         </is>
       </c>
       <c r="Z40" t="b">
@@ -6698,21 +6670,21 @@
         <v>0</v>
       </c>
       <c r="AE40" t="inlineStr"/>
-      <c r="AF40" t="inlineStr">
+      <c r="AF40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="inlineStr">
         <is>
           <t>Generates robust, unique passwords for personal and work accounts in line with approved complexity criteria.</t>
         </is>
       </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
+      <c r="AH40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
         <is>
           <t>authentication, password complexity, entropy, cyber security, password managers</t>
         </is>
-      </c>
-      <c r="AI40" t="b">
-        <v>0</v>
       </c>
       <c r="AJ40" t="b">
         <v>0</v>
@@ -6861,21 +6833,21 @@
         <v>0</v>
       </c>
       <c r="AE41" t="inlineStr"/>
-      <c r="AF41" t="inlineStr">
+      <c r="AF41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="inlineStr">
         <is>
           <t>Develops comprehensive physical security plans and disseminates them organisation‑wide to ensure coordinated protection.</t>
         </is>
       </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
+      <c r="AH41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
         <is>
           <t>risk assessment, access control systems, security policy development, facility protection, stakeholder communication</t>
         </is>
-      </c>
-      <c r="AI41" t="b">
-        <v>0</v>
       </c>
       <c r="AJ41" t="b">
         <v>0</v>
@@ -7024,21 +6996,21 @@
         <v>0</v>
       </c>
       <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr">
+      <c r="AF42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="inlineStr">
         <is>
           <t>Assesses device data sensitivity to assign appropriate risk categories for security management.</t>
         </is>
       </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
+      <c r="AH42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
         <is>
           <t>risk assessment, information sensitivity, device classification, cyber security, risk matrices</t>
         </is>
-      </c>
-      <c r="AI42" t="b">
-        <v>0</v>
       </c>
       <c r="AJ42" t="b">
         <v>0</v>
@@ -7167,16 +7139,16 @@
         <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>keep:2, "Physical Security Plan Communication":5</t>
+          <t>keep:0, "Physical Security Plan Communication":7</t>
         </is>
       </c>
       <c r="Z43" t="b">
@@ -7195,21 +7167,21 @@
         <v>0</v>
       </c>
       <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr">
+      <c r="AF43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="inlineStr">
         <is>
           <t>Delivers organisation‑wide briefings on physical security plans to support understanding and compliance.</t>
         </is>
       </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
+      <c r="AH43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
         <is>
           <t>physical security, risk assessment, security policy, stakeholder communication, access control</t>
         </is>
-      </c>
-      <c r="AI43" t="b">
-        <v>0</v>
       </c>
       <c r="AJ43" t="b">
         <v>0</v>
@@ -7338,7 +7310,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
@@ -7358,21 +7330,21 @@
         <v>0</v>
       </c>
       <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr">
+      <c r="AF44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="inlineStr">
         <is>
           <t>Selects appropriate security protocols for each device to mitigate identified risk levels.</t>
         </is>
       </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
+      <c r="AH44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
         <is>
           <t>risk assessment, encryption standards, device hardening, cyber security governance, protocol compliance</t>
         </is>
-      </c>
-      <c r="AI44" t="b">
-        <v>0</v>
       </c>
       <c r="AJ44" t="b">
         <v>0</v>
@@ -7521,21 +7493,21 @@
         <v>0</v>
       </c>
       <c r="AE45" t="inlineStr"/>
-      <c r="AF45" t="inlineStr">
+      <c r="AF45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="inlineStr">
         <is>
           <t>Advises the organisation by evaluating options and recommending optimal security strategies.</t>
         </is>
       </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
+      <c r="AH45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
         <is>
           <t>cyber security governance, risk assessment, security frameworks, threat modelling, ISO 27001</t>
         </is>
-      </c>
-      <c r="AI45" t="b">
-        <v>0</v>
       </c>
       <c r="AJ45" t="b">
         <v>0</v>
@@ -7665,7 +7637,7 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>keep:5, "Security Development Monitoring":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z46" t="b">
@@ -7680,21 +7652,21 @@
         <v>0</v>
       </c>
       <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr">
+      <c r="AF46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="inlineStr">
         <is>
           <t>Monitors emerging digital security developments to inform risk assessments and protective measures.</t>
         </is>
       </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
+      <c r="AH46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
         <is>
           <t>cyber security, threat intelligence, vulnerability tracking, security intelligence feeds, digital risk monitoring</t>
         </is>
-      </c>
-      <c r="AI46" t="b">
-        <v>0</v>
       </c>
       <c r="AJ46" t="b">
         <v>0</v>
@@ -7843,21 +7815,21 @@
         <v>0</v>
       </c>
       <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="inlineStr">
+      <c r="AF47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="inlineStr">
         <is>
           <t>Installs and configures software patches on desktop and mobile devices to maintain system security.</t>
         </is>
       </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
+      <c r="AH47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
         <is>
           <t>patch management, software updates, endpoint management, mobile device management, security patches</t>
         </is>
-      </c>
-      <c r="AI47" t="b">
-        <v>0</v>
       </c>
       <c r="AJ47" t="b">
         <v>0</v>
@@ -7986,7 +7958,7 @@
         <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -7995,7 +7967,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>keep:5, "Multi-factor Authentication Enablement":2</t>
+          <t>keep:6, "Multi-factor Authentication Enablement":1</t>
         </is>
       </c>
       <c r="Z48" t="b">
@@ -8010,21 +7982,21 @@
         <v>0</v>
       </c>
       <c r="AE48" t="inlineStr"/>
-      <c r="AF48" t="inlineStr">
+      <c r="AF48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="inlineStr">
         <is>
           <t>Enables multi‑factor authentication on supported systems to strengthen account security.</t>
         </is>
       </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
+      <c r="AH48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
         <is>
           <t>multi‑factor authentication, MFA, OTP, access control, cyber security</t>
         </is>
-      </c>
-      <c r="AI48" t="b">
-        <v>0</v>
       </c>
       <c r="AJ48" t="b">
         <v>0</v>
@@ -8156,21 +8128,21 @@
         <v>0</v>
       </c>
       <c r="AE49" t="inlineStr"/>
-      <c r="AF49" t="inlineStr">
+      <c r="AF49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="inlineStr">
         <is>
           <t>Develops detailed action plans aligned with policies, prioritising tasks and scheduling implementation.</t>
         </is>
       </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
+      <c r="AH49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
         <is>
           <t>project scheduling, prioritisation, policy compliance, change management, implementation planning</t>
         </is>
-      </c>
-      <c r="AI49" t="b">
-        <v>0</v>
       </c>
       <c r="AJ49" t="b">
         <v>0</v>
@@ -8306,21 +8278,21 @@
         <v>0</v>
       </c>
       <c r="AE50" t="inlineStr"/>
-      <c r="AF50" t="inlineStr">
+      <c r="AF50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="inlineStr">
         <is>
           <t>Ranks proposed changes to clarify improvement opportunities and inform implementation scheduling.</t>
         </is>
       </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
+      <c r="AH50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
         <is>
           <t>change management, prioritisation, opportunity assessment, implementation scheduling, project planning</t>
         </is>
-      </c>
-      <c r="AI50" t="b">
-        <v>0</v>
       </c>
       <c r="AJ50" t="b">
         <v>0</v>
@@ -8432,7 +8404,7 @@
         <v>1</v>
       </c>
       <c r="W51" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -8456,21 +8428,21 @@
         <v>0</v>
       </c>
       <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr">
+      <c r="AF51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="inlineStr">
         <is>
           <t>Explores emerging digital tools to organise and analyse data and support effective communication.</t>
         </is>
       </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
+      <c r="AH51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
         <is>
           <t>data management, digital collaboration tools, emerging technologies, cloud computing, data visualisation</t>
         </is>
-      </c>
-      <c r="AI51" t="b">
-        <v>0</v>
       </c>
       <c r="AJ51" t="b">
         <v>0</v>
@@ -8602,21 +8574,21 @@
         <v>0</v>
       </c>
       <c r="AE52" t="inlineStr"/>
-      <c r="AF52" t="inlineStr">
+      <c r="AF52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="inlineStr">
         <is>
           <t>Prepares evaluation documents, organises findings and submits them to a supervisor for review.</t>
         </is>
       </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
+      <c r="AH52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
         <is>
           <t>technical writing, document review, quality assurance, reporting standards, document control</t>
         </is>
-      </c>
-      <c r="AI52" t="b">
-        <v>0</v>
       </c>
       <c r="AJ52" t="b">
         <v>0</v>
@@ -8760,21 +8732,21 @@
         <v>0</v>
       </c>
       <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr">
+      <c r="AF53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="inlineStr">
         <is>
           <t>Analyses strategic objectives against current ICT capability in hybrid environments to identify gaps and propose improvements.</t>
         </is>
       </c>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
+      <c r="AH53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
         <is>
           <t>gap analysis, strategic alignment, technology roadmaps, ICT governance, digital transformation</t>
         </is>
-      </c>
-      <c r="AI53" t="b">
-        <v>0</v>
       </c>
       <c r="AJ53" t="b">
         <v>0</v>
@@ -8922,21 +8894,21 @@
         <v>0</v>
       </c>
       <c r="AE54" t="inlineStr"/>
-      <c r="AF54" t="inlineStr">
+      <c r="AF54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="inlineStr">
         <is>
           <t>Assesses proposed ICT system changes in hybrid environments for alignment with organisational strategic objectives.</t>
         </is>
       </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
+      <c r="AH54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
         <is>
           <t>impact assessment, ICT systems, strategic alignment, change management, performance metrics</t>
         </is>
-      </c>
-      <c r="AI54" t="b">
-        <v>0</v>
       </c>
       <c r="AJ54" t="b">
         <v>0</v>
@@ -8958,7 +8930,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Innovative Idea Investigation</t>
+          <t>Innovative Solution Investigation</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -9045,19 +9017,15 @@
         </is>
       </c>
       <c r="V55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 4/7: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>keep:3, "Innovative Idea Investigation":4</t>
+          <t>keep:6, "Innovative Idea Investigation":1</t>
         </is>
       </c>
       <c r="Z55" t="b">
@@ -9072,21 +9040,21 @@
         <v>0</v>
       </c>
       <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr">
+      <c r="AF55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="inlineStr">
         <is>
           <t>Researches and tests innovative ideas, applying findings to refine work practices and processes.</t>
         </is>
       </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
+      <c r="AH55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
         <is>
           <t>continuous improvement, process optimisation, ideation techniques, creative problem solving, innovation management</t>
         </is>
-      </c>
-      <c r="AI55" t="b">
-        <v>0</v>
       </c>
       <c r="AJ55" t="b">
         <v>0</v>
@@ -9108,7 +9076,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Financial Impact Interpretation</t>
+          <t>Financial Impact Assessment</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -9198,16 +9166,16 @@
         <v>1</v>
       </c>
       <c r="W56" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>keep:0, "Financial Impact Interpretation":4, "Financial Impact Assessment":3</t>
+          <t>keep:0, "Financial Impact Assessment":7</t>
         </is>
       </c>
       <c r="Z56" t="b">
@@ -9222,21 +9190,21 @@
         <v>0</v>
       </c>
       <c r="AE56" t="inlineStr"/>
-      <c r="AF56" t="inlineStr">
+      <c r="AF56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="inlineStr">
         <is>
           <t>Analyses numerical data and calculates financial impacts of proposed changes in hybrid environments.</t>
         </is>
       </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
+      <c r="AH56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
         <is>
           <t>financial analysis, quantitative modelling, cost‑benefit assessment, Excel, statistical calculations</t>
         </is>
-      </c>
-      <c r="AI56" t="b">
-        <v>0</v>
       </c>
       <c r="AJ56" t="b">
         <v>0</v>
@@ -9368,21 +9336,21 @@
         <v>0</v>
       </c>
       <c r="AE57" t="inlineStr"/>
-      <c r="AF57" t="inlineStr">
+      <c r="AF57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="inlineStr">
         <is>
           <t>Assesses policy compliance by documenting standards, targets and implementation approaches within action plans.</t>
         </is>
       </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
+      <c r="AH57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
         <is>
           <t>regulatory standards, compliance frameworks, risk assessment, governance risk and compliance, policy implementation planning</t>
         </is>
-      </c>
-      <c r="AI57" t="b">
-        <v>0</v>
       </c>
       <c r="AJ57" t="b">
         <v>0</v>
@@ -9514,21 +9482,21 @@
         <v>0</v>
       </c>
       <c r="AE58" t="inlineStr"/>
-      <c r="AF58" t="inlineStr">
+      <c r="AF58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="inlineStr">
         <is>
           <t>Develops detailed action plans with prioritised schedules to implement change initiatives efficiently.</t>
         </is>
       </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
+      <c r="AH58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
         <is>
           <t>action planning, prioritised schedules, timeline management, resource allocation, critical path</t>
         </is>
-      </c>
-      <c r="AI58" t="b">
-        <v>0</v>
       </c>
       <c r="AJ58" t="b">
         <v>0</v>
@@ -9660,21 +9628,21 @@
         <v>0</v>
       </c>
       <c r="AE59" t="inlineStr"/>
-      <c r="AF59" t="inlineStr">
+      <c r="AF59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="inlineStr">
         <is>
           <t>Assesses the complexity of ICT system changes and plans risk mitigation strategies across hybrid environments.</t>
         </is>
       </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
+      <c r="AH59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
         <is>
           <t>ICT systems, change management, implementation complexity, risk analysis, impact assessment</t>
         </is>
-      </c>
-      <c r="AI59" t="b">
-        <v>0</v>
       </c>
       <c r="AJ59" t="b">
         <v>0</v>
@@ -9818,21 +9786,21 @@
         <v>0</v>
       </c>
       <c r="AE60" t="inlineStr"/>
-      <c r="AF60" t="inlineStr">
+      <c r="AF60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="inlineStr">
         <is>
           <t>Prepares concise reports outlining changes, gaps and improvement opportunities for senior staff.</t>
         </is>
       </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
+      <c r="AH60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
         <is>
           <t>executive communication, gap analysis, change management, improvement recommendations, business reporting</t>
         </is>
-      </c>
-      <c r="AI60" t="b">
-        <v>0</v>
       </c>
       <c r="AJ60" t="b">
         <v>0</v>
@@ -9980,21 +9948,21 @@
         <v>0</v>
       </c>
       <c r="AE61" t="inlineStr"/>
-      <c r="AF61" t="inlineStr">
+      <c r="AF61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="inlineStr">
         <is>
           <t>Analyses the organisation’s strategic plan against the industry environment and objectives, documenting findings.</t>
         </is>
       </c>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
+      <c r="AH61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
         <is>
           <t>strategic alignment, industry benchmarking, SWOT analysis, organisational objectives, gap analysis</t>
         </is>
-      </c>
-      <c r="AI61" t="b">
-        <v>0</v>
       </c>
       <c r="AJ61" t="b">
         <v>0</v>
@@ -10126,21 +10094,21 @@
         <v>0</v>
       </c>
       <c r="AE62" t="inlineStr"/>
-      <c r="AF62" t="inlineStr">
+      <c r="AF62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="inlineStr">
         <is>
           <t>Uses structured analytical frameworks to evaluate options and resolve complex, non‑routine problems.</t>
         </is>
       </c>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
+      <c r="AH62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
         <is>
           <t>decision analysis, analytical reasoning, structured methodologies, risk assessment, scenario modelling</t>
         </is>
-      </c>
-      <c r="AI62" t="b">
-        <v>0</v>
       </c>
       <c r="AJ62" t="b">
         <v>0</v>
@@ -10272,21 +10240,21 @@
         <v>0</v>
       </c>
       <c r="AE63" t="inlineStr"/>
-      <c r="AF63" t="inlineStr">
+      <c r="AF63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="inlineStr">
         <is>
           <t>Translates technical terminology into plain English to support understanding across diverse staff groups.</t>
         </is>
       </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
+      <c r="AH63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
         <is>
           <t>plain language, jargon translation, stakeholder communication, technical writing, audience adaptation</t>
         </is>
-      </c>
-      <c r="AI63" t="b">
-        <v>0</v>
       </c>
       <c r="AJ63" t="b">
         <v>0</v>
@@ -10414,13 +10382,9 @@
         </is>
       </c>
       <c r="Z64" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>Legislative Analysis</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA64" t="inlineStr"/>
       <c r="AB64" t="b">
         <v>0</v>
       </c>
@@ -10429,21 +10393,21 @@
         <v>0</v>
       </c>
       <c r="AE64" t="inlineStr"/>
-      <c r="AF64" t="inlineStr">
+      <c r="AF64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="inlineStr">
         <is>
           <t>Analyses complex legislative material to assess compliance with organisational standards.</t>
         </is>
       </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
+      <c r="AH64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
         <is>
           <t>legislative compliance, policy analysis, regulatory standards, qualitative analysis</t>
         </is>
-      </c>
-      <c r="AI64" t="b">
-        <v>0</v>
       </c>
       <c r="AJ64" t="b">
         <v>0</v>
@@ -10578,21 +10542,21 @@
         <v>0</v>
       </c>
       <c r="AE65" t="inlineStr"/>
-      <c r="AF65" t="inlineStr">
+      <c r="AF65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="inlineStr">
         <is>
           <t>Evaluates organisational privacy policies against industry standards to ensure compliance in hybrid environments.</t>
         </is>
       </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
+      <c r="AH65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
         <is>
           <t>privacy policy, regulatory standards, risk assessment, audit, data protection</t>
         </is>
-      </c>
-      <c r="AI65" t="b">
-        <v>0</v>
       </c>
       <c r="AJ65" t="b">
         <v>0</v>
@@ -10727,21 +10691,21 @@
         <v>0</v>
       </c>
       <c r="AE66" t="inlineStr"/>
-      <c r="AF66" t="inlineStr">
+      <c r="AF66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="inlineStr">
         <is>
           <t>Reviews ethical practices and feedback and applies the organisational code of ethics to guide decisions.</t>
         </is>
       </c>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
+      <c r="AH66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
         <is>
           <t>professional ethics, codes of conduct, compliance, organisational governance, ethical frameworks</t>
         </is>
-      </c>
-      <c r="AI66" t="b">
-        <v>0</v>
       </c>
       <c r="AJ66" t="b">
         <v>0</v>
@@ -10876,21 +10840,21 @@
         <v>0</v>
       </c>
       <c r="AE67" t="inlineStr"/>
-      <c r="AF67" t="inlineStr">
+      <c r="AF67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="inlineStr">
         <is>
           <t>Collects and addresses feedback on review and grievance documentation from designated personnel.</t>
         </is>
       </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
+      <c r="AH67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
         <is>
           <t>grievance procedures, review processes, stakeholder communication, document management, complaint handling</t>
         </is>
-      </c>
-      <c r="AI67" t="b">
-        <v>0</v>
       </c>
       <c r="AJ67" t="b">
         <v>0</v>
@@ -11025,21 +10989,21 @@
         <v>0</v>
       </c>
       <c r="AE68" t="inlineStr"/>
-      <c r="AF68" t="inlineStr">
+      <c r="AF68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="inlineStr">
         <is>
           <t>Conducts industry‑standard tests to assess information integrity, confidentiality, security and availability.</t>
         </is>
       </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
+      <c r="AH68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
         <is>
           <t>penetration testing, vulnerability assessment, ISO 27001, CIA triad, security controls</t>
         </is>
-      </c>
-      <c r="AI68" t="b">
-        <v>0</v>
       </c>
       <c r="AJ68" t="b">
         <v>0</v>
@@ -11174,21 +11138,21 @@
         <v>0</v>
       </c>
       <c r="AE69" t="inlineStr"/>
-      <c r="AF69" t="inlineStr">
+      <c r="AF69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="inlineStr">
         <is>
           <t>Synthesises diverse sources into cohesive written reports using specialised terminology and supporting documentation.</t>
         </is>
       </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
+      <c r="AH69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
         <is>
           <t>literature review, source integration, technical writing, citation management, knowledge synthesis</t>
         </is>
-      </c>
-      <c r="AI69" t="b">
-        <v>0</v>
       </c>
       <c r="AJ69" t="b">
         <v>0</v>
@@ -11323,21 +11287,21 @@
         <v>0</v>
       </c>
       <c r="AE70" t="inlineStr"/>
-      <c r="AF70" t="inlineStr">
+      <c r="AF70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="inlineStr">
         <is>
           <t>Analyses and interprets intellectual property and copyright legislation to ensure organisational compliance.</t>
         </is>
       </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
+      <c r="AH70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
         <is>
           <t>intellectual property law, copyright legislation, policy compliance, legal research, regulatory analysis</t>
         </is>
-      </c>
-      <c r="AI70" t="b">
-        <v>0</v>
       </c>
       <c r="AJ70" t="b">
         <v>0</v>
@@ -11472,21 +11436,21 @@
         <v>0</v>
       </c>
       <c r="AE71" t="inlineStr"/>
-      <c r="AF71" t="inlineStr">
+      <c r="AF71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="inlineStr">
         <is>
           <t>Delivers updated policies, procedures and ethics documentation to designated personnel.</t>
         </is>
       </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
+      <c r="AH71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
         <is>
           <t>document dissemination, compliance communication, stakeholder engagement, internal governance, ethics training</t>
         </is>
-      </c>
-      <c r="AI71" t="b">
-        <v>0</v>
       </c>
       <c r="AJ71" t="b">
         <v>0</v>
@@ -11621,21 +11585,21 @@
         <v>0</v>
       </c>
       <c r="AE72" t="inlineStr"/>
-      <c r="AF72" t="inlineStr">
+      <c r="AF72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="inlineStr">
         <is>
           <t>Updates privacy policies, procedures and codes of ethics to reflect current legislation and compliance requirements.</t>
         </is>
       </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
+      <c r="AH72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
         <is>
           <t>privacy legislation, compliance governance, policy management, codes of ethics, regulatory documentation</t>
         </is>
-      </c>
-      <c r="AI72" t="b">
-        <v>0</v>
       </c>
       <c r="AJ72" t="b">
         <v>0</v>
@@ -11770,21 +11734,21 @@
         <v>0</v>
       </c>
       <c r="AE73" t="inlineStr"/>
-      <c r="AF73" t="inlineStr">
+      <c r="AF73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="inlineStr">
         <is>
           <t>Develops, records and submits review and grievance procedures to designated personnel.</t>
         </is>
       </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
+      <c r="AH73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
         <is>
           <t>policy drafting, grievance management, standard operating procedures, process documentation, compliance workflows</t>
         </is>
-      </c>
-      <c r="AI73" t="b">
-        <v>0</v>
       </c>
       <c r="AJ73" t="b">
         <v>0</v>
@@ -11912,32 +11876,28 @@
       </c>
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Foundation Skill 'Planning and organising' is implicit in the performance criteria and elements; it does not represent a distinct activity separate from the unit's PCs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC74" t="inlineStr"/>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="inlineStr"/>
-      <c r="AF74" t="inlineStr">
+      <c r="AF74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="inlineStr">
         <is>
           <t>Sequences and schedules complex activities, monitors progress and coordinates communication to maintain delivery momentum.</t>
         </is>
       </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
+      <c r="AH74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
         <is>
           <t>scheduling, resource allocation, stakeholder communication, project monitoring, Gantt charts</t>
         </is>
-      </c>
-      <c r="AI74" t="b">
-        <v>0</v>
       </c>
       <c r="AJ74" t="b">
         <v>0</v>
@@ -12072,21 +12032,21 @@
         <v>0</v>
       </c>
       <c r="AE75" t="inlineStr"/>
-      <c r="AF75" t="inlineStr">
+      <c r="AF75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="inlineStr">
         <is>
           <t>Monitors and analyses legislative changes to ensure ongoing compliance with rights and responsibilities.</t>
         </is>
       </c>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
+      <c r="AH75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
         <is>
           <t>compliance, legislation monitoring, regulatory analysis, policy tracking, legal research</t>
         </is>
-      </c>
-      <c r="AI75" t="b">
-        <v>0</v>
       </c>
       <c r="AJ75" t="b">
         <v>0</v>
@@ -12201,12 +12161,12 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>keep:5, "Digital Information Security":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z76" t="b">
@@ -12221,21 +12181,21 @@
         <v>0</v>
       </c>
       <c r="AE76" t="inlineStr"/>
-      <c r="AF76" t="inlineStr">
+      <c r="AF76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="inlineStr">
         <is>
           <t>Manages digital information securely by lawfully collecting, storing, accessing and sharing data using compliant systems.</t>
         </is>
       </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
+      <c r="AH76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
         <is>
           <t>cyber security, data protection, information governance, privacy compliance, access control</t>
         </is>
-      </c>
-      <c r="AI76" t="b">
-        <v>0</v>
       </c>
       <c r="AJ76" t="b">
         <v>0</v>
@@ -12370,21 +12330,21 @@
         <v>0</v>
       </c>
       <c r="AE77" t="inlineStr"/>
-      <c r="AF77" t="inlineStr">
+      <c r="AF77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="inlineStr">
         <is>
           <t>Distributes updated policies to stakeholders in accordance with organisational protocols.</t>
         </is>
       </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
+      <c r="AH77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
         <is>
           <t>policy dissemination, stakeholder engagement, communication protocols, change management, organisational compliance</t>
         </is>
-      </c>
-      <c r="AI77" t="b">
-        <v>0</v>
       </c>
       <c r="AJ77" t="b">
         <v>0</v>
@@ -12499,7 +12459,7 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.95</v>
       </c>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr">
@@ -12519,21 +12479,21 @@
         <v>0</v>
       </c>
       <c r="AE78" t="inlineStr"/>
-      <c r="AF78" t="inlineStr">
+      <c r="AF78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="inlineStr">
         <is>
           <t>Engages in verbal idea exchange, actively listening and questioning to draw out others’ views.</t>
         </is>
       </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
+      <c r="AH78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
         <is>
           <t>active listening, questioning techniques, stakeholder engagement, dialogue facilitation, interpersonal communication</t>
         </is>
-      </c>
-      <c r="AI78" t="b">
-        <v>0</v>
       </c>
       <c r="AJ78" t="b">
         <v>0</v>
@@ -12655,12 +12615,12 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>keep:6, "Blockchain Platform Installation":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z79" t="b">
@@ -12675,21 +12635,21 @@
         <v>0</v>
       </c>
       <c r="AE79" t="inlineStr"/>
-      <c r="AF79" t="inlineStr">
+      <c r="AF79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="inlineStr">
         <is>
           <t>Installs and configures blockchain platform components in line with approved design specifications.</t>
         </is>
       </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
+      <c r="AH79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
         <is>
           <t>distributed ledger, node deployment, consensus configuration, Ethereum, Docker</t>
         </is>
-      </c>
-      <c r="AI79" t="b">
-        <v>0</v>
       </c>
       <c r="AJ79" t="b">
         <v>0</v>
@@ -12820,7 +12780,7 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>keep:1, "Blockchain Anomaly Solving/Blockchain Anomaly Problem Solving":4, "Blockchain Anomaly Resolution":2</t>
+          <t>keep:2, "Blockchain Anomaly Solving/Blockchain Anomaly Problem Solving":4, "Blockchain Anomaly Resolution":1</t>
         </is>
       </c>
       <c r="Z80" t="b">
@@ -12835,21 +12795,21 @@
         <v>0</v>
       </c>
       <c r="AE80" t="inlineStr"/>
-      <c r="AF80" t="inlineStr">
+      <c r="AF80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="inlineStr">
         <is>
           <t>Identifies and resolves blockchain anomalies through contextual analysis to detect subtle deviations.</t>
         </is>
       </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
+      <c r="AH80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
         <is>
           <t>anomaly detection, blockchain analytics, smart contract debugging, cryptographic forensics, pattern recognition</t>
         </is>
-      </c>
-      <c r="AI80" t="b">
-        <v>0</v>
       </c>
       <c r="AJ80" t="b">
         <v>0</v>
@@ -12991,21 +12951,21 @@
         <v>0</v>
       </c>
       <c r="AE81" t="inlineStr"/>
-      <c r="AF81" t="inlineStr">
+      <c r="AF81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="inlineStr">
         <is>
           <t>Defines blockchain objectives and requirements aligned with organisational needs in hybrid environments.</t>
         </is>
       </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
+      <c r="AH81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
         <is>
           <t>distributed ledger, use‑case definition, stakeholder analysis, smart contract design, governance frameworks</t>
         </is>
-      </c>
-      <c r="AI81" t="b">
-        <v>0</v>
       </c>
       <c r="AJ81" t="b">
         <v>0</v>
@@ -13147,21 +13107,21 @@
         <v>0</v>
       </c>
       <c r="AE82" t="inlineStr"/>
-      <c r="AF82" t="inlineStr">
+      <c r="AF82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="inlineStr">
         <is>
           <t>Implements consensus mechanisms by configuring and deploying required system components.</t>
         </is>
       </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
+      <c r="AH82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
         <is>
           <t>blockchain, distributed ledger, consensus algorithms, peer‑to‑peer networking, Byzantine fault tolerance</t>
         </is>
-      </c>
-      <c r="AI82" t="b">
-        <v>0</v>
       </c>
       <c r="AJ82" t="b">
         <v>0</v>
@@ -13303,21 +13263,21 @@
         <v>0</v>
       </c>
       <c r="AE83" t="inlineStr"/>
-      <c r="AF83" t="inlineStr">
+      <c r="AF83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="inlineStr">
         <is>
           <t>Produces detailed design documentation aligned with organisational requirements to support project delivery.</t>
         </is>
       </c>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
+      <c r="AH83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
         <is>
           <t>technical specifications, design standards, engineering documentation, organisational requirements</t>
         </is>
-      </c>
-      <c r="AI83" t="b">
-        <v>0</v>
       </c>
       <c r="AJ83" t="b">
         <v>0</v>
@@ -13448,13 +13408,9 @@
         </is>
       </c>
       <c r="Z84" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>Design Documentation Preparation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA84" t="inlineStr"/>
       <c r="AB84" t="b">
         <v>0</v>
       </c>
@@ -13463,21 +13419,21 @@
         <v>0</v>
       </c>
       <c r="AE84" t="inlineStr"/>
-      <c r="AF84" t="inlineStr">
+      <c r="AF84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="inlineStr">
         <is>
           <t>Submits documentation for review, seeks feedback and incorporates approved amendments.</t>
         </is>
       </c>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
+      <c r="AH84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
         <is>
           <t>record‑keeping, feedback loops, compliance, workflow approvals, electronic filing</t>
         </is>
-      </c>
-      <c r="AI84" t="b">
-        <v>0</v>
       </c>
       <c r="AJ84" t="b">
         <v>0</v>
@@ -13619,21 +13575,21 @@
         <v>0</v>
       </c>
       <c r="AE85" t="inlineStr"/>
-      <c r="AF85" t="inlineStr">
+      <c r="AF85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="inlineStr">
         <is>
           <t>Designs integration workflows by mapping data flows and configuring tools to meet organisational needs.</t>
         </is>
       </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
+      <c r="AH85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
         <is>
           <t>systems integration, workflow orchestration, process automation, ETL, API middleware</t>
         </is>
-      </c>
-      <c r="AI85" t="b">
-        <v>0</v>
       </c>
       <c r="AJ85" t="b">
         <v>0</v>
@@ -13775,21 +13731,21 @@
         <v>0</v>
       </c>
       <c r="AE86" t="inlineStr"/>
-      <c r="AF86" t="inlineStr">
+      <c r="AF86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="inlineStr">
         <is>
           <t>Develops and records maintenance schedules aligned with equipment requirements and timelines.</t>
         </is>
       </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
+      <c r="AH86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
         <is>
           <t>preventive maintenance, asset management, CMMS, work order scheduling, reliability engineering</t>
         </is>
-      </c>
-      <c r="AI86" t="b">
-        <v>0</v>
       </c>
       <c r="AJ86" t="b">
         <v>0</v>
@@ -13915,12 +13871,12 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 5/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>keep:2, "Maintenance Testing":5</t>
+          <t>keep:1, "Maintenance Testing":6</t>
         </is>
       </c>
       <c r="Z87" t="b">
@@ -13935,21 +13891,21 @@
         <v>0</v>
       </c>
       <c r="AE87" t="inlineStr"/>
-      <c r="AF87" t="inlineStr">
+      <c r="AF87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="inlineStr">
         <is>
           <t>Plans, selects and conducts maintenance tests to verify equipment functionality and compliance.</t>
         </is>
       </c>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
+      <c r="AH87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr">
         <is>
           <t>preventive maintenance, test procedures, equipment inspection, reliability testing, compliance standards</t>
         </is>
-      </c>
-      <c r="AI87" t="b">
-        <v>0</v>
       </c>
       <c r="AJ87" t="b">
         <v>0</v>
@@ -14091,21 +14047,21 @@
         <v>0</v>
       </c>
       <c r="AE88" t="inlineStr"/>
-      <c r="AF88" t="inlineStr">
+      <c r="AF88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="inlineStr">
         <is>
           <t>Selects and configures security platforms for blockchain solutions based on risk assessments.</t>
         </is>
       </c>
-      <c r="AG88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
+      <c r="AH88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI88" t="inlineStr">
         <is>
           <t>blockchain, security architecture, platform evaluation, cryptography, risk assessment</t>
         </is>
-      </c>
-      <c r="AI88" t="b">
-        <v>0</v>
       </c>
       <c r="AJ88" t="b">
         <v>0</v>
@@ -14247,21 +14203,21 @@
         <v>0</v>
       </c>
       <c r="AE89" t="inlineStr"/>
-      <c r="AF89" t="inlineStr">
+      <c r="AF89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="inlineStr">
         <is>
           <t>Deploys and manages smart contracts on approved blockchain platforms in line with solution specifications.</t>
         </is>
       </c>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
+      <c r="AH89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="inlineStr">
         <is>
           <t>blockchain, Ethereum, Solidity, decentralised applications, Web3</t>
         </is>
-      </c>
-      <c r="AI89" t="b">
-        <v>0</v>
       </c>
       <c r="AJ89" t="b">
         <v>0</v>
@@ -14403,21 +14359,21 @@
         <v>0</v>
       </c>
       <c r="AE90" t="inlineStr"/>
-      <c r="AF90" t="inlineStr">
+      <c r="AF90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="inlineStr">
         <is>
           <t>Diagnoses and resolves blockchain solution issues and optimises performance for scalable deployment.</t>
         </is>
       </c>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
+      <c r="AH90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr">
         <is>
           <t>blockchain, smart contracts, Solidity, distributed ledger, performance scaling</t>
         </is>
-      </c>
-      <c r="AI90" t="b">
-        <v>0</v>
       </c>
       <c r="AJ90" t="b">
         <v>0</v>
@@ -14559,21 +14515,21 @@
         <v>0</v>
       </c>
       <c r="AE91" t="inlineStr"/>
-      <c r="AF91" t="inlineStr">
+      <c r="AF91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="inlineStr">
         <is>
           <t>Tests and evaluates solutions against organisational requirements to confirm suitability.</t>
         </is>
       </c>
-      <c r="AG91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH91" t="inlineStr">
+      <c r="AH91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
         <is>
           <t>benchmarking, requirements compliance, load testing, service level agreements, performance metrics</t>
         </is>
-      </c>
-      <c r="AI91" t="b">
-        <v>0</v>
       </c>
       <c r="AJ91" t="b">
         <v>0</v>
@@ -14712,28 +14668,28 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Foundation Skill already covered by performance criteria and other skills; not a distinct workplace activity</t>
+          <t>Foundation Skill already covered by performance criteria and other skills; describes generic oral communication rather than a distinct unit activity</t>
         </is>
       </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="inlineStr"/>
-      <c r="AF92" t="inlineStr">
+      <c r="AF92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="inlineStr">
         <is>
           <t>Engages stakeholders to clarify requirements and accountabilities using appropriate industry terminology.</t>
         </is>
       </c>
-      <c r="AG92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH92" t="inlineStr">
+      <c r="AH92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI92" t="inlineStr">
         <is>
           <t>stakeholder engagement, requirements gathering, industry terminology, verbal communication, active listening</t>
         </is>
-      </c>
-      <c r="AI92" t="b">
-        <v>0</v>
       </c>
       <c r="AJ92" t="b">
         <v>0</v>
@@ -14875,21 +14831,21 @@
         <v>0</v>
       </c>
       <c r="AE93" t="inlineStr"/>
-      <c r="AF93" t="inlineStr">
+      <c r="AF93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="inlineStr">
         <is>
           <t>Analyses hybrid environments to identify organisational use cases aligned with business needs.</t>
         </is>
       </c>
-      <c r="AG93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
+      <c r="AH93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI93" t="inlineStr">
         <is>
           <t>requirements analysis, business analysis, stakeholder mapping, use‑case modelling, functional requirements</t>
         </is>
-      </c>
-      <c r="AI93" t="b">
-        <v>0</v>
       </c>
       <c r="AJ93" t="b">
         <v>0</v>
@@ -15042,21 +14998,21 @@
         <v>0</v>
       </c>
       <c r="AE94" t="inlineStr"/>
-      <c r="AF94" t="inlineStr">
+      <c r="AF94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="inlineStr">
         <is>
           <t>Ingests data logs into analytics platforms as instructed to support monitoring and analysis.</t>
         </is>
       </c>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
+      <c r="AH94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr">
         <is>
           <t>data ingestion, log analytics, ETL pipelines, analytics platforms, monitoring</t>
         </is>
-      </c>
-      <c r="AI94" t="b">
-        <v>0</v>
       </c>
       <c r="AJ94" t="b">
         <v>0</v>
@@ -15205,21 +15161,21 @@
         <v>0</v>
       </c>
       <c r="AE95" t="inlineStr"/>
-      <c r="AF95" t="inlineStr">
+      <c r="AF95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="inlineStr">
         <is>
           <t>Identifies relevant legislation and internal policies governing the collection, analysis and use of threat data.</t>
         </is>
       </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
+      <c r="AH95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
         <is>
           <t>regulatory compliance, legislation, policy analysis, threat intelligence, risk assessment</t>
         </is>
-      </c>
-      <c r="AI95" t="b">
-        <v>0</v>
       </c>
       <c r="AJ95" t="b">
         <v>0</v>
@@ -15364,21 +15320,21 @@
         <v>0</v>
       </c>
       <c r="AE96" t="inlineStr"/>
-      <c r="AF96" t="inlineStr">
+      <c r="AF96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="inlineStr">
         <is>
           <t>Examines datasets to identify, document and resolve data discrepancies and inconsistencies.</t>
         </is>
       </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
+      <c r="AH96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
         <is>
           <t>data validation, anomaly detection, data quality, data auditing, profiling</t>
         </is>
-      </c>
-      <c r="AI96" t="b">
-        <v>0</v>
       </c>
       <c r="AJ96" t="b">
         <v>0</v>
@@ -15503,7 +15459,7 @@
         <v>1</v>
       </c>
       <c r="W97" t="n">
-        <v>0.9516666666666667</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -15527,21 +15483,21 @@
         <v>0</v>
       </c>
       <c r="AE97" t="inlineStr"/>
-      <c r="AF97" t="inlineStr">
+      <c r="AF97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="inlineStr">
         <is>
           <t>Compiles alerts, logs and event reports into structured datasets in line with organisational policies.</t>
         </is>
       </c>
-      <c r="AG97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
+      <c r="AH97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr">
         <is>
           <t>log analysis, data ingestion, security monitoring, data governance, ETL processes</t>
         </is>
-      </c>
-      <c r="AI97" t="b">
-        <v>0</v>
       </c>
       <c r="AJ97" t="b">
         <v>0</v>
@@ -15694,21 +15650,21 @@
         <v>0</v>
       </c>
       <c r="AE98" t="inlineStr"/>
-      <c r="AF98" t="inlineStr">
+      <c r="AF98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="inlineStr">
         <is>
           <t>Reviews test results to identify and correct false positives and false negatives.</t>
         </is>
       </c>
-      <c r="AG98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
+      <c r="AH98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI98" t="inlineStr">
         <is>
           <t>type I error, anomaly detection, validation testing, precision‑recall analysis, statistical significance</t>
         </is>
-      </c>
-      <c r="AI98" t="b">
-        <v>0</v>
       </c>
       <c r="AJ98" t="b">
         <v>0</v>
@@ -15849,21 +15805,21 @@
         <v>0</v>
       </c>
       <c r="AE99" t="inlineStr"/>
-      <c r="AF99" t="inlineStr">
+      <c r="AF99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="inlineStr">
         <is>
           <t>Produces formal investigation reports outlining findings and recommendations in accordance with organisational procedures.</t>
         </is>
       </c>
-      <c r="AG99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH99" t="inlineStr">
+      <c r="AH99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI99" t="inlineStr">
         <is>
           <t>incident reporting, root‑cause analysis, procedural compliance, report writing, safety management</t>
         </is>
-      </c>
-      <c r="AI99" t="b">
-        <v>0</v>
       </c>
       <c r="AJ99" t="b">
         <v>0</v>
@@ -16012,21 +15968,21 @@
         <v>0</v>
       </c>
       <c r="AE100" t="inlineStr"/>
-      <c r="AF100" t="inlineStr">
+      <c r="AF100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="inlineStr">
         <is>
           <t>Develops and validates mitigation strategies, action steps and lessons learned with relevant personnel.</t>
         </is>
       </c>
-      <c r="AG100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH100" t="inlineStr">
+      <c r="AH100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr">
         <is>
           <t>risk management, lessons learned, action planning, stakeholder engagement, mitigation planning</t>
         </is>
-      </c>
-      <c r="AI100" t="b">
-        <v>0</v>
       </c>
       <c r="AJ100" t="b">
         <v>0</v>
@@ -16175,21 +16131,21 @@
         <v>0</v>
       </c>
       <c r="AE101" t="inlineStr"/>
-      <c r="AF101" t="inlineStr">
+      <c r="AF101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="inlineStr">
         <is>
           <t>Assesses threats by evaluating likelihood and impact to prioritise risk mitigation actions.</t>
         </is>
       </c>
-      <c r="AG101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH101" t="inlineStr">
+      <c r="AH101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI101" t="inlineStr">
         <is>
           <t>risk assessment, probability analysis, threat modelling, impact evaluation, risk matrices</t>
         </is>
-      </c>
-      <c r="AI101" t="b">
-        <v>0</v>
       </c>
       <c r="AJ101" t="b">
         <v>0</v>
@@ -16334,21 +16290,21 @@
         <v>0</v>
       </c>
       <c r="AE102" t="inlineStr"/>
-      <c r="AF102" t="inlineStr">
+      <c r="AF102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="inlineStr">
         <is>
           <t>Identifies network and data‑source security equipment using system diagrams and technical documentation.</t>
         </is>
       </c>
-      <c r="AG102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
+      <c r="AH102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
         <is>
           <t>cyber security, network security, asset inventories, IDS, firewalls</t>
         </is>
-      </c>
-      <c r="AI102" t="b">
-        <v>0</v>
       </c>
       <c r="AJ102" t="b">
         <v>0</v>
@@ -16482,13 +16438,9 @@
         </is>
       </c>
       <c r="Z103" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>Data Log Ingestion</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA103" t="inlineStr"/>
       <c r="AB103" t="b">
         <v>0</v>
       </c>
@@ -16497,21 +16449,21 @@
         <v>0</v>
       </c>
       <c r="AE103" t="inlineStr"/>
-      <c r="AF103" t="inlineStr">
+      <c r="AF103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="inlineStr">
         <is>
           <t>Imports security logs into analytics platforms to support monitoring and threat detection.</t>
         </is>
       </c>
-      <c r="AG103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
+      <c r="AH103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
         <is>
           <t>log aggregation, SIEM, data ingestion, security analytics, ELK stack</t>
         </is>
-      </c>
-      <c r="AI103" t="b">
-        <v>0</v>
       </c>
       <c r="AJ103" t="b">
         <v>0</v>
@@ -16656,21 +16608,21 @@
         <v>0</v>
       </c>
       <c r="AE104" t="inlineStr"/>
-      <c r="AF104" t="inlineStr">
+      <c r="AF104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="inlineStr">
         <is>
           <t>Communicates threat findings through structured discussions and reviews with relevant personnel.</t>
         </is>
       </c>
-      <c r="AG104" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH104" t="inlineStr">
+      <c r="AH104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
         <is>
           <t>stakeholder engagement, threat intelligence, risk reporting, data briefings, cyber security communication</t>
         </is>
-      </c>
-      <c r="AI104" t="b">
-        <v>0</v>
       </c>
       <c r="AJ104" t="b">
         <v>0</v>
@@ -16815,21 +16767,21 @@
         <v>0</v>
       </c>
       <c r="AE105" t="inlineStr"/>
-      <c r="AF105" t="inlineStr">
+      <c r="AF105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="inlineStr">
         <is>
           <t>Collects and structures alerts, logs and event data in accordance with organisational data policies.</t>
         </is>
       </c>
-      <c r="AG105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH105" t="inlineStr">
+      <c r="AH105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr">
         <is>
           <t>threat intelligence, log analysis, SIEM, incident response, security monitoring</t>
         </is>
-      </c>
-      <c r="AI105" t="b">
-        <v>0</v>
       </c>
       <c r="AJ105" t="b">
         <v>0</v>
@@ -16957,9 +16909,13 @@
         </is>
       </c>
       <c r="Z106" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA106" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>Problem solving</t>
+        </is>
+      </c>
       <c r="AB106" t="b">
         <v>0</v>
       </c>
@@ -16968,21 +16924,21 @@
         <v>0</v>
       </c>
       <c r="AE106" t="inlineStr"/>
-      <c r="AF106" t="inlineStr">
+      <c r="AF106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="inlineStr">
         <is>
           <t>Monitors operational data to detect contextual anomalies and resolves deviations in a timely manner.</t>
         </is>
       </c>
-      <c r="AG106" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
+      <c r="AH106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
         <is>
           <t>outlier analysis, root‑cause analysis, statistical process control, monitoring and diagnostics</t>
         </is>
-      </c>
-      <c r="AI106" t="b">
-        <v>0</v>
       </c>
       <c r="AJ106" t="b">
         <v>0</v>
@@ -17101,7 +17057,7 @@
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>0.95</v>
+        <v>0.9528571428571428</v>
       </c>
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr">
@@ -17121,21 +17077,21 @@
         <v>0</v>
       </c>
       <c r="AE107" t="inlineStr"/>
-      <c r="AF107" t="inlineStr">
+      <c r="AF107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="inlineStr">
         <is>
           <t>Implements enhanced protection plan requirements and asset management processes to safeguard assets.</t>
         </is>
       </c>
-      <c r="AG107" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH107" t="inlineStr">
+      <c r="AH107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr">
         <is>
           <t>asset tracking, risk mitigation, protection plans, maintenance scheduling, capital budgeting</t>
         </is>
-      </c>
-      <c r="AI107" t="b">
-        <v>0</v>
       </c>
       <c r="AJ107" t="b">
         <v>0</v>
@@ -17274,21 +17230,21 @@
         <v>0</v>
       </c>
       <c r="AE108" t="inlineStr"/>
-      <c r="AF108" t="inlineStr">
+      <c r="AF108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="inlineStr">
         <is>
           <t>Conducts critical infrastructure research to support protection planning and documentation requirements.</t>
         </is>
       </c>
-      <c r="AG108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
+      <c r="AH108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="inlineStr">
         <is>
           <t>infrastructure protection, risk assessment, threat modelling, resilience analysis, policy compliance</t>
         </is>
-      </c>
-      <c r="AI108" t="b">
-        <v>0</v>
       </c>
       <c r="AJ108" t="b">
         <v>0</v>
@@ -17427,21 +17383,21 @@
         <v>0</v>
       </c>
       <c r="AE109" t="inlineStr"/>
-      <c r="AF109" t="inlineStr">
+      <c r="AF109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="inlineStr">
         <is>
           <t>Executes scheduled data backups in line with organisational policies and procedures.</t>
         </is>
       </c>
-      <c r="AG109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH109" t="inlineStr">
+      <c r="AH109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI109" t="inlineStr">
         <is>
           <t>disaster recovery, backup software, data retention policies, storage replication, ICT compliance</t>
         </is>
-      </c>
-      <c r="AI109" t="b">
-        <v>0</v>
       </c>
       <c r="AJ109" t="b">
         <v>0</v>
@@ -17580,21 +17536,21 @@
         <v>0</v>
       </c>
       <c r="AE110" t="inlineStr"/>
-      <c r="AF110" t="inlineStr">
+      <c r="AF110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="inlineStr">
         <is>
           <t>Implements device security controls in accordance with protection plans and technical specifications.</t>
         </is>
       </c>
-      <c r="AG110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH110" t="inlineStr">
+      <c r="AH110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI110" t="inlineStr">
         <is>
           <t>endpoint protection, device hardening, security policies, encryption, mobile device management</t>
         </is>
-      </c>
-      <c r="AI110" t="b">
-        <v>0</v>
       </c>
       <c r="AJ110" t="b">
         <v>0</v>
@@ -17733,21 +17689,21 @@
         <v>0</v>
       </c>
       <c r="AE111" t="inlineStr"/>
-      <c r="AF111" t="inlineStr">
+      <c r="AF111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="inlineStr">
         <is>
           <t>Submits protection plans for review and incorporates stakeholder feedback to improve outcomes.</t>
         </is>
       </c>
-      <c r="AG111" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH111" t="inlineStr">
+      <c r="AH111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI111" t="inlineStr">
         <is>
           <t>stakeholder communication, feedback loops, response management, plan documentation, compliance reporting</t>
         </is>
-      </c>
-      <c r="AI111" t="b">
-        <v>0</v>
       </c>
       <c r="AJ111" t="b">
         <v>0</v>
@@ -17886,21 +17842,21 @@
         <v>0</v>
       </c>
       <c r="AE112" t="inlineStr"/>
-      <c r="AF112" t="inlineStr">
+      <c r="AF112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="inlineStr">
         <is>
           <t>Implements network segmentation to isolate security zones in line with approved protection plans.</t>
         </is>
       </c>
-      <c r="AG112" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
+      <c r="AH112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="inlineStr">
         <is>
           <t>VLANs, firewall policies, micro‑segmentation, zero‑trust architecture, network security zones</t>
         </is>
-      </c>
-      <c r="AI112" t="b">
-        <v>0</v>
       </c>
       <c r="AJ112" t="b">
         <v>0</v>
@@ -18032,28 +17988,32 @@
       </c>
       <c r="AA113" t="inlineStr"/>
       <c r="AB113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC113" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Foundation Skill describing planning and organising is already implicit in performance criteria and elements; does not represent a distinct workplace activity</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="inlineStr"/>
-      <c r="AF113" t="inlineStr">
+      <c r="AF113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="inlineStr">
         <is>
           <t>Develops staged operational plans and regularly reviews priorities and performance during execution.</t>
         </is>
       </c>
-      <c r="AG113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
+      <c r="AH113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="inlineStr">
         <is>
           <t>operational planning, performance monitoring, resource allocation, timeline management, Gantt charts</t>
         </is>
-      </c>
-      <c r="AI113" t="b">
-        <v>0</v>
       </c>
       <c r="AJ113" t="b">
         <v>0</v>
@@ -18176,12 +18136,12 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>keep:3, "Critical Infrastructure Protection Analysis":4</t>
+          <t>keep:1, "Critical Infrastructure Protection Analysis":6</t>
         </is>
       </c>
       <c r="Z114" t="b">
@@ -18196,21 +18156,21 @@
         <v>0</v>
       </c>
       <c r="AE114" t="inlineStr"/>
-      <c r="AF114" t="inlineStr">
+      <c r="AF114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="inlineStr">
         <is>
           <t>Evaluates current critical infrastructure protection plans to identify gaps and recommend improvements.</t>
         </is>
       </c>
-      <c r="AG114" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
+      <c r="AH114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI114" t="inlineStr">
         <is>
           <t>critical infrastructure, risk assessment, cyber security resilience, ISO 27001, vulnerability analysis</t>
         </is>
-      </c>
-      <c r="AI114" t="b">
-        <v>0</v>
       </c>
       <c r="AJ114" t="b">
         <v>0</v>
@@ -18329,7 +18289,7 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>0.95</v>
+        <v>0.9357142857142857</v>
       </c>
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr">
@@ -18349,21 +18309,21 @@
         <v>0</v>
       </c>
       <c r="AE115" t="inlineStr"/>
-      <c r="AF115" t="inlineStr">
+      <c r="AF115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="inlineStr">
         <is>
           <t>Develops and records critical infrastructure protection plans aligned with organisational policies and procedures.</t>
         </is>
       </c>
-      <c r="AG115" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH115" t="inlineStr">
+      <c r="AH115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI115" t="inlineStr">
         <is>
           <t>critical infrastructure, risk assessment, security policy compliance, business continuity planning, incident response frameworks</t>
         </is>
-      </c>
-      <c r="AI115" t="b">
-        <v>0</v>
       </c>
       <c r="AJ115" t="b">
         <v>0</v>
@@ -18482,12 +18442,12 @@
         <v>0</v>
       </c>
       <c r="W116" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X116" t="inlineStr"/>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Protection Plan Testing":1</t>
         </is>
       </c>
       <c r="Z116" t="b">
@@ -18502,21 +18462,21 @@
         <v>0</v>
       </c>
       <c r="AE116" t="inlineStr"/>
-      <c r="AF116" t="inlineStr">
+      <c r="AF116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="inlineStr">
         <is>
           <t>Conducts protection plan testing to validate safeguards in line with organisational requirements.</t>
         </is>
       </c>
-      <c r="AG116" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH116" t="inlineStr">
+      <c r="AH116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI116" t="inlineStr">
         <is>
           <t>cyber security, risk assessment, compliance testing, security policies, vulnerability testing</t>
         </is>
-      </c>
-      <c r="AI116" t="b">
-        <v>0</v>
       </c>
       <c r="AJ116" t="b">
         <v>0</v>
@@ -18655,21 +18615,21 @@
         <v>0</v>
       </c>
       <c r="AE117" t="inlineStr"/>
-      <c r="AF117" t="inlineStr">
+      <c r="AF117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="inlineStr">
         <is>
           <t>Collects, analyses and reports test results for decision‑making purposes.</t>
         </is>
       </c>
-      <c r="AG117" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
+      <c r="AH117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI117" t="inlineStr">
         <is>
           <t>data interpretation, performance metrics, compliance reporting, organisational standards, business intelligence</t>
         </is>
-      </c>
-      <c r="AI117" t="b">
-        <v>0</v>
       </c>
       <c r="AJ117" t="b">
         <v>0</v>
@@ -18792,12 +18752,12 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 4/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>keep:2, "Risk Assessment":4, "Risk Evaluation":1</t>
+          <t>keep:0, "Risk Assessment":6, "Risk Evaluation":1</t>
         </is>
       </c>
       <c r="Z118" t="b">
@@ -18812,21 +18772,21 @@
         <v>0</v>
       </c>
       <c r="AE118" t="inlineStr"/>
-      <c r="AF118" t="inlineStr">
+      <c r="AF118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="inlineStr">
         <is>
           <t>Evaluates protection, vulnerability and risk levels and recommends mitigations aligned with organisational needs.</t>
         </is>
       </c>
-      <c r="AG118" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
+      <c r="AH118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI118" t="inlineStr">
         <is>
           <t>vulnerability analysis, mitigation planning, risk matrices, security governance, ISO 27001 compliance</t>
         </is>
-      </c>
-      <c r="AI118" t="b">
-        <v>0</v>
       </c>
       <c r="AJ118" t="b">
         <v>0</v>
@@ -18965,21 +18925,21 @@
         <v>0</v>
       </c>
       <c r="AE119" t="inlineStr"/>
-      <c r="AF119" t="inlineStr">
+      <c r="AF119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="inlineStr">
         <is>
           <t>Installs and configures software updates in line with documented technical specifications.</t>
         </is>
       </c>
-      <c r="AG119" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH119" t="inlineStr">
+      <c r="AH119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI119" t="inlineStr">
         <is>
           <t>patch management, vulnerability remediation, update deployment, configuration management, WSUS</t>
         </is>
-      </c>
-      <c r="AI119" t="b">
-        <v>0</v>
       </c>
       <c r="AJ119" t="b">
         <v>0</v>
@@ -19118,21 +19078,21 @@
         <v>0</v>
       </c>
       <c r="AE120" t="inlineStr"/>
-      <c r="AF120" t="inlineStr">
+      <c r="AF120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="inlineStr">
         <is>
           <t>Produces workplace documentation using mandated structure, layout and organisational language standards.</t>
         </is>
       </c>
-      <c r="AG120" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
+      <c r="AH120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI120" t="inlineStr">
         <is>
           <t>technical writing, process documentation, standard operating procedures, document formatting</t>
         </is>
-      </c>
-      <c r="AI120" t="b">
-        <v>0</v>
       </c>
       <c r="AJ120" t="b">
         <v>0</v>
@@ -19261,16 +19221,16 @@
         <v>1</v>
       </c>
       <c r="W121" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/7: </t>
+          <t xml:space="preserve">consensus 6/7: </t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>keep:0, "Data Type Identification":7</t>
+          <t>keep:1, "Data Type Identification":6</t>
         </is>
       </c>
       <c r="Z121" t="b">
@@ -19285,21 +19245,21 @@
         <v>0</v>
       </c>
       <c r="AE121" t="inlineStr"/>
-      <c r="AF121" t="inlineStr">
+      <c r="AF121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="inlineStr">
         <is>
           <t>Identifies and categorises data types to inform security architecture requirements.</t>
         </is>
       </c>
-      <c r="AG121" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH121" t="inlineStr">
+      <c r="AH121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI121" t="inlineStr">
         <is>
           <t>information security, data inventories, classification schemes, confidentiality levels, security architecture</t>
         </is>
-      </c>
-      <c r="AI121" t="b">
-        <v>0</v>
       </c>
       <c r="AJ121" t="b">
         <v>0</v>
@@ -19444,21 +19404,21 @@
         <v>0</v>
       </c>
       <c r="AE122" t="inlineStr"/>
-      <c r="AF122" t="inlineStr">
+      <c r="AF122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="inlineStr">
         <is>
           <t>Submits required documentation promptly to obtain initial stakeholder feedback.</t>
         </is>
       </c>
-      <c r="AG122" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH122" t="inlineStr">
+      <c r="AH122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="inlineStr">
         <is>
           <t>documentation, stakeholder communication, feedback loops, record‑keeping, internal reporting</t>
         </is>
-      </c>
-      <c r="AI122" t="b">
-        <v>0</v>
       </c>
       <c r="AJ122" t="b">
         <v>0</v>
@@ -19599,21 +19559,21 @@
         <v>0</v>
       </c>
       <c r="AE123" t="inlineStr"/>
-      <c r="AF123" t="inlineStr">
+      <c r="AF123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="inlineStr">
         <is>
           <t>Researches and documents industry‑standard design methodologies to inform security architecture planning.</t>
         </is>
       </c>
-      <c r="AG123" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
+      <c r="AH123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI123" t="inlineStr">
         <is>
           <t>security architecture, design methodologies, industry standards, security frameworks, risk assessment</t>
         </is>
-      </c>
-      <c r="AI123" t="b">
-        <v>0</v>
       </c>
       <c r="AJ123" t="b">
         <v>0</v>
@@ -19751,7 +19711,7 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>keep:0, "Contextual Anomaly Identification/Security Anomaly Identification":7</t>
+          <t>keep:0, "Contextual Anomaly Identification":7</t>
         </is>
       </c>
       <c r="Z124" t="b">
@@ -19763,28 +19723,28 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Foundation Skill 'Problem solving' is already implicit in performance criteria and other skills; it does not represent a distinct activity in this unit</t>
+          <t>Foundation Skill 'Problem solving' is already implicit in performance criteria and other skills; it describes a generic capability rather than a distinct unit activity</t>
         </is>
       </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="inlineStr"/>
-      <c r="AF124" t="inlineStr">
+      <c r="AF124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="inlineStr">
         <is>
           <t>Applies contextual awareness to identify security anomalies and deviations from standard operating patterns.</t>
         </is>
       </c>
-      <c r="AG124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH124" t="inlineStr">
+      <c r="AH124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI124" t="inlineStr">
         <is>
           <t>anomaly detection, threat analysis, security monitoring, pattern recognition, situational awareness</t>
         </is>
-      </c>
-      <c r="AI124" t="b">
-        <v>0</v>
       </c>
       <c r="AJ124" t="b">
         <v>0</v>
@@ -19806,7 +19766,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Security Architecture Documentation</t>
+          <t>Security Requirements Documentation</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -19906,15 +19866,19 @@
         </is>
       </c>
       <c r="V125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W125" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="X125" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 6/7: </t>
+        </is>
+      </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>keep:4, "Security Findings Documentation":3</t>
+          <t>keep:1, "Security Requirements Documentation/Security Findings Documentation":6</t>
         </is>
       </c>
       <c r="Z125" t="b">
@@ -19929,21 +19893,21 @@
         <v>0</v>
       </c>
       <c r="AE125" t="inlineStr"/>
-      <c r="AF125" t="inlineStr">
+      <c r="AF125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="inlineStr">
         <is>
           <t>Documents and validates security architecture findings with relevant personnel.</t>
         </is>
       </c>
-      <c r="AG125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="inlineStr">
+      <c r="AH125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI125" t="inlineStr">
         <is>
           <t>security architecture, risk assessment, compliance frameworks, ISO 27001, threat modelling</t>
         </is>
-      </c>
-      <c r="AI125" t="b">
-        <v>0</v>
       </c>
       <c r="AJ125" t="b">
         <v>0</v>
@@ -20068,7 +20032,7 @@
         <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>0.9514285714285714</v>
+        <v>0.9528571428571428</v>
       </c>
       <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr">
@@ -20088,21 +20052,21 @@
         <v>0</v>
       </c>
       <c r="AE126" t="inlineStr"/>
-      <c r="AF126" t="inlineStr">
+      <c r="AF126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="inlineStr">
         <is>
           <t>Prepares and delivers documented security architecture presentations for stakeholder engagement.</t>
         </is>
       </c>
-      <c r="AG126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="inlineStr">
+      <c r="AH126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI126" t="inlineStr">
         <is>
           <t>information security, enterprise architecture, risk assessment, security frameworks, technical presentations</t>
         </is>
-      </c>
-      <c r="AI126" t="b">
-        <v>0</v>
       </c>
       <c r="AJ126" t="b">
         <v>0</v>
@@ -20227,7 +20191,7 @@
         <v>0</v>
       </c>
       <c r="W127" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X127" t="inlineStr"/>
       <c r="Y127" t="inlineStr">
@@ -20247,21 +20211,21 @@
         <v>0</v>
       </c>
       <c r="AE127" t="inlineStr"/>
-      <c r="AF127" t="inlineStr">
+      <c r="AF127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="inlineStr">
         <is>
           <t>Validates security designs using industry‑recognised methodologies.</t>
         </is>
       </c>
-      <c r="AG127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
+      <c r="AH127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI127" t="inlineStr">
         <is>
           <t>security architecture, threat modelling, NIST framework, ISO 27001, risk assessment</t>
         </is>
-      </c>
-      <c r="AI127" t="b">
-        <v>0</v>
       </c>
       <c r="AJ127" t="b">
         <v>0</v>
@@ -20410,21 +20374,21 @@
         <v>0</v>
       </c>
       <c r="AE128" t="inlineStr"/>
-      <c r="AF128" t="inlineStr">
+      <c r="AF128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="inlineStr">
         <is>
           <t>Assesses assets to determine required security levels, perimeters, features and protection modes.</t>
         </is>
       </c>
-      <c r="AG128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="inlineStr">
+      <c r="AH128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI128" t="inlineStr">
         <is>
           <t>risk assessment, access control, security architecture, perimeter security, security policy</t>
         </is>
-      </c>
-      <c r="AI128" t="b">
-        <v>0</v>
       </c>
       <c r="AJ128" t="b">
         <v>0</v>
@@ -20570,28 +20534,28 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>FS describes work style (planning and organising) implicit in PCs, not a distinct skill</t>
+          <t>Foundation Skill describing planning process is already covered by PC 2.1/2.2 and element Design security architecture; not a distinct standalone skill</t>
         </is>
       </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="inlineStr"/>
-      <c r="AF129" t="inlineStr">
+      <c r="AF129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="inlineStr">
         <is>
           <t>Develops staged operational plans for security initiatives and reviews progress during delivery.</t>
         </is>
       </c>
-      <c r="AG129" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH129" t="inlineStr">
+      <c r="AH129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI129" t="inlineStr">
         <is>
           <t>cyber security governance, risk assessment, phased implementation, performance monitoring, project scheduling tools</t>
         </is>
-      </c>
-      <c r="AI129" t="b">
-        <v>0</v>
       </c>
       <c r="AJ129" t="b">
         <v>0</v>
@@ -20712,7 +20676,7 @@
         <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>0.95</v>
+        <v>0.9514285714285714</v>
       </c>
       <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr">
@@ -20732,21 +20696,21 @@
         <v>0</v>
       </c>
       <c r="AE130" t="inlineStr"/>
-      <c r="AF130" t="inlineStr">
+      <c r="AF130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="inlineStr">
         <is>
           <t>Analyses organisational operations and infrastructure to identify specific security requirements.</t>
         </is>
       </c>
-      <c r="AG130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
+      <c r="AH130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI130" t="inlineStr">
         <is>
           <t>risk assessment, threat modelling, security architecture, compliance standards, vulnerability analysis</t>
         </is>
-      </c>
-      <c r="AI130" t="b">
-        <v>0</v>
       </c>
       <c r="AJ130" t="b">
         <v>0</v>
@@ -20895,21 +20859,21 @@
         <v>0</v>
       </c>
       <c r="AE131" t="inlineStr"/>
-      <c r="AF131" t="inlineStr">
+      <c r="AF131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="inlineStr">
         <is>
           <t>Designs and documents security solutions aligned with organisational standards and requirements.</t>
         </is>
       </c>
-      <c r="AG131" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
+      <c r="AH131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI131" t="inlineStr">
         <is>
           <t>cyber security architecture, risk assessment, security compliance, solution documentation, threat modelling</t>
         </is>
-      </c>
-      <c r="AI131" t="b">
-        <v>0</v>
       </c>
       <c r="AJ131" t="b">
         <v>0</v>
@@ -21047,13 +21011,9 @@
         </is>
       </c>
       <c r="Z132" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>Security Architecture Documentation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA132" t="inlineStr"/>
       <c r="AB132" t="b">
         <v>0</v>
       </c>
@@ -21062,21 +21022,21 @@
         <v>0</v>
       </c>
       <c r="AE132" t="inlineStr"/>
-      <c r="AF132" t="inlineStr">
+      <c r="AF132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="inlineStr">
         <is>
           <t>Produces detailed technical documentation outlining findings and proposed solutions.</t>
         </is>
       </c>
-      <c r="AG132" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
+      <c r="AH132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI132" t="inlineStr">
         <is>
           <t>technical writing, documentation standards, reporting and analysis, knowledge management</t>
         </is>
-      </c>
-      <c r="AI132" t="b">
-        <v>0</v>
       </c>
       <c r="AJ132" t="b">
         <v>0</v>
@@ -21098,7 +21058,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Technical Documentation Reading</t>
+          <t>Technical Specification Reading</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -21198,19 +21158,15 @@
         </is>
       </c>
       <c r="V133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W133" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/7: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>keep:2, "Technical Documentation Reading":5</t>
+          <t>keep:5, "Technical Documentation Reading":2</t>
         </is>
       </c>
       <c r="Z133" t="b">
@@ -21225,21 +21181,21 @@
         <v>0</v>
       </c>
       <c r="AE133" t="inlineStr"/>
-      <c r="AF133" t="inlineStr">
+      <c r="AF133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="inlineStr">
         <is>
           <t>Reviews technical, manufacturer and organisational documentation to confirm job requirements prior to work commencement.</t>
         </is>
       </c>
-      <c r="AG133" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="inlineStr">
+      <c r="AH133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="inlineStr">
         <is>
           <t>technical documentation, specification standards, manufacturer manuals, job requirement analysis, engineering drawings</t>
         </is>
-      </c>
-      <c r="AI133" t="b">
-        <v>0</v>
       </c>
       <c r="AJ133" t="b">
         <v>0</v>
@@ -21381,12 +21337,12 @@
         <v>0</v>
       </c>
       <c r="W134" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>keep:7</t>
+          <t>keep:6, "Strategic Decision Making":1</t>
         </is>
       </c>
       <c r="Z134" t="b">
@@ -21405,21 +21361,21 @@
         <v>0</v>
       </c>
       <c r="AE134" t="inlineStr"/>
-      <c r="AF134" t="inlineStr">
+      <c r="AF134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="inlineStr">
         <is>
           <t>Makes independent strategic decisions to align actions with organisational objectives and improve performance.</t>
         </is>
       </c>
-      <c r="AG134" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH134" t="inlineStr">
+      <c r="AH134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI134" t="inlineStr">
         <is>
           <t>autonomy, strategic decision‑making, self‑management, leadership, organisational performance</t>
         </is>
-      </c>
-      <c r="AI134" t="b">
-        <v>0</v>
       </c>
       <c r="AJ134" t="b">
         <v>0</v>
@@ -21557,12 +21513,12 @@
         <v>0</v>
       </c>
       <c r="W135" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>keep:6, "Forensic Evidence Procedure Development":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z135" t="b">
@@ -21577,21 +21533,21 @@
         <v>0</v>
       </c>
       <c r="AE135" t="inlineStr"/>
-      <c r="AF135" t="inlineStr">
+      <c r="AF135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="inlineStr">
         <is>
           <t>Designs and implements forensic evidence collection processes to preserve data during incident response.</t>
         </is>
       </c>
-      <c r="AG135" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
+      <c r="AH135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="inlineStr">
         <is>
           <t>chain of custody, evidence preservation, incident response, digital forensics tools, crime scene documentation</t>
         </is>
-      </c>
-      <c r="AI135" t="b">
-        <v>0</v>
       </c>
       <c r="AJ135" t="b">
         <v>0</v>
@@ -21730,7 +21686,7 @@
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>keep:5, "Incident Report Preparation":2</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z136" t="b">
@@ -21745,21 +21701,21 @@
         <v>0</v>
       </c>
       <c r="AE136" t="inlineStr"/>
-      <c r="AF136" t="inlineStr">
+      <c r="AF136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="inlineStr">
         <is>
           <t>Prepares detailed incident reports documenting response actions against task requirements.</t>
         </is>
       </c>
-      <c r="AG136" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH136" t="inlineStr">
+      <c r="AH136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI136" t="inlineStr">
         <is>
           <t>security incident response, incident reporting, ITIL, SIEM, compliance documentation</t>
         </is>
-      </c>
-      <c r="AI136" t="b">
-        <v>0</v>
       </c>
       <c r="AJ136" t="b">
         <v>0</v>
@@ -21921,21 +21877,21 @@
         <v>0</v>
       </c>
       <c r="AE137" t="inlineStr"/>
-      <c r="AF137" t="inlineStr">
+      <c r="AF137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="inlineStr">
         <is>
           <t>Evaluates incident response plans for effectiveness across hybrid operating environments.</t>
         </is>
       </c>
-      <c r="AG137" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
+      <c r="AH137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="inlineStr">
         <is>
           <t>security operations, post‑incident analysis, efficiency metrics, response plan documentation, SOC tools</t>
         </is>
-      </c>
-      <c r="AI137" t="b">
-        <v>0</v>
       </c>
       <c r="AJ137" t="b">
         <v>0</v>
@@ -22093,21 +22049,21 @@
         <v>0</v>
       </c>
       <c r="AE138" t="inlineStr"/>
-      <c r="AF138" t="inlineStr">
+      <c r="AF138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="inlineStr">
         <is>
           <t>Develops and records incident response plans aligned with organisational requirements.</t>
         </is>
       </c>
-      <c r="AG138" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="inlineStr">
+      <c r="AH138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="inlineStr">
         <is>
           <t>cyber security, incident handling, NIST framework, playbook development, risk management</t>
         </is>
-      </c>
-      <c r="AI138" t="b">
-        <v>0</v>
       </c>
       <c r="AJ138" t="b">
         <v>0</v>
@@ -22261,21 +22217,21 @@
         <v>0</v>
       </c>
       <c r="AE139" t="inlineStr"/>
-      <c r="AF139" t="inlineStr">
+      <c r="AF139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="inlineStr">
         <is>
           <t>Documents incident response team roles and services to support coordinated response.</t>
         </is>
       </c>
-      <c r="AG139" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
+      <c r="AH139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI139" t="inlineStr">
         <is>
           <t>incident response, service documentation, team coordination, organisational compliance, ticketing systems</t>
         </is>
-      </c>
-      <c r="AI139" t="b">
-        <v>0</v>
       </c>
       <c r="AJ139" t="b">
         <v>0</v>
@@ -22413,16 +22369,16 @@
         <v>1</v>
       </c>
       <c r="W140" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 6/7: </t>
+          <t xml:space="preserve">consensus 7/7: </t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Exercise Design/Incident Response Red‑Team Design":6, "Incident Response Red Teaming":1</t>
+          <t>keep:0, "Incident Response Exercise Design/Incident Response Training Design":7</t>
         </is>
       </c>
       <c r="Z140" t="b">
@@ -22437,21 +22393,21 @@
         <v>0</v>
       </c>
       <c r="AE140" t="inlineStr"/>
-      <c r="AF140" t="inlineStr">
+      <c r="AF140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="inlineStr">
         <is>
           <t>Designs and conducts red‑team exercises and incident response simulations, including staffing and training plans.</t>
         </is>
       </c>
-      <c r="AG140" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH140" t="inlineStr">
+      <c r="AH140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI140" t="inlineStr">
         <is>
           <t>adversary simulation, incident response planning, threat modelling, security training programmes, MITRE ATT&amp;CK framework</t>
         </is>
-      </c>
-      <c r="AI140" t="b">
-        <v>0</v>
       </c>
       <c r="AJ140" t="b">
         <v>0</v>
@@ -22589,12 +22545,12 @@
         <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>keep:6, "Communication Effectiveness Assessment":1</t>
+          <t>keep:7</t>
         </is>
       </c>
       <c r="Z141" t="b">
@@ -22609,21 +22565,21 @@
         <v>0</v>
       </c>
       <c r="AE141" t="inlineStr"/>
-      <c r="AF141" t="inlineStr">
+      <c r="AF141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="inlineStr">
         <is>
           <t>Evaluates the effectiveness of incident response communications across internal and external stakeholders.</t>
         </is>
       </c>
-      <c r="AG141" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH141" t="inlineStr">
+      <c r="AH141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI141" t="inlineStr">
         <is>
           <t>incident response, stakeholder communication, internal coordination, external liaison, communication effectiveness</t>
         </is>
-      </c>
-      <c r="AI141" t="b">
-        <v>0</v>
       </c>
       <c r="AJ141" t="b">
         <v>0</v>
@@ -22765,7 +22721,7 @@
         <v>1</v>
       </c>
       <c r="W142" t="n">
-        <v>0.9028571428571429</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
@@ -22774,7 +22730,7 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>keep:0, "Technical Data Interpretation/Data Interpretation":7</t>
+          <t>keep:0, "Technical Data Interpretation":7</t>
         </is>
       </c>
       <c r="Z142" t="b">
@@ -22786,28 +22742,32 @@
         </is>
       </c>
       <c r="AB142" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC142" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Foundation Skill implicit in PCs; interpreting and documenting data is already required in multiple performance criteria (e.g., evidence collection, incident analysis) and does not add a distinct capability</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="inlineStr"/>
-      <c r="AF142" t="inlineStr">
+      <c r="AF142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="inlineStr">
         <is>
           <t>Interprets and documents numerical and technical system data to support risk assessment.</t>
         </is>
       </c>
-      <c r="AG142" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH142" t="inlineStr">
+      <c r="AH142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI142" t="inlineStr">
         <is>
           <t>quantitative analysis, technical data interpretation, risk assessment, system modelling, data documentation</t>
         </is>
-      </c>
-      <c r="AI142" t="b">
-        <v>0</v>
       </c>
       <c r="AJ142" t="b">
         <v>0</v>
@@ -22969,21 +22929,21 @@
         <v>0</v>
       </c>
       <c r="AE143" t="inlineStr"/>
-      <c r="AF143" t="inlineStr">
+      <c r="AF143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="inlineStr">
         <is>
           <t>Executes incident response actions in accordance with approved incident response plans.</t>
         </is>
       </c>
-      <c r="AG143" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH143" t="inlineStr">
+      <c r="AH143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI143" t="inlineStr">
         <is>
           <t>incident response, security operations centres, SIEM, playbook execution, forensic analysis</t>
         </is>
-      </c>
-      <c r="AI143" t="b">
-        <v>0</v>
       </c>
       <c r="AJ143" t="b">
         <v>0</v>
@@ -23145,21 +23105,21 @@
         <v>0</v>
       </c>
       <c r="AE144" t="inlineStr"/>
-      <c r="AF144" t="inlineStr">
+      <c r="AF144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="inlineStr">
         <is>
           <t>Develops and documents incident management policies aligned with organisational specifications.</t>
         </is>
       </c>
-      <c r="AG144" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH144" t="inlineStr">
+      <c r="AH144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI144" t="inlineStr">
         <is>
           <t>incident management, risk assessment, governance, compliance, ISO 27001</t>
         </is>
-      </c>
-      <c r="AI144" t="b">
-        <v>0</v>
       </c>
       <c r="AJ144" t="b">
         <v>0</v>
@@ -23318,28 +23278,28 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Foundation Skill implicit in performance criteria; interpreting and documenting technical data is already required in multiple PCs (e.g., evidence collection, incident analysis) and does not add a distinct standalone capability</t>
+          <t>Foundation Skill implicit in PCs; interpreting data is embedded in multiple performance criteria and not a distinct standalone skill</t>
         </is>
       </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
       <c r="AE145" t="inlineStr"/>
-      <c r="AF145" t="inlineStr">
+      <c r="AF145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="inlineStr">
         <is>
           <t>Analyses and records numerical system data to inform technical decision‑making.</t>
         </is>
       </c>
-      <c r="AG145" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH145" t="inlineStr">
+      <c r="AH145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI145" t="inlineStr">
         <is>
           <t>quantitative analysis, technical system data, measurement instrumentation, data documentation, engineering diagnostics</t>
         </is>
-      </c>
-      <c r="AI145" t="b">
-        <v>0</v>
       </c>
       <c r="AJ145" t="b">
         <v>0</v>
@@ -23490,21 +23450,21 @@
         <v>0</v>
       </c>
       <c r="AE146" t="inlineStr"/>
-      <c r="AF146" t="inlineStr">
+      <c r="AF146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="inlineStr">
         <is>
           <t>Assesses system impacts on business continuity to identify risks and mitigation strategies.</t>
         </is>
       </c>
-      <c r="AG146" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH146" t="inlineStr">
+      <c r="AH146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI146" t="inlineStr">
         <is>
           <t>business continuity, risk assessment, impact analysis, disaster recovery, resilience planning</t>
         </is>
-      </c>
-      <c r="AI146" t="b">
-        <v>0</v>
       </c>
       <c r="AJ146" t="b">
         <v>0</v>
@@ -23655,21 +23615,21 @@
         <v>0</v>
       </c>
       <c r="AE147" t="inlineStr"/>
-      <c r="AF147" t="inlineStr">
+      <c r="AF147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="inlineStr">
         <is>
           <t>Designs and implements compliance strategies to align organisational processes with regulatory requirements.</t>
         </is>
       </c>
-      <c r="AG147" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH147" t="inlineStr">
+      <c r="AH147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI147" t="inlineStr">
         <is>
           <t>regulatory compliance, policy enforcement, risk management, governance, audit</t>
         </is>
-      </c>
-      <c r="AI147" t="b">
-        <v>0</v>
       </c>
       <c r="AJ147" t="b">
         <v>0</v>
@@ -23824,21 +23784,21 @@
         <v>0</v>
       </c>
       <c r="AE148" t="inlineStr"/>
-      <c r="AF148" t="inlineStr">
+      <c r="AF148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="inlineStr">
         <is>
           <t>Develops contingency plans by identifying threats and defining response actions.</t>
         </is>
       </c>
-      <c r="AG148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH148" t="inlineStr">
+      <c r="AH148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI148" t="inlineStr">
         <is>
           <t>risk assessment, business continuity, threat identification, mitigation strategies, scenario analysis</t>
         </is>
-      </c>
-      <c r="AI148" t="b">
-        <v>0</v>
       </c>
       <c r="AJ148" t="b">
         <v>0</v>
@@ -23989,21 +23949,21 @@
         <v>0</v>
       </c>
       <c r="AE149" t="inlineStr"/>
-      <c r="AF149" t="inlineStr">
+      <c r="AF149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="inlineStr">
         <is>
           <t>Evaluates prevention and recovery options for compliance and cost effectiveness.</t>
         </is>
       </c>
-      <c r="AG149" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH149" t="inlineStr">
+      <c r="AH149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI149" t="inlineStr">
         <is>
           <t>cost‑benefit analysis, budgeting, risk assessment, business case evaluation, financial modelling</t>
         </is>
-      </c>
-      <c r="AI149" t="b">
-        <v>0</v>
       </c>
       <c r="AJ149" t="b">
         <v>0</v>
@@ -24154,21 +24114,21 @@
         <v>0</v>
       </c>
       <c r="AE150" t="inlineStr"/>
-      <c r="AF150" t="inlineStr">
+      <c r="AF150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="inlineStr">
         <is>
           <t>Develops comprehensive disaster recovery plans detailing procedures, resources and recovery timeframes.</t>
         </is>
       </c>
-      <c r="AG150" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH150" t="inlineStr">
+      <c r="AH150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI150" t="inlineStr">
         <is>
           <t>business continuity, backup and restore, recovery time objectives, risk assessment, disaster recovery testing</t>
         </is>
-      </c>
-      <c r="AI150" t="b">
-        <v>0</v>
       </c>
       <c r="AJ150" t="b">
         <v>0</v>
@@ -24319,21 +24279,21 @@
         <v>0</v>
       </c>
       <c r="AE151" t="inlineStr"/>
-      <c r="AF151" t="inlineStr">
+      <c r="AF151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="inlineStr">
         <is>
           <t>Reviews operational procedures against industry benchmarks to verify risk controls.</t>
         </is>
       </c>
-      <c r="AG151" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH151" t="inlineStr">
+      <c r="AH151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI151" t="inlineStr">
         <is>
           <t>compliance, risk management, standard operating procedures, regulatory guidance, audit</t>
         </is>
-      </c>
-      <c r="AI151" t="b">
-        <v>0</v>
       </c>
       <c r="AJ151" t="b">
         <v>0</v>
@@ -24481,7 +24441,7 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>Risk Analysis</t>
+          <t>Numeracy</t>
         </is>
       </c>
       <c r="AB152" t="b">
@@ -24492,21 +24452,21 @@
         <v>0</v>
       </c>
       <c r="AE152" t="inlineStr"/>
-      <c r="AF152" t="inlineStr">
+      <c r="AF152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="inlineStr">
         <is>
           <t>Analyses and documents numerical, financial and technical data to support operational decisions.</t>
         </is>
       </c>
-      <c r="AG152" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH152" t="inlineStr">
+      <c r="AH152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI152" t="inlineStr">
         <is>
           <t>quantitative analysis, financial modelling, technical data interpretation, statistical methods, data reporting</t>
         </is>
-      </c>
-      <c r="AI152" t="b">
-        <v>0</v>
       </c>
       <c r="AJ152" t="b">
         <v>0</v>
@@ -24657,21 +24617,21 @@
         <v>0</v>
       </c>
       <c r="AE153" t="inlineStr"/>
-      <c r="AF153" t="inlineStr">
+      <c r="AF153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="inlineStr">
         <is>
           <t>Designs and implements prevention and recovery strategies to strengthen system resilience.</t>
         </is>
       </c>
-      <c r="AG153" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH153" t="inlineStr">
+      <c r="AH153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI153" t="inlineStr">
         <is>
           <t>risk assessment, mitigation planning, contingency strategies, recovery planning, scenario analysis</t>
         </is>
-      </c>
-      <c r="AI153" t="b">
-        <v>0</v>
       </c>
       <c r="AJ153" t="b">
         <v>0</v>
@@ -24806,12 +24766,12 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.9416666666666665</v>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>keep:5, "Plan Improvement":2</t>
+          <t>keep:6, "Process Improvement":1</t>
         </is>
       </c>
       <c r="Z154" t="b">
@@ -24830,21 +24790,21 @@
         <v>0</v>
       </c>
       <c r="AE154" t="inlineStr"/>
-      <c r="AF154" t="inlineStr">
+      <c r="AF154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="inlineStr">
         <is>
           <t>Collects and analyses data, incorporates feedback and refines plans and processes.</t>
         </is>
       </c>
-      <c r="AG154" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH154" t="inlineStr">
+      <c r="AH154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI154" t="inlineStr">
         <is>
           <t>data analysis, feedback loops, process improvement, root‑cause analysis, continuous improvement</t>
         </is>
-      </c>
-      <c r="AI154" t="b">
-        <v>0</v>
       </c>
       <c r="AJ154" t="b">
         <v>0</v>
@@ -24995,21 +24955,21 @@
         <v>0</v>
       </c>
       <c r="AE155" t="inlineStr"/>
-      <c r="AF155" t="inlineStr">
+      <c r="AF155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="inlineStr">
         <is>
           <t>Conducts comprehensive risk assessments and develops disaster recovery and contingency solutions.</t>
         </is>
       </c>
-      <c r="AG155" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH155" t="inlineStr">
+      <c r="AH155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI155" t="inlineStr">
         <is>
           <t>risk assessment, disaster recovery, contingency planning, business continuity, threat modelling</t>
         </is>
-      </c>
-      <c r="AI155" t="b">
-        <v>0</v>
       </c>
       <c r="AJ155" t="b">
         <v>0</v>
@@ -25160,21 +25120,21 @@
         <v>0</v>
       </c>
       <c r="AE156" t="inlineStr"/>
-      <c r="AF156" t="inlineStr">
+      <c r="AF156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="inlineStr">
         <is>
           <t>Engages stakeholders through timely document submission, feedback collection and response.</t>
         </is>
       </c>
-      <c r="AG156" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH156" t="inlineStr">
+      <c r="AH156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI156" t="inlineStr">
         <is>
           <t>stakeholder engagement, feedback loops, document management, communication protocols, collaboration tools</t>
         </is>
-      </c>
-      <c r="AI156" t="b">
-        <v>0</v>
       </c>
       <c r="AJ156" t="b">
         <v>0</v>
@@ -25196,7 +25156,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Strategy Prioritisation</t>
+          <t>Strategic Planning</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -25302,19 +25262,15 @@
         </is>
       </c>
       <c r="V157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/7: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>keep:2, "Strategy Prioritisation":5</t>
+          <t>keep:6, "Strategy Prioritisation":1</t>
         </is>
       </c>
       <c r="Z157" t="b">
@@ -25329,21 +25285,21 @@
         <v>0</v>
       </c>
       <c r="AE157" t="inlineStr"/>
-      <c r="AF157" t="inlineStr">
+      <c r="AF157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="inlineStr">
         <is>
           <t>Develops and aligns hybrid work priorities and outcomes through structured strategic planning.</t>
         </is>
       </c>
-      <c r="AG157" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH157" t="inlineStr">
+      <c r="AH157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI157" t="inlineStr">
         <is>
           <t>priority alignment, outcome mapping, roadmap development, performance metrics, scenario analysis</t>
         </is>
-      </c>
-      <c r="AI157" t="b">
-        <v>0</v>
       </c>
       <c r="AJ157" t="b">
         <v>0</v>
@@ -25483,9 +25439,13 @@
         </is>
       </c>
       <c r="Z158" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA158" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>Teamwork</t>
+        </is>
+      </c>
       <c r="AB158" t="b">
         <v>0</v>
       </c>
@@ -25494,21 +25454,21 @@
         <v>0</v>
       </c>
       <c r="AE158" t="inlineStr"/>
-      <c r="AF158" t="inlineStr">
+      <c r="AF158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="inlineStr">
         <is>
           <t>Collaborates with team members using communication tools and strategies to maintain effective working relationships.</t>
         </is>
       </c>
-      <c r="AG158" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH158" t="inlineStr">
+      <c r="AH158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI158" t="inlineStr">
         <is>
           <t>communication tools, relationship building, stakeholder engagement, collaboration platforms, interpersonal communication</t>
         </is>
-      </c>
-      <c r="AI158" t="b">
-        <v>0</v>
       </c>
       <c r="AJ158" t="b">
         <v>0</v>
@@ -25659,21 +25619,21 @@
         <v>0</v>
       </c>
       <c r="AE159" t="inlineStr"/>
-      <c r="AF159" t="inlineStr">
+      <c r="AF159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="inlineStr">
         <is>
           <t>Prepares evaluation and strategy documents outlining findings and recommendations for stakeholders.</t>
         </is>
       </c>
-      <c r="AG159" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH159" t="inlineStr">
+      <c r="AH159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI159" t="inlineStr">
         <is>
           <t>specification drafting, process documentation, evaluation reporting, strategic articulation, document control</t>
         </is>
-      </c>
-      <c r="AI159" t="b">
-        <v>0</v>
       </c>
       <c r="AJ159" t="b">
         <v>0</v>
@@ -25824,21 +25784,21 @@
         <v>0</v>
       </c>
       <c r="AE160" t="inlineStr"/>
-      <c r="AF160" t="inlineStr">
+      <c r="AF160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="inlineStr">
         <is>
           <t>Assesses system vulnerabilities through structured threat identification and analysis to support mitigation planning.</t>
         </is>
       </c>
-      <c r="AG160" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH160" t="inlineStr">
+      <c r="AH160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI160" t="inlineStr">
         <is>
           <t>risk analysis, vulnerability assessment, threat modelling, cyber security, intelligence gathering</t>
         </is>
-      </c>
-      <c r="AI160" t="b">
-        <v>0</v>
       </c>
       <c r="AJ160" t="b">
         <v>0</v>
@@ -25887,7 +25847,7 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -25940,23 +25900,53 @@
 No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr"/>
-      <c r="V161" t="inlineStr"/>
-      <c r="W161" t="inlineStr"/>
-      <c r="X161" t="inlineStr"/>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Response Substantiation</t>
+        </is>
+      </c>
+      <c r="V161" t="b">
+        <v>0</v>
+      </c>
+      <c r="W161" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>added from uncovered PCs</t>
+        </is>
+      </c>
       <c r="Y161" t="inlineStr"/>
-      <c r="Z161" t="inlineStr"/>
+      <c r="Z161" t="b">
+        <v>0</v>
+      </c>
       <c r="AA161" t="inlineStr"/>
-      <c r="AB161" t="inlineStr"/>
+      <c r="AB161" t="b">
+        <v>0</v>
+      </c>
       <c r="AC161" t="inlineStr"/>
-      <c r="AD161" t="inlineStr"/>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
       <c r="AE161" t="inlineStr"/>
-      <c r="AF161" t="inlineStr"/>
-      <c r="AG161" t="inlineStr"/>
-      <c r="AH161" t="inlineStr"/>
-      <c r="AI161" t="inlineStr"/>
+      <c r="AF161" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>Provides clear, evidence‑based answers to stakeholder questions, supporting decisions with relevant data and reasoning.</t>
+        </is>
+      </c>
+      <c r="AH161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>evidence based answers, stakeholder queries, substantiated responses, data support, reasoning justification</t>
+        </is>
+      </c>
       <c r="AJ161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -25983,7 +25973,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ASSIST</t>
+          <t>APPLY</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -25993,16 +25983,16 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Assists in confirming and documenting the types of information stored on each registered digital device.</t>
+          <t>Identify and confirm the types of information stored on each registered digital device within the organisation.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>device data inventory, information classification, data mapping, asset documentation, storage verification</t>
+          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
         </is>
       </c>
       <c r="J162" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -26055,23 +26045,53 @@
 No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr"/>
-      <c r="V162" t="inlineStr"/>
-      <c r="W162" t="inlineStr"/>
-      <c r="X162" t="inlineStr"/>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Device Data Identification</t>
+        </is>
+      </c>
+      <c r="V162" t="b">
+        <v>0</v>
+      </c>
+      <c r="W162" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>added from uncovered PCs</t>
+        </is>
+      </c>
       <c r="Y162" t="inlineStr"/>
-      <c r="Z162" t="inlineStr"/>
+      <c r="Z162" t="b">
+        <v>0</v>
+      </c>
       <c r="AA162" t="inlineStr"/>
-      <c r="AB162" t="inlineStr"/>
+      <c r="AB162" t="b">
+        <v>0</v>
+      </c>
       <c r="AC162" t="inlineStr"/>
-      <c r="AD162" t="inlineStr"/>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
       <c r="AE162" t="inlineStr"/>
-      <c r="AF162" t="inlineStr"/>
-      <c r="AG162" t="inlineStr"/>
-      <c r="AH162" t="inlineStr"/>
-      <c r="AI162" t="inlineStr"/>
+      <c r="AF162" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>Identify and confirm the types of information stored on each registered digital device within the organisation.</t>
+        </is>
+      </c>
+      <c r="AH162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>device data inventory, information classification, data mapping, asset documentation, digital records</t>
+        </is>
+      </c>
       <c r="AJ162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -26113,7 +26133,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>approval process, stakeholder engagement, documentation review, final sign‑off, authority confirmation</t>
+          <t>approval coordination, documentation confirmation, stakeholder sign‑off, final authorization, personnel engagement</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -26172,23 +26192,53 @@
 No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr"/>
-      <c r="V163" t="inlineStr"/>
-      <c r="W163" t="inlineStr"/>
-      <c r="X163" t="inlineStr"/>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Sign‑off Acquisition</t>
+        </is>
+      </c>
+      <c r="V163" t="b">
+        <v>0</v>
+      </c>
+      <c r="W163" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>added from uncovered PCs</t>
+        </is>
+      </c>
       <c r="Y163" t="inlineStr"/>
-      <c r="Z163" t="inlineStr"/>
+      <c r="Z163" t="b">
+        <v>0</v>
+      </c>
       <c r="AA163" t="inlineStr"/>
-      <c r="AB163" t="inlineStr"/>
+      <c r="AB163" t="b">
+        <v>0</v>
+      </c>
       <c r="AC163" t="inlineStr"/>
-      <c r="AD163" t="inlineStr"/>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
       <c r="AE163" t="inlineStr"/>
-      <c r="AF163" t="inlineStr"/>
-      <c r="AG163" t="inlineStr"/>
-      <c r="AH163" t="inlineStr"/>
-      <c r="AI163" t="inlineStr"/>
+      <c r="AF163" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>Secures final approval from designated personnel by coordinating, presenting, and confirming required documentation.</t>
+        </is>
+      </c>
+      <c r="AH163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>approval coordination, documentation confirmation, stakeholder sign‑off, final authorization, personnel engagement</t>
+        </is>
+      </c>
       <c r="AJ163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -26225,16 +26275,16 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation, considering relevant legislation and policies.</t>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>process analysis, transaction types, blockchain suitability, legislative compliance, organisational policies</t>
+          <t>process evaluation, transaction analysis, blockchain suitability, organisational assessment, compliance impact</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -26297,23 +26347,53 @@
 No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr"/>
-      <c r="V164" t="inlineStr"/>
-      <c r="W164" t="inlineStr"/>
-      <c r="X164" t="inlineStr"/>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Process Suitability Assessment</t>
+        </is>
+      </c>
+      <c r="V164" t="b">
+        <v>0</v>
+      </c>
+      <c r="W164" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>added from uncovered PCs</t>
+        </is>
+      </c>
       <c r="Y164" t="inlineStr"/>
-      <c r="Z164" t="inlineStr"/>
+      <c r="Z164" t="b">
+        <v>0</v>
+      </c>
       <c r="AA164" t="inlineStr"/>
-      <c r="AB164" t="inlineStr"/>
+      <c r="AB164" t="b">
+        <v>0</v>
+      </c>
       <c r="AC164" t="inlineStr"/>
-      <c r="AD164" t="inlineStr"/>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
       <c r="AE164" t="inlineStr"/>
-      <c r="AF164" t="inlineStr"/>
-      <c r="AG164" t="inlineStr"/>
-      <c r="AH164" t="inlineStr"/>
-      <c r="AI164" t="inlineStr"/>
+      <c r="AF164" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>Evaluates organisational processes and transaction types to determine their suitability for blockchain implementation.</t>
+        </is>
+      </c>
+      <c r="AH164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>process evaluation, transaction analysis, blockchain suitability, organisational assessment, compliance impact</t>
+        </is>
+      </c>
       <c r="AJ164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -26412,23 +26492,53 @@
 No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr"/>
-      <c r="V165" t="inlineStr"/>
-      <c r="W165" t="inlineStr"/>
-      <c r="X165" t="inlineStr"/>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Data Log Strategy Discussion</t>
+        </is>
+      </c>
+      <c r="V165" t="b">
+        <v>0</v>
+      </c>
+      <c r="W165" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>added from uncovered PCs</t>
+        </is>
+      </c>
       <c r="Y165" t="inlineStr"/>
-      <c r="Z165" t="inlineStr"/>
+      <c r="Z165" t="b">
+        <v>0</v>
+      </c>
       <c r="AA165" t="inlineStr"/>
-      <c r="AB165" t="inlineStr"/>
+      <c r="AB165" t="b">
+        <v>0</v>
+      </c>
       <c r="AC165" t="inlineStr"/>
-      <c r="AD165" t="inlineStr"/>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
       <c r="AE165" t="inlineStr"/>
-      <c r="AF165" t="inlineStr"/>
-      <c r="AG165" t="inlineStr"/>
-      <c r="AH165" t="inlineStr"/>
-      <c r="AI165" t="inlineStr"/>
+      <c r="AF165" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>Facilitates discussions with relevant personnel to confirm data log requirements and processing strategies.</t>
+        </is>
+      </c>
+      <c r="AH165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>data log requirements, processing strategy, personnel coordination, discussion facilitation, requirement confirmation</t>
+        </is>
+      </c>
       <c r="AJ165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -26465,7 +26575,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Evaluates gathered threat data results to confirm reliability and consistency before further processing.</t>
+          <t>The worker evaluates gathered threat data results to confirm their reliability and consistency before further processing.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -26527,23 +26637,53 @@
 No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr"/>
-      <c r="V166" t="inlineStr"/>
-      <c r="W166" t="inlineStr"/>
-      <c r="X166" t="inlineStr"/>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Reliability Consistency Analysis</t>
+        </is>
+      </c>
+      <c r="V166" t="b">
+        <v>0</v>
+      </c>
+      <c r="W166" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>added from uncovered PCs</t>
+        </is>
+      </c>
       <c r="Y166" t="inlineStr"/>
-      <c r="Z166" t="inlineStr"/>
+      <c r="Z166" t="b">
+        <v>0</v>
+      </c>
       <c r="AA166" t="inlineStr"/>
-      <c r="AB166" t="inlineStr"/>
+      <c r="AB166" t="b">
+        <v>0</v>
+      </c>
       <c r="AC166" t="inlineStr"/>
-      <c r="AD166" t="inlineStr"/>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
       <c r="AE166" t="inlineStr"/>
-      <c r="AF166" t="inlineStr"/>
-      <c r="AG166" t="inlineStr"/>
-      <c r="AH166" t="inlineStr"/>
-      <c r="AI166" t="inlineStr"/>
+      <c r="AF166" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>The worker evaluates gathered threat data results to confirm their reliability and consistency before further processing.</t>
+        </is>
+      </c>
+      <c r="AH166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>reliability assessment, consistency verification, data validation, threat analysis, result evaluation</t>
+        </is>
+      </c>
       <c r="AJ166" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -26649,23 +26789,53 @@
 No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr"/>
-      <c r="V167" t="inlineStr"/>
-      <c r="W167" t="inlineStr"/>
-      <c r="X167" t="inlineStr"/>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Plan Alignment Evaluation</t>
+        </is>
+      </c>
+      <c r="V167" t="b">
+        <v>0</v>
+      </c>
+      <c r="W167" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>added from uncovered PCs</t>
+        </is>
+      </c>
       <c r="Y167" t="inlineStr"/>
-      <c r="Z167" t="inlineStr"/>
+      <c r="Z167" t="b">
+        <v>0</v>
+      </c>
       <c r="AA167" t="inlineStr"/>
-      <c r="AB167" t="inlineStr"/>
+      <c r="AB167" t="b">
+        <v>0</v>
+      </c>
       <c r="AC167" t="inlineStr"/>
-      <c r="AD167" t="inlineStr"/>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
       <c r="AE167" t="inlineStr"/>
-      <c r="AF167" t="inlineStr"/>
-      <c r="AG167" t="inlineStr"/>
-      <c r="AH167" t="inlineStr"/>
-      <c r="AI167" t="inlineStr"/>
+      <c r="AF167" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>Evaluates how well the current protection plan meets organisational needs and regulatory requirements.</t>
+        </is>
+      </c>
+      <c r="AH167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>plan effectiveness, organisational alignment, regulatory compliance, critical assets, operational systems</t>
+        </is>
+      </c>
       <c r="AJ167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -26778,23 +26948,53 @@
 No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr"/>
-      <c r="V168" t="inlineStr"/>
-      <c r="W168" t="inlineStr"/>
-      <c r="X168" t="inlineStr"/>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Plan Alignment Documentation</t>
+        </is>
+      </c>
+      <c r="V168" t="b">
+        <v>0</v>
+      </c>
+      <c r="W168" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>added from uncovered PCs</t>
+        </is>
+      </c>
       <c r="Y168" t="inlineStr"/>
-      <c r="Z168" t="inlineStr"/>
+      <c r="Z168" t="b">
+        <v>0</v>
+      </c>
       <c r="AA168" t="inlineStr"/>
-      <c r="AB168" t="inlineStr"/>
+      <c r="AB168" t="b">
+        <v>0</v>
+      </c>
       <c r="AC168" t="inlineStr"/>
-      <c r="AD168" t="inlineStr"/>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
       <c r="AE168" t="inlineStr"/>
-      <c r="AF168" t="inlineStr"/>
-      <c r="AG168" t="inlineStr"/>
-      <c r="AH168" t="inlineStr"/>
-      <c r="AI168" t="inlineStr"/>
+      <c r="AF168" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>The worker determines how the current incident response plan meets required standards and records the findings for review.</t>
+        </is>
+      </c>
+      <c r="AH168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>incident response plan, alignment assessment, documentation, requirements, feedback</t>
+        </is>
+      </c>
       <c r="AJ168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -26831,16 +27031,16 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Assist in gathering, processing, and preserving incident evidence in line with organisational requirements and standards.</t>
+          <t>Assist in gathering, processing, and securely preserving evidence in line with established incident response requirements.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>evidence collection, evidence processing, evidence preservation, incident response, organisational requirements</t>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, assistance</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -26906,23 +27106,53 @@
 No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr"/>
-      <c r="V169" t="inlineStr"/>
-      <c r="W169" t="inlineStr"/>
-      <c r="X169" t="inlineStr"/>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Evidence Preservation Assistance</t>
+        </is>
+      </c>
+      <c r="V169" t="b">
+        <v>0</v>
+      </c>
+      <c r="W169" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>added from uncovered PCs</t>
+        </is>
+      </c>
       <c r="Y169" t="inlineStr"/>
-      <c r="Z169" t="inlineStr"/>
+      <c r="Z169" t="b">
+        <v>0</v>
+      </c>
       <c r="AA169" t="inlineStr"/>
-      <c r="AB169" t="inlineStr"/>
+      <c r="AB169" t="b">
+        <v>0</v>
+      </c>
       <c r="AC169" t="inlineStr"/>
-      <c r="AD169" t="inlineStr"/>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
       <c r="AE169" t="inlineStr"/>
-      <c r="AF169" t="inlineStr"/>
-      <c r="AG169" t="inlineStr"/>
-      <c r="AH169" t="inlineStr"/>
-      <c r="AI169" t="inlineStr"/>
+      <c r="AF169" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>Assist in gathering, processing, and securely preserving evidence in line with established incident response requirements.</t>
+        </is>
+      </c>
+      <c r="AH169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>evidence collection, evidence processing, evidence preservation, incident response, assistance</t>
+        </is>
+      </c>
       <c r="AJ169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -26959,7 +27189,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Identify essential business functions, critical data, and software, and assess risk impacts on ICT systems.</t>
+          <t>Identifies essential business functions, critical data, and software, and evaluates risk impacts on ICT systems.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -26968,7 +27198,7 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -27029,23 +27259,53 @@
 No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr"/>
-      <c r="V170" t="inlineStr"/>
-      <c r="W170" t="inlineStr"/>
-      <c r="X170" t="inlineStr"/>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Critical Function Identification</t>
+        </is>
+      </c>
+      <c r="V170" t="b">
+        <v>0</v>
+      </c>
+      <c r="W170" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>added from uncovered PCs</t>
+        </is>
+      </c>
       <c r="Y170" t="inlineStr"/>
-      <c r="Z170" t="inlineStr"/>
+      <c r="Z170" t="b">
+        <v>0</v>
+      </c>
       <c r="AA170" t="inlineStr"/>
-      <c r="AB170" t="inlineStr"/>
+      <c r="AB170" t="b">
+        <v>0</v>
+      </c>
       <c r="AC170" t="inlineStr"/>
-      <c r="AD170" t="inlineStr"/>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
       <c r="AE170" t="inlineStr"/>
-      <c r="AF170" t="inlineStr"/>
-      <c r="AG170" t="inlineStr"/>
-      <c r="AH170" t="inlineStr"/>
-      <c r="AI170" t="inlineStr"/>
+      <c r="AF170" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>Identifies essential business functions, critical data, and software, and evaluates risk impacts on ICT systems.</t>
+        </is>
+      </c>
+      <c r="AH170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>business critical functions, security environment, critical data, software assets, risk impact assessment</t>
+        </is>
+      </c>
       <c r="AJ170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -27152,23 +27412,53 @@
 No licensing, legislative or certification requirements apply to this unit at the time of publication.</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr"/>
-      <c r="V171" t="inlineStr"/>
-      <c r="W171" t="inlineStr"/>
-      <c r="X171" t="inlineStr"/>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Disaster Strategy Documentation</t>
+        </is>
+      </c>
+      <c r="V171" t="b">
+        <v>0</v>
+      </c>
+      <c r="W171" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>added from uncovered PCs</t>
+        </is>
+      </c>
       <c r="Y171" t="inlineStr"/>
-      <c r="Z171" t="inlineStr"/>
+      <c r="Z171" t="b">
+        <v>0</v>
+      </c>
       <c r="AA171" t="inlineStr"/>
-      <c r="AB171" t="inlineStr"/>
+      <c r="AB171" t="b">
+        <v>0</v>
+      </c>
       <c r="AC171" t="inlineStr"/>
-      <c r="AD171" t="inlineStr"/>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
       <c r="AE171" t="inlineStr"/>
-      <c r="AF171" t="inlineStr"/>
-      <c r="AG171" t="inlineStr"/>
-      <c r="AH171" t="inlineStr"/>
-      <c r="AI171" t="inlineStr"/>
+      <c r="AF171" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>Creates and records detailed disaster strategy processes, cut‑over criteria, and secures final task sign‑off.</t>
+        </is>
+      </c>
+      <c r="AH171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>disaster strategy, process documentation, cut‑over criteria, task sign‑off, implementation</t>
+        </is>
+      </c>
       <c r="AJ171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
